--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82131CB-A348-41AF-B4E9-ADE23F53971C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627F0505-D06A-4DFA-B6CE-B66164A99EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3698,29 +3698,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,13 +4131,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>13.639056095083927</v>
+        <v>13.36048258046131</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.21093739792614596</v>
+        <v>0.20236403420229543</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4239,22 +4239,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4266,13 +4266,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4292,13 +4292,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4349,13 +4349,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4419,13 +4419,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4441,7 +4441,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4463,22 +4463,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4539,22 +4539,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4612,22 +4612,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4664,13 +4664,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4793,13 +4793,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4825,13 +4825,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="C107" s="256">
         <f>Valuation_Model!C74</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D107" s="257">
         <f>Valuation_Model!D74</f>
@@ -4865,11 +4865,11 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>36.91 HKD</v>
+        <v>31.78 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C108" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D108" s="244">
         <f>Valuation_Model!D75</f>
@@ -4887,11 +4887,11 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>27.58 HKD</v>
+        <v>25.13 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
-        <v>0.26999999999999996</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
-        <v>0.44999999999999996</v>
+        <v>0.42499999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C111" s="243">
         <f>Valuation_Model!C78</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D111" s="244">
         <f>Valuation_Model!D78</f>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>20.77 HKD</v>
+        <v>19.78 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>24.535432379107018</v>
+        <v>23.991343483359721</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4974,13 +4974,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4993,22 +4993,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>12.562141378102794</v>
+        <v>12.283567863480178</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>13.639056095083927</v>
+        <v>13.36048258046131</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44410777506011379</v>
+        <v>0.44311236301843304</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5104,13 +5104,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5161,22 +5161,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5200,17 +5200,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5227,6 +5216,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>24.539879475424097</v>
+        <v>23.990191457005579</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15008,11 +15008,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2970295.2236168161</v>
+        <v>2955618.9168191827</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2750273.3552007554</v>
+        <v>2736684.1822399837</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15030,11 +15030,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3132593.5617293129</v>
+        <v>3101713.5857495568</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2685694.0686979704</v>
+        <v>2659219.466520539</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15052,11 +15052,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3303759.9579205639</v>
+        <v>3255029.6363568511</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2622631.1711887824</v>
+        <v>2583947.4708162267</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15074,11 +15074,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3484278.9670849852</v>
+        <v>3415924.0176913314</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2561049.0562782548</v>
+        <v>2510806.1278875284</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15096,11 +15096,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3674661.6204259694</v>
+        <v>3584771.3226047144</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2500912.9536467376</v>
+        <v>2439735.1273732316</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15118,11 +15118,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3875446.8721339479</v>
+        <v>3761964.6598738697</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2442188.9094179445</v>
+        <v>2370675.8660601415</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15140,11 +15140,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>4087203.1251116344</v>
+        <v>3947916.5694331438</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2384843.7669880162</v>
+        <v>2303571.3995604725</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15162,11 +15162,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4310529.8400656087</v>
+        <v>4143059.982846125</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2328845.1483047265</v>
+        <v>2238366.3953570509</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15184,11 +15184,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4546059.2325194357</v>
+        <v>4347849.2312530158</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2274161.4355862811</v>
+        <v>2175007.0871776296</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15206,11 +15206,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4794458.062552386</v>
+        <v>4562761.1031403039</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2220761.7534693768</v>
+        <v>2113441.2306606793</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15228,11 +15228,11 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>5056429.5223303176</v>
+        <v>4788295.9543954376</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2168615.9515764387</v>
+        <v>2053618.0602761158</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15250,11 +15250,11 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5332715.2267721491</v>
+        <v>5024978.8732308932</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2117694.5874921978</v>
+        <v>1995488.247465418</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15272,11 +15272,11 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>5624097.3129872866</v>
+        <v>5273360.9026898379</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2067968.9101400012</v>
+        <v>1939003.8599666471</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15294,11 +15294,11 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5931400.6544273123</v>
+        <v>5534020.3235795787</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2019410.8435484585</v>
+        <v>1884118.3222908017</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15316,11 +15316,11 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>6255495.1960199634</v>
+        <v>5807564.0008197464</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1971992.9709992672</v>
+        <v>1830786.377316942</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>37128690.295210198</v>
+        <v>36945236.460239783</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>11704511.631812554</v>
+        <v>11646679.33209395</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>46821556.514347762</v>
+        <v>45481148.553063363</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15712,11 +15712,11 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>46821556.514347762</v>
+        <v>45481148.553063363</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C55" s="132">
         <f>C77</f>
@@ -15728,11 +15728,11 @@
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>35768857.625495642</v>
+        <v>35205068.665891752</v>
       </c>
       <c r="C56" s="124">
         <v>36340968.470146462</v>
@@ -15751,10 +15751,10 @@
         <v>37510887.977851793</v>
       </c>
       <c r="E56" s="124">
+        <v>38716320.083494902</v>
+      </c>
+      <c r="F56" s="124">
         <v>39958803.905536152</v>
-      </c>
-      <c r="F56" s="124">
-        <v>41239925.522459745</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15763,7 +15763,7 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>36314608.993515097</v>
+        <v>35205068.665891744</v>
       </c>
       <c r="C57" s="124">
         <v>37477914.258620426</v>
@@ -15772,10 +15772,10 @@
         <v>39978560.519387558</v>
       </c>
       <c r="E57" s="124">
+        <v>42734270.196406573</v>
+      </c>
+      <c r="F57" s="124">
         <v>45775354.170617849</v>
-      </c>
-      <c r="F57" s="124">
-        <v>49135473.286340058</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15784,7 +15784,7 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>36973335.397705279</v>
+        <v>35205068.665891744</v>
       </c>
       <c r="C58" s="124">
         <v>38885199.917383611</v>
@@ -15793,10 +15793,10 @@
         <v>43195484.615519248</v>
       </c>
       <c r="E58" s="124">
+        <v>48261115.593823448</v>
+      </c>
+      <c r="F58" s="124">
         <v>54232036.738321215</v>
-      </c>
-      <c r="F58" s="124">
-        <v>61287601.010313198</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15805,7 +15805,7 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>37627157.139046498</v>
+        <v>35205068.665891744</v>
       </c>
       <c r="C59" s="124">
         <v>40318998.320719153</v>
@@ -15814,10 +15814,10 @@
         <v>46657943.836927794</v>
       </c>
       <c r="E59" s="124">
+        <v>54565743.918039709</v>
+      </c>
+      <c r="F59" s="124">
         <v>64485548.98913493</v>
-      </c>
-      <c r="F59" s="124">
-        <v>76988009.646113306</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15826,7 +15826,7 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>38219133.923668995</v>
+        <v>35205068.665891737</v>
       </c>
       <c r="C60" s="124">
         <v>41652510.397308387</v>
@@ -15835,10 +15835,10 @@
         <v>50068583.960390151</v>
       </c>
       <c r="E60" s="124">
+        <v>61172802.710238017</v>
+      </c>
+      <c r="F60" s="124">
         <v>75961953.330205008</v>
-      </c>
-      <c r="F60" s="124">
-        <v>95817225.920933262</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15847,7 +15847,7 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>38727170.078919023</v>
+        <v>35205068.665891737</v>
       </c>
       <c r="C61" s="124">
         <v>42828853.551297322</v>
@@ -15856,10 +15856,10 @@
         <v>53262678.661871754</v>
       </c>
       <c r="E61" s="124">
+        <v>67779021.874591023</v>
+      </c>
+      <c r="F61" s="124">
         <v>88270637.479689032</v>
-      </c>
-      <c r="F61" s="124">
-        <v>117558359.89971982</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15883,7 +15883,7 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="133">
         <f>B55</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C64" s="133">
         <f>C55</f>
@@ -15895,11 +15895,11 @@
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -15936,7 +15936,7 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>20.007277218594798</v>
+        <v>19.776072954697451</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
@@ -15948,11 +15948,11 @@
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>21.725532656102466</v>
+        <v>21.2160023565357</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>22.250907932361688</v>
+        <v>21.725532656102466</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>20.231084444977089</v>
+        <v>19.776072954697447</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
@@ -15975,11 +15975,11 @@
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>24.110842264515082</v>
+        <v>22.863723870778671</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>25.488793807418229</v>
+        <v>24.110842264515082</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>20.501221613852373</v>
+        <v>19.776072954697447</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
@@ -16002,11 +16002,11 @@
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>27.578843960491987</v>
+        <v>25.130228384598826</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>30.472260931679948</v>
+        <v>27.578843960491987</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16017,7 +16017,7 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>20.769347429109704</v>
+        <v>19.776072954697447</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
@@ -16029,11 +16029,11 @@
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>31.783707698826568</v>
+        <v>27.715693967094246</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>36.910842886314242</v>
+        <v>31.783707698826568</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>21.012111240641453</v>
+        <v>19.776072954697444</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
@@ -16056,11 +16056,11 @@
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>36.490067361721721</v>
+        <v>30.425183286732462</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>44.632517840081078</v>
+        <v>36.490067361721721</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>21.2204518321109</v>
+        <v>19.776072954697444</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
@@ -16082,11 +16082,11 @@
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>41.537736724253726</v>
+        <v>33.134328283313941</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>53.548341380489717</v>
+        <v>41.537736724253726</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
@@ -16121,11 +16121,11 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>36.910842886314242</v>
+        <v>31.783707698826568</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
@@ -16135,7 +16135,7 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
@@ -16143,11 +16143,11 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>27.578843960491987</v>
+        <v>25.130228384598826</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.26999999999999996</v>
+        <v>0.255</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.44999999999999996</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="H76" s="121"/>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H77" s="121"/>
     </row>
@@ -16204,7 +16204,7 @@
       </c>
       <c r="C78" s="143">
         <f>Scenarios!C50</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>20.769347429109704</v>
+        <v>19.776072954697447</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>25.087130492314564</v>
+        <v>24.543041596567267</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16719,7 +16719,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="165">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="345"/>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>27.578843960491987</v>
+        <v>25.130228384598826</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>24.057136514817582</v>
+        <v>23.322551842049634</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16820,7 +16820,7 @@
         <v>136</v>
       </c>
       <c r="C50" s="165">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D50" s="165"/>
       <c r="E50" s="345"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>20.769347429109704</v>
+        <v>19.776072954697447</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16878,7 +16878,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="165">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="345"/>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>36.910842886314242</v>
+        <v>31.783707698826568</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16904,7 +16904,7 @@
         <v>149</v>
       </c>
       <c r="C58" s="166">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D58" s="166"/>
       <c r="E58" s="345"/>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.535432379107018</v>
+        <v>23.991343483359721</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16965,7 +16965,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>5.4640473721959612E-2</v>
+        <v>4.9429467411718955E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.539879475424097</v>
+        <v>23.990191457005579</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.217596461108054</v>
+        <v>0.22253123344895756</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>12.562141378102794</v>
+        <v>12.283567863480178</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17123,7 +17123,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>13.639056095083927</v>
+        <v>13.36048258046131</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44410777506011379</v>
+        <v>0.44311236301843304</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.21093739792614596</v>
+        <v>0.20236403420229543</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627F0505-D06A-4DFA-B6CE-B66164A99EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8702DB5D-FEE4-4475-A1FF-DA02B82B952E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3698,29 +3698,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4076,7 +4076,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>14.96</v>
+        <v>14.62</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>38668.576673759999</v>
+        <v>37789.745385720002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4131,13 +4131,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4171,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>13.36048258046131</v>
+        <v>13.677042438413379</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.20236403420229543</v>
+        <v>0.22170440631904209</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4239,22 +4239,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4266,13 +4266,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C30" s="188">
         <f>Normalized_FCF!C8</f>
-        <v>3916333.2298004925</v>
+        <v>3205414.6239021346</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4292,13 +4292,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4349,13 +4349,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>93295.094561295133</v>
+        <v>96061.560615225811</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-161125.90543870488</v>
+        <v>-158359.43938477419</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4419,13 +4419,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-938801.83109044691</v>
+        <v>-761763.79612934007</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4441,7 +4441,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4463,22 +4463,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2273287.3685612953</v>
+        <v>2276053.8346152259</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2816405.4932713406</v>
+        <v>2285291.38838802</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.7204543835549769E-2</v>
+        <v>6.4508135967563232E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.687821612349914E-2</v>
+        <v>3.749843268269646E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4539,22 +4539,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4612,22 +4612,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>14.437249697247807</v>
+        <v>11.788861848072179</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4664,13 +4664,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.79399059216043799</v>
+        <v>0.7990176387280199</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14218830.600339578</v>
+        <v>14101839.483409913</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.8310014881140013</v>
+        <v>5.81963904711069</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.3018123614960867</v>
+        <v>0.30372324660088923</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4793,13 +4793,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4825,13 +4825,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4857,15 +4857,15 @@
       </c>
       <c r="C107" s="256">
         <f>Valuation_Model!C74</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D107" s="257">
         <f>Valuation_Model!D74</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>31.78 HKD</v>
+        <v>44.69 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4879,19 +4879,19 @@
       </c>
       <c r="C108" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D108" s="244">
         <f>Valuation_Model!D75</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>25.13 HKD</v>
+        <v>26.92 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
-        <v>0.255</v>
+        <v>0.21249999999999994</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4901,19 +4901,19 @@
       </c>
       <c r="C109" s="243">
         <f>Valuation_Model!C76</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D109" s="244">
         <f>Valuation_Model!D76</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.05 HKD</v>
+        <v>22.2 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
-        <v>0.42499999999999999</v>
+        <v>0.46750000000000003</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
@@ -4927,11 +4927,11 @@
       </c>
       <c r="D110" s="244">
         <f>Valuation_Model!D77</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>21.29 HKD</v>
+        <v>18.83 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4949,11 +4949,11 @@
       </c>
       <c r="D111" s="244">
         <f>Valuation_Model!D78</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>19.78 HKD</v>
+        <v>17.11 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>23.991343483359721</v>
+        <v>24.622857747833486</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4974,13 +4974,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4993,22 +4993,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>1.0769147169811319</v>
+        <v>1.0701392715226352</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>12.283567863480178</v>
+        <v>12.606903166890744</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>13.36048258046131</v>
+        <v>13.677042438413379</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.44311236301843304</v>
+        <v>0.44453878674514158</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5104,13 +5104,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5161,22 +5161,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5200,6 +5200,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5216,17 +5227,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8608,11 +8608,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.704864111724486</v>
+        <v>10.772640544997893</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.4687553971579232</v>
+        <v>4.4970487317420531</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0.4943749385949549</v>
+        <v>0.60402076709908736</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.314915549328939</v>
+        <v>0.25775000437452</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14218830.600339578</v>
+        <v>14101839.483409913</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8870,11 +8870,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2214365.1773135848</v>
+        <v>-2213617.5186202214</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-1972678.6998302105</v>
+        <v>-2031174.2582950436</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>364</v>
@@ -8886,11 +8886,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2028873042685575</v>
+        <v>8.2056578642013953</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>9.2078796215336034</v>
+        <v>8.9427029344330702</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>331</v>
@@ -8903,7 +8903,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>3945357.3996604211</v>
+        <v>4062348.5165900872</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>365</v>
@@ -9018,11 +9018,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2052305.2200000002</v>
+        <v>-2065299.1194412503</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.79399059216043799</v>
+        <v>-0.7990176387280199</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9035,11 +9035,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15071960.436359953</v>
+        <v>15042590.822647545</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.8310014881140004</v>
+        <v>5.8196390471106891</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9052,11 +9052,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>780123.96000000008</v>
+        <v>785063.21181750018</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.30181236149608676</v>
+        <v>0.30372324660088929</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9069,11 +9069,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13799779.176359953</v>
+        <v>13762354.915023796</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.3388232574496488</v>
+        <v>5.3243446549835589</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="C5" s="191">
         <f>C25</f>
-        <v>-21019128.270199507</v>
+        <v>-21529127.876097865</v>
       </c>
       <c r="E5" s="302"/>
       <c r="G5" s="183">
@@ -9319,7 +9319,7 @@
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
-        <v>5143321.2298004925</v>
+        <v>4633321.6239021346</v>
       </c>
       <c r="E6" s="302"/>
       <c r="G6" s="184">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="C7" s="191">
         <f>C35</f>
-        <v>-1226988</v>
+        <v>-1427907</v>
       </c>
       <c r="E7" s="302"/>
       <c r="G7" s="191">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
-        <v>3916333.2298004925</v>
+        <v>3205414.6239021346</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="308"/>
@@ -9653,24 +9653,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-161125.90543870488</v>
+        <v>-158359.43938477419</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-161125.90543870488</v>
+        <v>-158359.43938477419</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-72722.597745827021</v>
+        <v>-69498.638297386715</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-23307.773762573124</v>
+        <v>-20423.937797925319</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80942.166612978894</v>
+        <v>-80007.632127146455</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9708,24 +9708,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3755207.3243617876</v>
+        <v>3047055.1845173603</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3369978.3685612953</v>
+        <v>3372744.8346152259</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>2944874.6762541733</v>
+        <v>2948098.6357026133</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4035794.6512374268</v>
+        <v>4038678.4872020744</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4640431.5873870207</v>
+        <v>4641366.1218728535</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-938801.83109044691</v>
+        <v>-761763.79612934007</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -9875,26 +9875,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2816405.4932713406</v>
+        <v>2285291.38838802</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2273287.3685612953</v>
+        <v>2276053.8346152259</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1875615.6762541733</v>
+        <v>1878839.6357026133</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2684465.6512374268</v>
+        <v>2687349.4872020744</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3323075.5873870207</v>
+        <v>3324010.1218728535</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -9983,26 +9983,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2816405.4932713406</v>
+        <v>2285291.38838802</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2273287.3685612953</v>
+        <v>2276053.8346152259</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1875615.6762541733</v>
+        <v>1878839.6357026133</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2684465.6512374268</v>
+        <v>2687349.4872020744</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3323075.5873870207</v>
+        <v>3324010.1218728535</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
-        <v>-7882695.8898119386</v>
+        <v>-8392695.4957102966</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="299"/>
@@ -10217,7 +10217,7 @@
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
-        <v>-21019128.270199507</v>
+        <v>-21529127.876097865</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="307"/>
@@ -10344,8 +10344,8 @@
         <v>Selling Expenses</v>
       </c>
       <c r="C29" s="63">
-        <f>AVERAGE(G29:J29)</f>
-        <v>0.30129808333932717</v>
+        <f>G29</f>
+        <v>0.32079165583139668</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
-        <v>0.80340826917600006</v>
+        <v>0.82290184166806957</v>
       </c>
       <c r="E30" s="302"/>
       <c r="G30" s="30">
@@ -10469,8 +10469,8 @@
         <v>176</v>
       </c>
       <c r="C33" s="198">
-        <f>AVERAGE(G33:J33)</f>
-        <v>-1226988</v>
+        <f>G33</f>
+        <v>-1427907</v>
       </c>
       <c r="E33" s="300" t="s">
         <v>346</v>
@@ -10586,7 +10586,7 @@
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
-        <v>-1226988</v>
+        <v>-1427907</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="301"/>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C38" s="23">
         <f>ABS(C33/$C$4)</f>
-        <v>4.6898819623139645E-2</v>
+        <v>5.4578490442953362E-2</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="299"/>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
-        <v>4.6898819623139645E-2</v>
+        <v>5.4578490442953362E-2</v>
       </c>
       <c r="E40" s="302"/>
       <c r="G40" s="30">
@@ -10844,19 +10844,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.32560507588568677</v>
+        <v>0.32533785719326741</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36329779792452166</v>
+        <v>0.36290026068033093</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.33498784922552877</v>
+        <v>0.33474854123265141</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2839479052286471</v>
+        <v>0.28389071993555443</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10982,24 +10982,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>93295.094561295133</v>
+        <v>96061.560615225811</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>93295.094561295133</v>
+        <v>96061.560615225811</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>108723.40225417298</v>
+        <v>111947.36170261329</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>97253.226237426876</v>
+        <v>100137.06220207468</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>31515.833387021106</v>
+        <v>32450.367872853545</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11094,24 +11094,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-161125.90543870488</v>
+        <v>-158359.43938477419</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-161125.90543870488</v>
+        <v>-158359.43938477419</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-72722.597745827021</v>
+        <v>-69498.638297386715</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-23307.773762573124</v>
+        <v>-20423.937797925319</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80942.166612978894</v>
+        <v>-80007.632127146455</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>15.393120968003791</v>
+        <v>12.598860250931073</v>
       </c>
       <c r="E55" s="302"/>
       <c r="G55" s="42">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
-        <v>0.80340826917600006</v>
+        <v>0.82290184166806957</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="299"/>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
-        <v>0.19659173082399997</v>
+        <v>0.17709815833193046</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="299"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
-        <v>4.6898819623139645E-2</v>
+        <v>5.4578490442953362E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="299"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
-        <v>0.14969291120086031</v>
+        <v>0.12251966788897709</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="299"/>
@@ -12181,26 +12181,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.1586704807095709E-3</v>
+        <v>6.0529286214111638E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.6189116819003807E-3</v>
+        <v>5.5224372609456113E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.6350207968191819E-3</v>
+        <v>2.5182042850598867E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>9.0328364162843003E-4</v>
+        <v>7.9152170852656489E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5859099314322239E-3</v>
+        <v>3.5445080684201324E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12238,26 +12238,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.14353424072015075</v>
+        <v>0.11646673926756591</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.11752058597469969</v>
+        <v>0.11761706039565445</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10670419177099839</v>
+        <v>0.10682100828275767</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.15640564073468299</v>
+        <v>0.15651740266778486</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.20558097727859317</v>
+        <v>0.2056223791416053</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.5883560180037688E-2</v>
+        <v>2.9116684816891478E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12410,26 +12410,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.10765068054011306</v>
+        <v>8.7350054450674425E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>7.9275898662892946E-2</v>
+        <v>7.9372373083847703E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>6.7960805402519045E-2</v>
+        <v>6.8077621914278325E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.10403541470656878</v>
+        <v>0.10414717663967063</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.14721930793733343</v>
+        <v>0.14726070980034553</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12517,26 +12517,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.10765068054011306</v>
+        <v>8.7350054450674425E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>7.9275898662892946E-2</v>
+        <v>7.9372373083847703E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>6.7960805402519045E-2</v>
+        <v>6.8077621914278325E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.10403541470656878</v>
+        <v>0.10414717663967063</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.14721930793733343</v>
+        <v>0.14726070980034553</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12586,12 +12586,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12642,12 +12642,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>1426028.1277630189</v>
+        <v>1417056.2234426606</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>1426028.1277630189</v>
+        <v>1417056.2234426606</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.50632912454187973</v>
+        <v>0.62007682286949495</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.62729778359060473</v>
+        <v>0.62259345622298001</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -12752,12 +12752,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.687821612349914E-2</v>
+        <v>3.749843268269646E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.687821612349914E-2</v>
+        <v>3.749843268269646E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -12889,26 +12889,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>0.11431199659745994</v>
+        <v>-9.6565161631926855E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.14435374643780974</v>
+        <v>0.14404070263117497</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.27031107111675357</v>
+        <v>-0.27003383779009249</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.13029756494913847</v>
+        <v>-0.1298513452387563</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4877487103528138</v>
+        <v>1.4882497169764712</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13504,15 +13504,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.4994118247947061</v>
+        <v>2.4951230061989262</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.4578707677619163</v>
+        <v>1.4563063042740438</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.9636432661259322</v>
+        <v>1.9630911942961888</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13608,24 +13608,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.14353424072015075</v>
+        <v>0.11646673926756591</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.11752058597469969</v>
+        <v>0.11761706039565445</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10670419177099839</v>
+        <v>0.10682100828275767</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.15640564073468299</v>
+        <v>0.15651740266778486</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.20558097727859317</v>
+        <v>0.2056223791416053</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
-        <v>0.15002987622939012</v>
+        <v>0.12279546480584161</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="305"/>
@@ -13894,50 +13894,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.1549799757798245</v>
+        <v>0.94310894784577437</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.93225261637726409</v>
+        <v>0.9392967339357251</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.76917139719681582</v>
+        <v>0.77537178891148462</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.100872754386885</v>
+        <v>1.1090329050584524</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.362760359118862</v>
+        <v>1.3717741661291969</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.53965092930557346</v>
+        <v>0.5430676578898207</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.42459498273053775</v>
+        <v>0.42728324978511362</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.21710046216665421</v>
+        <v>0.21847500506921647</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.15570013387344489</v>
+        <v>0.15668592870689602</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.0920253167366974E-2</v>
+        <v>9.1495902741960844E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>2.0853080960365031E-3</v>
+        <v>2.098510948828508E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13951,50 +13951,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.7204543835549769E-2</v>
+        <v>6.4508135967563232E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.2316351362116579E-2</v>
+        <v>6.4247382622142621E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.1415200347380736E-2</v>
+        <v>5.3035006081496895E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.3587750961690165E-2</v>
+        <v>7.5857243848047359E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.1093606892972051E-2</v>
+        <v>9.3828602334418393E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.6072923081923357E-2</v>
+        <v>3.7145530635418651E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.8382017562201718E-2</v>
+        <v>2.9225940477777951E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.4512062979054425E-2</v>
+        <v>1.4943570798168021E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.0407762959454872E-2</v>
+        <v>1.0717231785697402E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.0775570299042092E-3</v>
+        <v>6.2582696813926709E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.3939225240885714E-4</v>
+        <v>1.4353700060386513E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14008,23 +14008,23 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2416015124823464E-5</v>
+        <v>8.4332666639354238E-5</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2416015124823464E-5</v>
+        <v>8.4332666639354238E-5</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0509396387371209E-4</v>
+        <v>1.0753800954519378E-4</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.392414063568493E-5</v>
+        <v>4.4945632278375277E-5</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.392414063568493E-5</v>
+        <v>4.4945632278375277E-5</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14794,7 +14794,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2816405.4932713406</v>
+        <v>2285291.38838802</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>35205068.665891759</v>
+        <v>28566142.354850248</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14218830.600339578</v>
+        <v>14101839.483409913</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -14892,7 +14892,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>48223728.266231336</v>
+        <v>41467810.838260159</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06</v>
+        <v>1.0667112500000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14953,7 +14953,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14963,7 +14963,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>23.990191457005579</v>
+        <v>24.625357371246121</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15008,11 +15008,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2955618.9168191827</v>
+        <v>2437716.3832667922</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2736684.1822399837</v>
+        <v>2257144.7993211034</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15030,11 +15030,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>3101713.5857495568</v>
+        <v>2600307.8624643022</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15042,7 +15042,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2659219.466520539</v>
+        <v>2229344.8752265964</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15052,11 +15052,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>3255029.6363568511</v>
+        <v>2773743.9129536571</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2583947.4708162267</v>
+        <v>2201887.3464360558</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15074,11 +15074,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3415924.0176913314</v>
+        <v>2958747.8489397853</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2510806.1278875284</v>
+        <v>2174767.9958680333</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15096,11 +15096,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3584771.3226047144</v>
+        <v>3156091.2284378102</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2439735.1273732316</v>
+        <v>2147982.6583803897</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15118,11 +15118,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3761964.6598738697</v>
+        <v>3366597.0710519995</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2370675.8660601415</v>
+        <v>2121527.2201305912</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15140,11 +15140,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3947916.5694331438</v>
+        <v>3591143.2903750222</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2303571.3995604725</v>
+        <v>2095397.6179438818</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15162,11 +15162,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4143059.982846125</v>
+        <v>3830666.355322313</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2238366.3953570509</v>
+        <v>2069589.838689235</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15184,11 +15184,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4347849.2312530158</v>
+        <v>4086165.1956711356</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2175007.0871776296</v>
+        <v>2044099.9186630019</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15206,11 +15206,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4562761.1031403039</v>
+        <v>4358705.3680923507</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2113441.2306606793</v>
+        <v>2018923.9429801335</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15228,11 +15228,11 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4788295.9543954376</v>
+        <v>4649423.5000493377</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2053618.0602761158</v>
+        <v>1994058.0449729203</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15250,11 +15250,11 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5024978.8732308932</v>
+        <v>4959532.0300972955</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1995488.247465418</v>
+        <v>1969498.4055971203</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15272,11 +15272,11 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>5273360.9026898379</v>
+        <v>5290324.2643523403</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1939003.8599666471</v>
+        <v>1945241.2528454135</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15294,11 +15294,11 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5534020.3235795787</v>
+        <v>5643179.7702183751</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1884118.3222908017</v>
+        <v>1921282.8611680726</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15316,11 +15316,11 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5807564.0008197464</v>
+        <v>6019570.1298662378</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1830786.377316942</v>
+        <v>1897619.5509007762</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15338,19 +15338,19 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6421065.0774599761</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.29189046756100923</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1874247.6876994604</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15360,19 +15360,19 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6849339.045725558</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27026895144537894</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1851163.6819821389</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15382,19 +15382,19 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7306178.149164401</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25024902911609154</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1828363.9883775939</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15404,19 +15404,19 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7793487.6330352155</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.23171206399638106</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1805845.1051808603</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15426,19 +15426,19 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8313299.8191700839</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>0</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.21454820740405653</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1783603.5738154089</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>36945236.460239783</v>
+        <v>30471454.7908349</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15676,11 +15676,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.31524170496588994</v>
+        <v>0.21454820740405653</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>11646679.33209395</v>
+        <v>6537596.0023673782</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>45481148.553063363</v>
+        <v>46769186.368546158</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15712,7 +15712,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>45481148.553063363</v>
+        <v>46769186.368546158</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15724,15 +15724,15 @@
       </c>
       <c r="D55" s="132">
         <f>C76</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -15742,19 +15742,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>35205068.665891752</v>
+        <v>28566142.35485024</v>
       </c>
       <c r="C56" s="124">
-        <v>36340968.470146462</v>
+        <v>29487835.643311966</v>
       </c>
       <c r="D56" s="124">
-        <v>37510887.977851793</v>
+        <v>30922510.754459143</v>
       </c>
       <c r="E56" s="124">
-        <v>38716320.083494902</v>
+        <v>32423424.351988211</v>
       </c>
       <c r="F56" s="124">
-        <v>39958803.905536152</v>
+        <v>33462953.711531028</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15763,19 +15763,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>35205068.665891744</v>
+        <v>28566142.354850236</v>
       </c>
       <c r="C57" s="124">
-        <v>37477914.258620426</v>
+        <v>30410377.665641867</v>
       </c>
       <c r="D57" s="124">
-        <v>39978560.519387558</v>
+        <v>33530129.11923106</v>
       </c>
       <c r="E57" s="124">
-        <v>42734270.196406573</v>
+        <v>37143097.091824263</v>
       </c>
       <c r="F57" s="124">
-        <v>45775354.170617849</v>
+        <v>39869569.291038275</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15784,19 +15784,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>35205068.665891744</v>
+        <v>28566142.354850233</v>
       </c>
       <c r="C58" s="124">
-        <v>38885199.917383611</v>
+        <v>31552279.215208128</v>
       </c>
       <c r="D58" s="124">
-        <v>43195484.615519248</v>
+        <v>37021211.20419392</v>
       </c>
       <c r="E58" s="124">
-        <v>48261115.593823448</v>
+        <v>44005029.39968092</v>
       </c>
       <c r="F58" s="124">
-        <v>54232036.738321215</v>
+        <v>49730064.487676337</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15805,19 +15805,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>35205068.665891744</v>
+        <v>28566142.354850233</v>
       </c>
       <c r="C59" s="124">
-        <v>40318998.320719153</v>
+        <v>32715693.770269688</v>
       </c>
       <c r="D59" s="124">
-        <v>46657943.836927794</v>
+        <v>40888058.504714973</v>
       </c>
       <c r="E59" s="124">
-        <v>54565743.918039709</v>
+        <v>52324947.573217206</v>
       </c>
       <c r="F59" s="124">
-        <v>64485548.98913493</v>
+        <v>62469710.371512175</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -15826,19 +15826,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>35205068.665891737</v>
+        <v>28566142.354850225</v>
       </c>
       <c r="C60" s="124">
-        <v>41652510.397308387</v>
+        <v>33797733.864361778</v>
       </c>
       <c r="D60" s="124">
-        <v>50068583.960390151</v>
+        <v>44814767.792200834</v>
       </c>
       <c r="E60" s="124">
-        <v>61172802.710238017</v>
+        <v>61637146.428447738</v>
       </c>
       <c r="F60" s="124">
-        <v>75961953.330205008</v>
+        <v>77748137.396933392</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -15847,19 +15847,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>35205068.665891737</v>
+        <v>28566142.354850229</v>
       </c>
       <c r="C61" s="124">
-        <v>42828853.551297322</v>
+        <v>34752243.747978568</v>
       </c>
       <c r="D61" s="124">
-        <v>53262678.661871754</v>
+        <v>48612075.849363364</v>
       </c>
       <c r="E61" s="124">
-        <v>67779021.874591023</v>
+        <v>71624674.842380583</v>
       </c>
       <c r="F61" s="124">
-        <v>88270637.479689032</v>
+        <v>95389356.452290609</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -15891,15 +15891,15 @@
       </c>
       <c r="D64" s="133">
         <f>D55</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -15909,23 +15909,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15936,23 +15936,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>19.776072954697451</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>20.241894205060998</v>
+        <v>17.49357689780474</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>20.721666598596684</v>
+        <v>18.085647975239173</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>21.2160023565357</v>
+        <v>18.705054783038651</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>21.725532656102466</v>
+        <v>19.134054535768108</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15963,23 +15963,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>19.776072954697447</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>20.708144403184768</v>
+        <v>17.874297553579307</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>21.733634647609765</v>
+        <v>19.161776920930457</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>22.863723870778671</v>
+        <v>20.65280009659487</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>24.110842264515082</v>
+        <v>21.777978417485166</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15990,23 +15990,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>19.776072954697447</v>
+        <v>17.113206503055732</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>21.285258302428609</v>
+        <v>18.345544929046177</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>23.052863332368528</v>
+        <v>20.602499433920347</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>25.130228384598826</v>
+        <v>23.484627053951272</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.578843960491987</v>
+        <v>25.847271855246401</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16017,23 +16017,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>19.776072954697447</v>
+        <v>17.113206503055732</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>21.873244815419721</v>
+        <v>18.825670431862921</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>24.472783538189471</v>
+        <v>22.19829518565907</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>27.715693967094246</v>
+        <v>26.918145122884049</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>31.783707698826568</v>
+        <v>31.104751967621535</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16044,23 +16044,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>19.776072954697444</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>22.420104899878716</v>
+        <v>19.272213791651254</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.871453245588292</v>
+        <v>23.818795172415349</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>30.425183286732462</v>
+        <v>30.761164052160265</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>36.490067361721721</v>
+        <v>37.409952831677344</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16070,23 +16070,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>19.776072954697444</v>
+        <v>17.113206503055732</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>22.902511567082303</v>
+        <v>19.666127152818387</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>27.181319821892497</v>
+        <v>25.385893015882459</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>33.134328283313941</v>
+        <v>34.882882386157092</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>41.537736724253726</v>
+        <v>44.690246113555276</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16113,15 +16113,15 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>31.783707698826568</v>
+        <v>44.690246113555276</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16135,19 +16135,19 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>25.130228384598826</v>
+        <v>26.918145122884049</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.255</v>
+        <v>0.21249999999999994</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -16158,19 +16158,19 @@
       </c>
       <c r="C76" s="143">
         <f>Scenarios!C26</f>
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.052863332368528</v>
+        <v>22.19829518565907</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.42499999999999999</v>
+        <v>0.46750000000000003</v>
       </c>
       <c r="H76" s="121"/>
     </row>
@@ -16185,11 +16185,11 @@
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>21.285258302428609</v>
+        <v>18.825670431862921</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16208,11 +16208,11 @@
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>19.776072954697447</v>
+        <v>17.113206503055732</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.96</v>
+        <v>-14.62</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>24.543041596567267</v>
+        <v>25.171084833654508</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16379,7 +16379,7 @@
       </c>
       <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 15-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 20-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+        <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
       <c r="F7" s="346"/>
       <c r="H7" s="276">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2273287.3685612953</v>
+        <v>2276053.8346152259</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2816405.4932713406</v>
+        <v>2285291.38838802</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.11887395301890247</v>
+        <v>-0.1185992870057041</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
@@ -16529,7 +16529,7 @@
         <v>135</v>
       </c>
       <c r="C18" s="151">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E18" s="346" t="s">
         <v>343</v>
@@ -16553,7 +16553,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.96</v>
+        <v>14.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>19.776072954697455</v>
+        <v>17.113206503055739</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="C25" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D25" s="164"/>
       <c r="E25" s="345"/>
@@ -16603,7 +16603,7 @@
         <v>136</v>
       </c>
       <c r="C26" s="165">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
       <c r="E26" s="345"/>
@@ -16615,7 +16615,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.052863332368528</v>
+        <v>22.19829518565907</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16629,7 +16629,7 @@
         <v>149</v>
       </c>
       <c r="C28" s="166">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
       <c r="E28" s="345"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="C31" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D31" s="164"/>
       <c r="E31" s="345"/>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>21.285258302428609</v>
+        <v>18.825670431862921</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="C37" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D37" s="164"/>
       <c r="E37" s="345"/>
@@ -16719,7 +16719,7 @@
         <v>136</v>
       </c>
       <c r="C38" s="165">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="345"/>
@@ -16731,7 +16731,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>25.130228384598826</v>
+        <v>26.918145122884049</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
-        <v>0.3</v>
+        <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
       <c r="E40" s="345"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.322551842049634</v>
+        <v>22.703732719206084</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16784,7 +16784,7 @@
         <v>135</v>
       </c>
       <c r="C46" s="151">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="C49" s="167">
         <f>C46</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D49" s="164"/>
       <c r="E49" s="345"/>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>19.776072954697447</v>
+        <v>17.113206503055732</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="C55" s="167">
         <f>C46</f>
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D55" s="164"/>
       <c r="E55" s="345"/>
@@ -16878,7 +16878,7 @@
         <v>136</v>
       </c>
       <c r="C56" s="165">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
       <c r="E56" s="345"/>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>31.783707698826568</v>
+        <v>44.690246113555276</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>23.991343483359721</v>
+        <v>24.622857747833486</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="C64" s="167">
         <f>C18</f>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
@@ -16965,7 +16965,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>4.9429467411718955E-2</v>
+        <v>6.6698275613022898E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>23.990191457005579</v>
+        <v>24.625357371246121</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17041,7 +17041,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.22253123344895756</v>
+        <v>0.21623585326735834</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.55169811320754714</v>
+        <v>0.5482270858210222</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.0769147169811319</v>
+        <v>1.0701392715226352</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>12.283567863480178</v>
+        <v>12.606903166890744</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17123,7 +17123,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>13.36048258046131</v>
+        <v>13.677042438413379</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.44311236301843304</v>
+        <v>0.44453878674514158</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.96</v>
+        <v>14.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.20236403420229543</v>
+        <v>0.22170440631904209</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8702DB5D-FEE4-4475-A1FF-DA02B82B952E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF66D713-8B06-4F84-B3DA-0EFD2E979C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1825,14 +1821,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2322,16 +2310,58 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李宁</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>2331.HK</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>李宁</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNS_02</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -3005,7 +3035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3698,29 +3728,32 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4010,7 +4043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4030,15 +4063,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4062,13 +4095,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4095,7 +4128,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4105,7 +4138,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4131,24 +4164,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="B12" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4158,10 +4191,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4171,7 +4204,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4184,18 +4217,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4204,10 +4242,10 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>13.677042438413379</v>
+        <v>13.677042438413375</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4215,11 +4253,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22170440631904209</v>
+        <v>0.22170440631904187</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4230,7 +4268,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,22 +4277,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="B25" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="B26" s="342" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4266,13 +4304,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4292,13 +4330,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4327,13 +4365,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4349,21 +4387,21 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96061.560615225811</v>
+        <v>96061.560615225826</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4374,7 +4412,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4407,7 +4445,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4419,13 +4457,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4441,13 +4479,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4463,26 +4501,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="B53" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
-        <v>377</v>
-      </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="B54" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4508,25 +4546,25 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.4508135967563232E-2</v>
+        <v>6.4508135967563204E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.749843268269646E-2</v>
+        <v>3.7498432682696467E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,22 +4577,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
-        <v>378</v>
-      </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="B63" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4563,7 +4601,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4571,26 +4609,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4607,27 +4645,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="B73" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
-        <v>380</v>
-      </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="B74" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4639,11 +4677,11 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>11.788861848072179</v>
+        <v>11.788861848072175</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4652,7 +4690,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,13 +4702,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
-        <v>381</v>
-      </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="B81" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4683,13 +4721,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="B85" s="339" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4706,11 +4744,11 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.7990176387280199</v>
+        <v>0.79901763872801979</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4724,7 +4762,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4737,11 +4775,11 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14101839.483409913</v>
+        <v>14101839.483409911</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4750,11 +4788,11 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.81963904711069</v>
+        <v>5.8196390471106874</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4781,11 +4819,11 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>0.30372324660088923</v>
+        <v>0.30372324660088917</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4793,21 +4831,21 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
-        <v>382</v>
-      </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="B98" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4816,7 +4854,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,13 +4863,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
-        <v>383</v>
-      </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="B104" s="340" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4966,7 +5004,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>24.622857747833486</v>
+        <v>24.622857747833478</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4974,17 +5012,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
-        <v>386</v>
-      </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="B115" s="343" t="s">
+        <v>383</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,22 +5031,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
-        <v>384</v>
-      </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="B119" s="344" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
-        <v>385</v>
-      </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="B120" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5017,7 +5055,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5026,7 +5064,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5039,7 +5077,7 @@
       </c>
       <c r="C124" s="237">
         <f>Scenarios!C77</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
       <c r="D124" s="236" t="str">
         <f>Market_currency</f>
@@ -5048,7 +5086,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>416</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5058,7 +5096,7 @@
       </c>
       <c r="C127" s="240">
         <f>Scenarios!C81</f>
-        <v>1.0701392715226352</v>
+        <v>1.0701392715226354</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5068,7 +5106,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>12.606903166890744</v>
+        <v>12.60690316689074</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5077,7 +5115,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>13.677042438413379</v>
+        <v>13.677042438413375</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5093,124 +5131,160 @@
         <v>0.44453878674514158</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>1.5374014324364951</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>22.240624158106684</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>23.77802559054318</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>3.4310889740839845E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>389</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>395</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
-        <v>397</v>
-      </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
-        <v>398</v>
-      </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
-        <v>399</v>
-      </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5227,9 +5301,20 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B143:F143"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5774,7 +5859,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181">
@@ -5808,7 +5893,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181">
@@ -5842,7 +5927,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181">
@@ -5881,7 +5966,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5899,7 +5984,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>221</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7204,7 +7289,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7257,7 +7342,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8575,13 +8660,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8589,7 +8674,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8608,11 +8693,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.772640544997893</v>
+        <v>10.772640544997891</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.4970487317420531</v>
+        <v>4.4970487317420522</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8742,7 +8827,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8765,7 +8850,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8787,7 +8872,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8803,7 +8888,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14101839.483409913</v>
+        <v>14101839.483409911</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>228</v>
@@ -8854,7 +8939,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8866,52 +8951,52 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2213617.5186202214</v>
+        <v>-2213617.5186202219</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2031174.2582950436</v>
+        <v>-2031174.2582950441</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2056578642013953</v>
+        <v>8.2056578642013935</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9427029344330702</v>
+        <v>8.9427029344330666</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4062348.5165900872</v>
+        <v>4062348.5165900881</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8919,7 +9004,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8995,7 +9080,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9006,23 +9091,23 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2065299.1194412503</v>
+        <v>-2065299.1194412501</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-0.7990176387280199</v>
+        <v>-0.79901763872801979</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9031,15 +9116,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15042590.822647545</v>
+        <v>15042590.822647542</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.8196390471106891</v>
+        <v>5.8196390471106874</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9052,11 +9137,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>785063.21181750018</v>
+        <v>785063.21181749995</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>0.30372324660088929</v>
+        <v>0.30372324660088917</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9065,15 +9150,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13762354.915023796</v>
+        <v>13762354.915023791</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.3243446549835589</v>
+        <v>5.3243446549835562</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9662,11 +9747,11 @@
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69498.638297386715</v>
+        <v>-69498.6382973867</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20423.937797925319</v>
+        <v>-20423.937797925304</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
@@ -9717,7 +9802,7 @@
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>2948098.6357026133</v>
+        <v>2948098.6357026137</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
@@ -9886,7 +9971,7 @@
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>1878839.6357026133</v>
+        <v>1878839.6357026137</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
@@ -9936,7 +10021,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9961,7 +10046,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -9994,7 +10079,7 @@
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>1878839.6357026133</v>
+        <v>1878839.6357026137</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
@@ -10289,7 +10374,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10349,7 +10434,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10473,7 +10558,7 @@
         <v>-1427907</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10531,7 +10616,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10839,7 +10924,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10848,7 +10933,7 @@
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.36290026068033093</v>
+        <v>0.36290026068033088</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
@@ -10978,28 +11063,28 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96061.560615225811</v>
+        <v>96061.560615225826</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96061.560615225811</v>
+        <v>96061.560615225826</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111947.36170261329</v>
+        <v>111947.3617026133</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100137.06220207468</v>
+        <v>100137.0622020747</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32450.367872853545</v>
+        <v>32450.367872853549</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11033,7 +11118,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11103,11 +11188,11 @@
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69498.638297386715</v>
+        <v>-69498.6382973867</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20423.937797925319</v>
+        <v>-20423.937797925304</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
@@ -11166,7 +11251,7 @@
         <v>2.3646804360316024E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11193,7 +11278,7 @@
         <v>0.13140650687425529</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11508,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12069,7 +12154,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12192,11 +12277,11 @@
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5182042850598867E-3</v>
+        <v>2.5182042850598859E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9152170852656489E-4</v>
+        <v>7.9152170852656424E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
@@ -12249,7 +12334,7 @@
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.10682100828275767</v>
+        <v>0.1068210082827577</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
@@ -12421,7 +12506,7 @@
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>6.8077621914278325E-2</v>
+        <v>6.8077621914278352E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
@@ -12528,7 +12613,7 @@
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>6.8077621914278325E-2</v>
+        <v>6.8077621914278352E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
@@ -12586,12 +12671,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12642,12 +12727,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/$C$3</f>
-        <v>1417056.2234426606</v>
+        <v>1417056.2234426609</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
-        <v>1417056.2234426606</v>
+        <v>1417056.2234426609</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12697,12 +12782,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>0.62007682286949495</v>
+        <v>0.62007682286949506</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>0.62259345622298001</v>
+        <v>0.62259345622298023</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -12748,16 +12833,16 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.749843268269646E-2</v>
+        <v>3.7498432682696467E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.749843268269646E-2</v>
+        <v>3.7498432682696467E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -12896,11 +12981,11 @@
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>0.14404070263117497</v>
+        <v>0.14404070263117474</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.27003383779009249</v>
+        <v>-0.27003383779009238</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
@@ -13442,7 +13527,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13494,7 +13579,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13504,7 +13589,7 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.4951230061989262</v>
+        <v>2.4951230061989258</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
@@ -13617,7 +13702,7 @@
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.10682100828275767</v>
+        <v>0.1068210082827577</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
@@ -13894,50 +13979,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.94310894784577437</v>
+        <v>0.94310894784577415</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.9392967339357251</v>
+        <v>0.93929673393572488</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.77537178891148462</v>
+        <v>0.77537178891148473</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1090329050584524</v>
+        <v>1.1090329050584522</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3717741661291969</v>
+        <v>1.3717741661291967</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.5430676578898207</v>
+        <v>0.54306765788982059</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.42728324978511362</v>
+        <v>0.42728324978511351</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.21847500506921647</v>
+        <v>0.21847500506921644</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.15668592870689602</v>
+        <v>0.15668592870689596</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.1495902741960844E-2</v>
+        <v>9.149590274196083E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>2.098510948828508E-3</v>
+        <v>2.0985109488285076E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13947,54 +14032,54 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.4508135967563232E-2</v>
+        <v>6.4508135967563204E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.4247382622142621E-2</v>
+        <v>6.4247382622142607E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.3035006081496895E-2</v>
+        <v>5.3035006081496909E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.5857243848047359E-2</v>
+        <v>7.5857243848047345E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.3828602334418393E-2</v>
+        <v>9.3828602334418379E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7145530635418651E-2</v>
+        <v>3.7145530635418644E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.9225940477777951E-2</v>
+        <v>2.9225940477777945E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.4943570798168021E-2</v>
+        <v>1.4943570798168019E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.0717231785697402E-2</v>
+        <v>1.0717231785697398E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2582696813926709E-3</v>
+        <v>6.2582696813926701E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.4353700060386513E-4</v>
+        <v>1.4353700060386511E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14003,7 +14088,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14832,10 +14917,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14850,8 +14935,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14860,14 +14945,14 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14101839.483409913</v>
+        <v>14101839.483409911</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14882,8 +14967,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14906,7 +14991,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0667112500000002</v>
+        <v>1.06671125</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14920,7 +15005,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14973,7 +15058,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>24.625357371246121</v>
+        <v>24.625357371246114</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15909,23 +15994,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15936,23 +16021,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.113206503055736</v>
+        <v>17.113206503055732</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>17.49357689780474</v>
+        <v>17.493576897804733</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.085647975239173</v>
+        <v>18.085647975239169</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>18.705054783038651</v>
+        <v>18.705054783038648</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>19.134054535768108</v>
+        <v>19.134054535768104</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15963,23 +16048,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.113206503055736</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>17.874297553579307</v>
+        <v>17.874297553579304</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>19.161776920930457</v>
+        <v>19.161776920930453</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.65280009659487</v>
+        <v>20.652800096594866</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>21.777978417485166</v>
+        <v>21.777978417485162</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15990,23 +16075,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.113206503055732</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>18.345544929046177</v>
+        <v>18.345544929046174</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>20.602499433920347</v>
+        <v>20.602499433920343</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>23.484627053951272</v>
+        <v>23.484627053951264</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>25.847271855246401</v>
+        <v>25.847271855246397</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16017,23 +16102,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.113206503055732</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>18.825670431862921</v>
+        <v>18.825670431862918</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>22.19829518565907</v>
+        <v>22.198295185659067</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>26.918145122884049</v>
+        <v>26.918145122884042</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>31.104751967621535</v>
+        <v>31.104751967621528</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16044,23 +16129,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.113206503055729</v>
+        <v>17.113206503055725</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>19.272213791651254</v>
+        <v>19.27221379165125</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>23.818795172415349</v>
+        <v>23.818795172415342</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>30.761164052160265</v>
+        <v>30.761164052160257</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>37.409952831677344</v>
+        <v>37.409952831677337</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16070,23 +16155,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.113206503055732</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>19.666127152818387</v>
+        <v>19.666127152818383</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>25.385893015882459</v>
+        <v>25.385893015882452</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>34.882882386157092</v>
+        <v>34.882882386157085</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>44.690246113555276</v>
+        <v>44.690246113555268</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16121,7 +16206,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>44.690246113555276</v>
+        <v>44.690246113555268</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16143,7 +16228,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>26.918145122884049</v>
+        <v>26.918145122884042</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16166,7 +16251,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>22.19829518565907</v>
+        <v>22.198295185659067</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16189,7 +16274,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>18.825670431862921</v>
+        <v>18.825670431862918</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16212,7 +16297,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.113206503055732</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16228,7 +16313,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16280,7 +16365,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16300,7 +16385,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16333,7 +16418,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
@@ -16342,7 +16427,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
@@ -16354,7 +16439,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16362,12 +16447,12 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>25.171084833654508</v>
+        <v>25.171084833654501</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16377,11 +16462,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16402,8 +16487,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16424,8 +16509,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16435,8 +16520,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16447,10 +16532,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16468,8 +16553,8 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16486,8 +16571,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16504,8 +16589,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1185992870057041</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16521,7 +16606,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16531,25 +16616,25 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16559,23 +16644,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.113206503055739</v>
+        <v>17.113206503055736</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16595,8 +16680,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16606,8 +16691,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16615,14 +16700,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>22.19829518565907</v>
+        <v>22.198295185659067</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16632,8 +16717,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16653,8 +16738,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16664,8 +16749,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16673,14 +16758,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>18.825670431862921</v>
+        <v>18.825670431862918</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16690,8 +16775,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16711,8 +16796,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16722,8 +16807,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16731,14 +16816,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>26.918145122884049</v>
+        <v>26.918145122884042</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16749,8 +16834,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16758,7 +16843,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>22.703732719206084</v>
+        <v>22.70373271920608</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16812,8 +16897,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16823,8 +16908,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16832,14 +16917,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.113206503055732</v>
+        <v>17.113206503055729</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16849,12 +16934,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16870,8 +16955,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16881,8 +16966,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16890,14 +16975,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>44.690246113555276</v>
+        <v>44.690246113555268</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16907,8 +16992,8 @@
         <v>0.1</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16916,14 +17001,14 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.622857747833486</v>
+        <v>24.622857747833478</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16932,7 +17017,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16941,10 +17026,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16957,7 +17042,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16969,7 +17054,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16978,27 +17063,27 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.625357371246121</v>
+        <v>24.625357371246114</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17008,19 +17093,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17030,18 +17115,18 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.21623585326735834</v>
+        <v>0.21623585326735828</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17060,7 +17145,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17074,7 +17159,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.5482270858210222</v>
+        <v>0.54822708582102231</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17083,12 +17168,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -17101,7 +17186,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.0701392715226352</v>
+        <v>1.0701392715226354</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17113,7 +17198,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>12.606903166890744</v>
+        <v>12.60690316689074</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17123,7 +17208,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>13.677042438413379</v>
+        <v>13.677042438413375</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17142,12 +17227,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17160,53 +17245,109 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22170440631904209</v>
+        <v>0.22170440631904187</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>413</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>1.5374014324364951</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>22.240624158106684</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>414</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>23.77802559054318</v>
+      </c>
+      <c r="D93" t="s">
+        <v>411</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>3.4310889740839845E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF66D713-8B06-4F84-B3DA-0EFD2E979C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB00FC-54F7-49EE-82AA-CC78016F5925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="427">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2321,31 +2317,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3035,7 +3047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3731,6 +3743,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4043,7 +4060,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4063,10 +4080,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4095,13 +4112,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4128,7 +4145,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4164,24 +4181,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4191,10 +4208,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4217,19 +4234,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4241,11 +4258,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>13.677042438413375</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4253,7 +4270,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4268,7 +4285,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4277,22 +4294,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4304,13 +4321,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4330,13 +4347,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4365,13 +4382,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4387,17 +4404,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4412,7 +4429,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4457,13 +4474,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4479,13 +4496,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4501,22 +4518,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4546,7 +4563,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4555,7 +4572,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4564,7 +4581,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4577,22 +4594,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>375</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4601,7 +4618,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4609,26 +4626,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4645,27 +4662,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4677,7 +4694,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4690,7 +4707,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4702,13 +4719,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4721,13 +4738,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4744,7 +4761,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4755,537 +4772,577 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>0.36794481423679237</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>7.4171010848313429E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>422</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>0.60402076709908736</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>18164188</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>14101839.483409911</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>5.8196390471106874</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>735966</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>0.30372324660088917</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>378</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>17.113206503055736</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>371</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>380</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>421</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>4.4970487317420522</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>370</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>379</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>44.69 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.08</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>20</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>26.92 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.21249999999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.05</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>20</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>22.2 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.46750000000000003</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>20</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>18.83 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.17</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>17.11 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>24.622857747833478</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>383</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>419</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>382</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>417</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>380</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>381</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>0.54822708582102231</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>1.0701392715226354</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>12.60690316689074</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>13.677042438413375</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.44453878674514158</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.5374014324364951</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>1.4729055780285607</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>22.240624158106684</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="239">
+        <v>20.835569454922162</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>416</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>23.77802559054318</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>22.308475032950721</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>3.4310889740839845E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>9.399326181325951E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>388</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>387</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>392</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>395</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5294,24 +5351,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5859,7 +5916,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181">
@@ -5893,7 +5950,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181">
@@ -5927,7 +5984,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181">
@@ -5984,7 +6041,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7289,7 +7346,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8666,7 +8723,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>421</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8674,7 +8731,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8827,7 +8884,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8850,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8872,7 +8929,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8939,7 +8996,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8951,7 +9008,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8962,12 +9019,12 @@
         <v>-2031174.2582950441</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8978,12 +9035,12 @@
         <v>8.9427029344330666</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8991,12 +9048,12 @@
         <v>4062348.5165900881</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9004,7 +9061,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9080,7 +9137,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9091,15 +9148,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9116,7 +9173,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9150,7 +9207,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -10021,7 +10078,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10046,7 +10103,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10374,7 +10431,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10434,7 +10491,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10558,7 +10615,7 @@
         <v>-1427907</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10616,7 +10673,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10924,7 +10981,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11063,7 +11120,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11118,7 +11175,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11251,7 +11308,7 @@
         <v>2.3646804360316024E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11278,7 +11335,7 @@
         <v>0.13140650687425529</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11593,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12154,7 +12211,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12833,7 +12890,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13527,7 +13584,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13579,7 +13636,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14088,7 +14145,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14917,10 +14974,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14935,8 +14992,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14951,8 +15008,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14967,8 +15024,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16313,7 +16370,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16385,7 +16442,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16439,7 +16496,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16452,7 +16509,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16462,11 +16519,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16487,8 +16544,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16509,8 +16566,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16520,8 +16577,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16532,10 +16589,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16553,8 +16610,8 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16571,8 +16628,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16589,8 +16646,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.1185992870057041</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16606,7 +16663,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16616,25 +16673,25 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16644,12 +16701,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16659,8 +16716,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16680,8 +16737,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16691,8 +16748,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16706,8 +16763,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16717,8 +16774,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16738,8 +16795,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16749,8 +16806,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16764,8 +16821,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16775,8 +16832,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16796,8 +16853,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16807,8 +16864,8 @@
         <v>0.08</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16822,8 +16879,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16834,8 +16891,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16897,8 +16954,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16908,8 +16965,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16923,8 +16980,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16934,12 +16991,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16955,8 +17012,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16966,8 +17023,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16981,8 +17038,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16992,8 +17049,8 @@
         <v>0.1</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -17008,7 +17065,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -17017,7 +17074,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17026,10 +17083,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -17042,7 +17099,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -17054,7 +17111,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -17070,20 +17127,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17093,19 +17150,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17115,14 +17172,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17145,7 +17202,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17168,15 +17225,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17227,12 +17284,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17245,7 +17302,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17257,16 +17314,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17275,7 +17332,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.5374014324364951</v>
+        <v>1.4729055780285607</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17285,27 +17342,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>22.240624158106684</v>
+        <v>20.835569454922162</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>23.77802559054318</v>
+        <v>22.308475032950721</v>
       </c>
       <c r="D93" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>3.4310889740839845E-2</v>
+        <v>9.399326181325951E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17313,7 +17370,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17321,30 +17378,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>337</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>338</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CCC6F0-A9CF-42AC-B83E-F9A52082AF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C286CC8F-E91A-4397-9024-B0C28F89E86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3747,29 +3747,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4180,13 +4180,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4293,22 +4293,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4320,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4346,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4381,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4403,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4473,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4495,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4517,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4593,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4666,22 +4666,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4718,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4874,13 +4874,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4919,13 +4919,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,13 +5068,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5087,22 +5087,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5259,13 +5259,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5302,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5316,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,6 +5355,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5371,17 +5382,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C286CC8F-E91A-4397-9024-B0C28F89E86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F25C1B-6A4E-4977-B1AD-E532B6B4AAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3747,29 +3747,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4180,13 +4180,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4293,22 +4293,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4320,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4346,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4381,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4403,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4473,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4495,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4517,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4593,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4666,22 +4666,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4718,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4874,13 +4874,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4919,13 +4919,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,13 +5068,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5087,22 +5087,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.4654175514181245</v>
+        <v>1.4128343711970417</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>21.567448242737161</v>
+        <v>20.391308438970054</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>23.032865794155285</v>
+        <v>21.804142810167097</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.10333211205084314</v>
+        <v>0.15116621366779659</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5259,13 +5259,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5302,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5316,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,17 +5355,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5382,6 +5371,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17365,8 +17365,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17375,7 +17375,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.4654175514181245</v>
+        <v>1.4128343711970417</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>21.567448242737161</v>
+        <v>20.391308438970054</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>23.032865794155285</v>
+        <v>21.804142810167097</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.10333211205084314</v>
+        <v>0.15116621366779659</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F25C1B-6A4E-4977-B1AD-E532B6B4AAD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8860EAE-E113-4D89-B46D-AC75AC94E7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3739,14 +3744,14 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4082,7 +4087,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4114,10 +4119,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4128,7 +4133,7 @@
         <v>14.62</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4210,7 +4215,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4233,7 +4238,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4242,13 +4247,13 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4258,7 +4263,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>14.221973350893821</v>
+        <v>12.687574878788222</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4269,7 +4274,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4632,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4644,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4772,28 +4777,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.36794481423679237</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>7.4171010848313429E-2</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>0.60402076709908736</v>
       </c>
@@ -4896,8 +4901,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -5078,7 +5083,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5124,7 +5129,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5142,14 +5147,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5159,7 +5164,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.0701392715226354</v>
+        <v>0.99564227238319514</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5169,7 +5174,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>13.151834079371186</v>
+        <v>11.691932606405027</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5178,7 +5183,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>14.221973350893821</v>
+        <v>12.687574878788222</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5191,19 +5196,19 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4463395514486459</v>
+        <v>0.50607357888367177</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5212,7 +5217,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>1.4128343711970417</v>
       </c>
     </row>
@@ -5222,16 +5227,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>20.391308438970054</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>21.804142810167097</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5244,7 +5249,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>0.15116621366779659</v>
       </c>
     </row>
@@ -6084,7 +6089,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8766,7 +8771,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11922,7 +11927,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12254,7 +12259,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16465,7 +16470,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17277,7 +17282,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17286,7 +17291,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.0701392715226354</v>
+        <v>0.99564227238319514</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17298,7 +17303,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>13.151834079371186</v>
+        <v>11.691932606405027</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17308,7 +17313,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>14.221973350893821</v>
+        <v>12.687574878788222</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17319,7 +17324,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.4463395514486459</v>
+        <v>0.50607357888367177</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17357,16 +17362,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17375,9 +17380,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.4128343711970417</v>
+        <v>1.1548302039285423</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17385,69 +17392,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>20.391308438970054</v>
+        <v>14.865263852009171</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>21.804142810167097</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>16.020094055937715</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.15116621366779659</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.37633883554648095</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>1.4128343711970417</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>20.391308438970054</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>21.804142810167097</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>0.15116621366779659</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8860EAE-E113-4D89-B46D-AC75AC94E7C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C3D4C9-A892-48D0-B50D-D7E57EB16C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3752,29 +3752,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4185,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4225,7 +4225,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06671125</v>
+        <v>1.0671017599999999</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>12.687574878788222</v>
+        <v>12.691501140813982</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23821680012512947</v>
+        <v>0.23834947369112891</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4298,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96061.560615225826</v>
+        <v>96059.516833022921</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158359.43938477419</v>
+        <v>-158361.48316697706</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4478,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806616.12112934003</v>
+        <v>-806615.61018378939</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4500,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532352.8346152259</v>
+        <v>2532350.7908330234</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419848.3633880201</v>
+        <v>2419846.8305513682</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8306347295356576E-2</v>
+        <v>6.8331310133345272E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7498432682696467E-2</v>
+        <v>3.7484709986796393E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4598,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4671,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.482984968226415</v>
+        <v>12.487546926868847</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4723,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.79901763872801979</v>
+        <v>0.79931014935645794</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14101839.483409911</v>
+        <v>14101925.91294059</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8196390471106874</v>
+        <v>5.8218052274638872</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23175327635353246</v>
+        <v>0.2318381184061018</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4879,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>4.4970487317420522</v>
+        <v>4.4986950465252065</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4924,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>46.94 HKD</v>
+        <v>46.95 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>28.12 HKD</v>
+        <v>28.13 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.12 HKD</v>
+        <v>23.13 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.55 HKD</v>
+        <v>19.56 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>25.687175936271849</v>
+        <v>25.696602430940541</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5073,13 +5073,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5092,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0.99564227238319514</v>
+        <v>0.99527791325798076</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>11.691932606405027</v>
+        <v>11.696223227556001</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>12.687574878788222</v>
+        <v>12.691501140813982</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50607357888367177</v>
+        <v>0.50610197690833592</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C97</f>
-        <v>1.4128343711970417</v>
+        <v>1.4123173390160657</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C98</f>
-        <v>20.391308438970054</v>
+        <v>20.398791494357866</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C99</f>
-        <v>21.804142810167097</v>
+        <v>21.811108833373932</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F99</f>
-        <v>0.15116621366779659</v>
+        <v>0.1512065109778169</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5264,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5307,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5321,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5360,6 +5360,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5376,17 +5387,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8798,11 +8798,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.772640544997891</v>
+        <v>10.776584277530221</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.4970487317420522</v>
+        <v>4.4986950465252065</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14101839.483409911</v>
+        <v>14101925.91294059</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9060,11 +9060,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2213617.5186202219</v>
+        <v>-2213574.3038548827</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2031174.2582950441</v>
+        <v>-2031131.0435297049</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9076,11 +9076,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2056578642013935</v>
+        <v>8.205818060124539</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9427029344330666</v>
+        <v>8.9428932012354192</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9093,7 +9093,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4062348.5165900881</v>
+        <v>4062262.0870594098</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9208,11 +9208,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2065299.1194412501</v>
+        <v>-2066055.2003011198</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.79901763872801979</v>
+        <v>-0.79931014935645794</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9225,11 +9225,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15042590.822647542</v>
+        <v>15048189.961088508</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.8196390471106874</v>
+        <v>5.8218052274638872</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9242,11 +9242,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>599035.38342724997</v>
+        <v>599254.68298707192</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23175327635353241</v>
+        <v>0.23183811840610175</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9259,11 +9259,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13576327.086633541</v>
+        <v>13581389.44377446</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.2523746847361998</v>
+        <v>5.2543331965135307</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9843,24 +9843,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158359.43938477419</v>
+        <v>-158361.48316697706</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158359.43938477419</v>
+        <v>-158361.48316697706</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69498.6382973867</v>
+        <v>-69501.020061997275</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20423.937797925304</v>
+        <v>-20426.068289500385</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80007.632127146455</v>
+        <v>-80008.322533214305</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9898,24 +9898,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226464.4845173601</v>
+        <v>3226462.4407351576</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3629043.8346152259</v>
+        <v>3629041.7908330234</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3326070.6357026137</v>
+        <v>3326068.253938003</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239833.4872020744</v>
+        <v>4239831.3567104992</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800588.1218728535</v>
+        <v>4800587.4314667853</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806616.12112934003</v>
+        <v>-806615.61018378939</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10065,26 +10065,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419848.3633880201</v>
+        <v>2419846.8305513682</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532352.8346152259</v>
+        <v>2532350.7908330234</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256811.6357026137</v>
+        <v>2256809.253938003</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888504.4872020744</v>
+        <v>2888502.3567104992</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483232.1218728535</v>
+        <v>3483231.4314667853</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10173,26 +10173,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419848.3633880201</v>
+        <v>2419846.8305513682</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532352.8346152259</v>
+        <v>2532350.7908330234</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256811.6357026137</v>
+        <v>2256809.253938003</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888504.4872020744</v>
+        <v>2888502.3567104992</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483232.1218728535</v>
+        <v>3483231.4314667853</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11034,19 +11034,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30234957121477529</v>
+        <v>0.30234974157542677</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32163804631795034</v>
+        <v>0.3216382767655489</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31885984511248722</v>
+        <v>0.3188600054069809</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447284730868882</v>
+        <v>0.27447288679100218</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11172,24 +11172,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96061.560615225826</v>
+        <v>96059.516833022921</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96061.560615225826</v>
+        <v>96059.516833022921</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111947.3617026133</v>
+        <v>111944.97993800273</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100137.0622020747</v>
+        <v>100134.93171049962</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32450.367872853549</v>
+        <v>32449.677466785695</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11284,24 +11284,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158359.43938477419</v>
+        <v>-158361.48316697706</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158359.43938477419</v>
+        <v>-158361.48316697706</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69498.6382973867</v>
+        <v>-69501.020061997275</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20423.937797925304</v>
+        <v>-20426.068289500385</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80007.632127146455</v>
+        <v>-80008.322533214305</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12371,26 +12371,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0529286214111638E-3</v>
+        <v>6.0530067403274709E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5224372609456113E-3</v>
+        <v>5.5225085333562374E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5182042850598859E-3</v>
+        <v>2.5182905855974979E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9152170852656424E-4</v>
+        <v>7.9160427489296213E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5445080684201324E-3</v>
+        <v>3.5445386548756106E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12428,26 +12428,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12332425083199339</v>
+        <v>0.12332417271307709</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655492449167491</v>
+        <v>0.1265548532192643</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1205163947442856</v>
+        <v>0.120516308443748</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16431308589273252</v>
+        <v>0.16431300332636611</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267625198679979</v>
+        <v>0.21267622140034431</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12485,7 +12485,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0831062707998347E-2</v>
+        <v>3.0831043178269273E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12600,26 +12600,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.249318812399504E-2</v>
+        <v>9.249312953480783E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8310237179868148E-2</v>
+        <v>8.8310165907457536E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.1773008375806255E-2</v>
+        <v>8.177292207526865E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11194285986461831</v>
+        <v>0.1119427772982519</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431458264554004</v>
+        <v>0.15431455205908456</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12707,26 +12707,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.249318812399504E-2</v>
+        <v>9.249312953480783E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8310237179868148E-2</v>
+        <v>8.8310165907457536E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.1773008375806255E-2</v>
+        <v>8.177292207526865E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11194285986461831</v>
+        <v>0.1119427772982519</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431458264554004</v>
+        <v>0.15431455205908456</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12776,12 +12776,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12832,12 +12832,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1417056.2234426609</v>
+        <v>1416537.6462585912</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1417056.2234426609</v>
+        <v>1416537.6462585912</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12887,12 +12887,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.58559711628320632</v>
+        <v>0.58538318556957158</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.5595808783328462</v>
+        <v>0.55937654900986977</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -12942,12 +12942,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7498432682696467E-2</v>
+        <v>3.7484709986796393E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7498432682696467E-2</v>
+        <v>3.7484709986796393E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13079,26 +13079,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093262259824699</v>
+        <v>-0.11093268507262255</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1090428345220964E-2</v>
+        <v>9.1090595190373991E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21551857030651111</v>
+        <v>-0.2155187378682546</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11680957008492787</v>
+        <v>-0.11680988686523119</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633551724680181</v>
+        <v>1.4633548181957257</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13694,15 +13694,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.0772384924985126</v>
+        <v>2.077240684749861</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3548893613770632</v>
+        <v>1.3548903607116709</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733563459708444</v>
+        <v>1.8733567172859908</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13798,24 +13798,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12332425083199339</v>
+        <v>0.12332417271307709</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655492449167491</v>
+        <v>0.1265548532192643</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.1205163947442856</v>
+        <v>0.120516308443748</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16431308589273252</v>
+        <v>0.16431300332636611</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267625198679979</v>
+        <v>0.21267622140034431</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14084,50 +14084,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.99863879745811324</v>
+        <v>0.99900375414950782</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0450678760544658</v>
+        <v>1.0454496189286648</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.93135573784965753</v>
+        <v>0.93169571256281025</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.192046861776564</v>
+        <v>1.1924823760708823</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.437482939048444</v>
+        <v>1.4380088990235842</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57752161729686979</v>
+        <v>0.57773304092887012</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.56902827576017323</v>
+        <v>0.56923659008325456</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24473548632915829</v>
+        <v>0.24482508101072406</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18714466992405168</v>
+        <v>0.18721318130897616</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.5505564960017428E-2</v>
+        <v>9.5540528384442283E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>4.9658568824490525E-3</v>
+        <v>4.9676748221878196E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14141,50 +14141,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8306347295356576E-2</v>
+        <v>6.8331310133345272E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.1482070865558536E-2</v>
+        <v>7.1508181869265719E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.3704222835133897E-2</v>
+        <v>6.3727476919480872E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.1535353062692481E-2</v>
+        <v>8.1565142002112331E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8323046446542009E-2</v>
+        <v>9.8359021821038589E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.9502162605805052E-2</v>
+        <v>3.9516623866543789E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8921222692214312E-2</v>
+        <v>3.8935471277924391E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6739773346727653E-2</v>
+        <v>1.6745901573920936E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2800593018060991E-2</v>
+        <v>1.2805279159300695E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.5325283830381282E-3</v>
+        <v>6.5349198621369557E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3966189346436749E-4</v>
+        <v>3.3978623954773052E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14984,7 +14984,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419848.3633880201</v>
+        <v>2419846.8305513682</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15016,7 +15016,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30248104.542350251</v>
+        <v>30248085.3818921</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14101839.483409911</v>
+        <v>14101925.91294059</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42975379.225760162</v>
+        <v>42975446.494832695</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15096,7 +15096,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06671125</v>
+        <v>1.0671017599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15163,7 +15163,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>25.689822736436984</v>
+        <v>25.699250198389777</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2581248.0764709967</v>
+        <v>2581246.4413967836</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2390044.5152509226</v>
+        <v>2390043.0012933179</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2753412.8721010447</v>
+        <v>2753411.127970201</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2360607.7435708544</v>
+        <v>2360606.2482597744</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15242,7 +15242,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2937060.7627208857</v>
+        <v>2937058.9022595221</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2331533.5272831293</v>
+        <v>2331532.0503889155</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3132957.6509650387</v>
+        <v>3132955.6664141109</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2302817.4010063545</v>
+        <v>2302815.9423021781</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15286,7 +15286,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3341920.5238530342</v>
+        <v>3341918.4069359815</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2274454.9543566126</v>
+        <v>2274453.5136184371</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3564820.8600298022</v>
+        <v>3564818.6019180319</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2246441.831270088</v>
+        <v>2246440.4082766366</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3802588.2642631242</v>
+        <v>3802585.8555391929</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2218773.7293340419</v>
+        <v>2218772.3238667632</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15352,7 +15352,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4056214.3443557923</v>
+        <v>4056211.7749741282</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2191446.399126017</v>
+        <v>2191445.0109690512</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15374,7 +15374,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4326756.8466411326</v>
+        <v>4326754.1058861427</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15386,7 +15386,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2164455.6435611956</v>
+        <v>2164454.2725013425</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4615344.0673089372</v>
+        <v>4615341.1437503155</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2137797.3172477805</v>
+        <v>2137795.9630744648</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4923179.5579592399</v>
+        <v>4923176.4394042995</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2111467.325850328</v>
+        <v>2111465.9883555681</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15440,7 +15440,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5251547.1450084066</v>
+        <v>5251543.8184512286</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2085461.6254609127</v>
+        <v>2085460.3044392883</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>5601816.2838809611</v>
+        <v>5601812.7354481565</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2059776.2219780441</v>
+        <v>2059774.9172266661</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15484,7 +15484,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5975447.770316774</v>
+        <v>5975443.9852096196</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2034407.1704932286</v>
+        <v>2034405.881811705</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15506,7 +15506,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>6373999.8326125862</v>
+        <v>6373995.7950453116</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2009350.5746850888</v>
+        <v>2009349.3018754972</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>6799134.6302055428</v>
+        <v>6799130.323339493</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1984602.5862209455</v>
+        <v>1984601.3290878003</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7252625.1857010415</v>
+        <v>7252620.5915744528</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1960159.4041657671</v>
+        <v>1960158.1625159911</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>7736362.7792548817</v>
+        <v>7736357.8787079714</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1936017.2743984016</v>
+        <v>1936016.0480412953</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8252364.8361479575</v>
+        <v>8252359.6087430194</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1912172.4890350001</v>
+        <v>1912171.2777822127</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>8802783.3404485714</v>
+        <v>8802777.7643847391</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1888621.3858595337</v>
+        <v>1888620.189525034</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>32265600.955887459</v>
+        <v>32265580.517459795</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6922526.8459002674</v>
+        <v>6922522.4608722497</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15881,7 +15881,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>49522935.966054514</v>
+        <v>49522904.596084177</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15902,7 +15902,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>49522935.966054514</v>
+        <v>49522904.596084177</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15932,19 +15932,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30248104.542350248</v>
+        <v>30248085.381892096</v>
       </c>
       <c r="C56" s="124">
-        <v>31224066.735601693</v>
+        <v>31224046.956926864</v>
       </c>
       <c r="D56" s="124">
-        <v>32743214.900839329</v>
+        <v>32743194.159870327</v>
       </c>
       <c r="E56" s="124">
-        <v>34332501.646075539</v>
+        <v>34332479.89838355</v>
       </c>
       <c r="F56" s="124">
-        <v>35433238.047641315</v>
+        <v>35433215.602695256</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15953,19 +15953,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30248104.54235024</v>
+        <v>30248085.381892089</v>
       </c>
       <c r="C57" s="124">
-        <v>32200927.635806788</v>
+        <v>32200907.238346003</v>
       </c>
       <c r="D57" s="124">
-        <v>35504368.714482665</v>
+        <v>35504346.22447937</v>
       </c>
       <c r="E57" s="124">
-        <v>39330066.68887531</v>
+        <v>39330041.775509387</v>
       </c>
       <c r="F57" s="124">
-        <v>42217072.399663359</v>
+        <v>42217045.657543108</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15974,19 +15974,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30248104.54235024</v>
+        <v>30248085.381892081</v>
       </c>
       <c r="C58" s="124">
-        <v>33410063.85795711</v>
+        <v>33410042.694577131</v>
       </c>
       <c r="D58" s="124">
-        <v>39201004.212553442</v>
+        <v>39200979.380941287</v>
       </c>
       <c r="E58" s="124">
-        <v>46596026.622570626</v>
+        <v>46595997.106631316</v>
       </c>
       <c r="F58" s="124">
-        <v>52658149.316603415</v>
+        <v>52658115.960653305</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15995,19 +15995,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30248104.542350236</v>
+        <v>30248085.381892081</v>
       </c>
       <c r="C59" s="124">
-        <v>34641979.762122542</v>
+        <v>34641957.818393737</v>
       </c>
       <c r="D59" s="124">
-        <v>43295529.820614971</v>
+        <v>43295502.395353138</v>
       </c>
       <c r="E59" s="124">
-        <v>55405818.003246665</v>
+        <v>55405782.906804353</v>
       </c>
       <c r="F59" s="124">
-        <v>66147900.076084591</v>
+        <v>66147858.175142676</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16016,19 +16016,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30248104.542350233</v>
+        <v>30248085.381892078</v>
       </c>
       <c r="C60" s="124">
-        <v>35787729.912021764</v>
+        <v>35787707.242525235</v>
       </c>
       <c r="D60" s="124">
-        <v>47453442.063712202</v>
+        <v>47453412.004648842</v>
       </c>
       <c r="E60" s="124">
-        <v>65266315.125790089</v>
+        <v>65266273.783282302</v>
       </c>
       <c r="F60" s="124">
-        <v>82325914.31989944</v>
+        <v>82325862.171103328</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16037,19 +16037,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30248104.542350236</v>
+        <v>30248085.381892078</v>
       </c>
       <c r="C61" s="124">
-        <v>36798440.927450314</v>
+        <v>36798417.617725708</v>
       </c>
       <c r="D61" s="124">
-        <v>51474333.987646006</v>
+        <v>51474301.381575741</v>
       </c>
       <c r="E61" s="124">
-        <v>75841904.921275347</v>
+        <v>75841856.879731447</v>
       </c>
       <c r="F61" s="124">
-        <v>101005840.77312404</v>
+        <v>101005776.79165429</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16099,23 +16099,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16126,23 +16126,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.138126093116174</v>
+        <v>18.144793756202368</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.765058061187737</v>
+        <v>18.771954839162504</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.42093527568257</v>
+        <v>19.428071746706287</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>19.875194349519322</v>
+        <v>19.882496831406062</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16153,23 +16153,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.735359652962611</v>
+        <v>17.741880123382373</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.541263417513978</v>
+        <v>18.548078408807804</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>19.904549016808218</v>
+        <v>19.911862226479904</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.483362996390127</v>
+        <v>21.49125319018038</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>22.674791333345713</v>
+        <v>22.683116939564353</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16180,23 +16180,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.735359652962611</v>
+        <v>17.741880123382369</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.04025763596189</v>
+        <v>19.047254986762923</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.430100652310607</v>
+        <v>21.437971381156256</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>24.481926708210949</v>
+        <v>24.490912739549255</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>26.983683020220703</v>
+        <v>26.993583328781792</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16207,23 +16207,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.735359652962607</v>
+        <v>17.741880123382369</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.548652722083251</v>
+        <v>19.555835867977592</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.119856172227191</v>
+        <v>23.128344429237561</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>28.117608845722</v>
+        <v>28.127923552180135</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>32.550721302568569</v>
+        <v>32.562656108364855</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16234,23 +16234,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.735359652962607</v>
+        <v>17.741880123382369</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.021488363024332</v>
+        <v>20.028844308665224</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>24.835770501904211</v>
+        <v>24.844885846924843</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>32.186903078278412</v>
+        <v>32.198704925195365</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.227169684269455</v>
+        <v>39.241544425824152</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16260,23 +16260,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.735359652962607</v>
+        <v>17.741880123382369</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.438595173639555</v>
+        <v>20.446103552694762</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.495138393041124</v>
+        <v>26.504860160941483</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>36.551306416753306</v>
+        <v>36.564703252976095</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>46.936123506374294</v>
+        <v>46.953315517083951</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>46.936123506374294</v>
+        <v>46.953315517083951</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.117608845722</v>
+        <v>28.127923552180135</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.119856172227191</v>
+        <v>23.128344429237561</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.548652722083251</v>
+        <v>19.555835867977592</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.735359652962607</v>
+        <v>17.741880123382369</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>26.235403022092871</v>
+        <v>26.244628890947503</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532352.8346152259</v>
+        <v>2532350.7908330234</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16608,7 +16608,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419848.3633880201</v>
+        <v>2419846.8305513682</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10081869990840897</v>
+        <v>-0.10081888240033665</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.735359652962615</v>
+        <v>17.741880123382376</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.119856172227191</v>
+        <v>23.128344429237561</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16863,7 +16863,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.548652722083251</v>
+        <v>19.555835867977592</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16921,7 +16921,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.117608845722</v>
+        <v>28.127923552180135</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.655053650572103</v>
+        <v>23.663737497721208</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.735359652962607</v>
+        <v>17.741880123382369</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>46.936123506374294</v>
+        <v>46.953315517083951</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17106,7 +17106,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>25.687175936271849</v>
+        <v>25.696602430940541</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17168,7 +17168,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>25.689822736436984</v>
+        <v>25.699250198389777</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17231,7 +17231,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.2044745867652788</v>
+        <v>0.20447579444148378</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.54822708582102231</v>
+        <v>0.5480264600069632</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.99564227238319514</v>
+        <v>0.99527791325798076</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>11.691932606405027</v>
+        <v>11.696223227556001</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.687574878788222</v>
+        <v>12.691501140813982</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.50607357888367177</v>
+        <v>0.50610197690833592</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23821680012512947</v>
+        <v>0.23834947369112891</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17380,7 +17380,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1548302039285423</v>
+        <v>1.1544075893665195</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17392,7 +17392,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>14.865263852009171</v>
+        <v>14.870718999386886</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>16.020094055937715</v>
+        <v>16.025126588753405</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37633883554648095</v>
+        <v>0.37637177397981569</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.4128343711970417</v>
+        <v>1.4123173390160657</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>20.391308438970054</v>
+        <v>20.398791494357866</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>21.804142810167097</v>
+        <v>21.811108833373932</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.15116621366779659</v>
+        <v>0.1512065109778169</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C3D4C9-A892-48D0-B50D-D7E57EB16C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE0174C-B217-43F4-843E-7E0CE8A098E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4064,7 +4066,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4087,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4119,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4225,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0671017599999999</v>
+        <v>1.06707424</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4238,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4250,7 +4252,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4263,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>12.691501140813982</v>
+        <v>12.691224440750165</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4278,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23834947369112891</v>
+        <v>0.23834012469037225</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4422,7 +4424,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96059.516833022921</v>
+        <v>96059.660813338982</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4452,7 +4454,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158361.48316697706</v>
+        <v>-158361.339186661</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4492,7 +4494,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806615.61018378939</v>
+        <v>-806615.64617886837</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4545,7 +4547,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532350.7908330234</v>
+        <v>2532350.9348133393</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4558,7 +4560,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419846.8305513682</v>
+        <v>2419846.9385366049</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4571,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8331310133345272E-2</v>
+        <v>6.8329550953551019E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4580,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7484709986796393E-2</v>
+        <v>3.7485676722924174E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4637,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4649,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4702,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.487546926868847</v>
+        <v>12.487225436761449</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4769,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.79931014935645794</v>
+        <v>0.799289535562971</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4778,7 +4780,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4787,7 +4789,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4796,7 +4798,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4827,7 +4829,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14101925.91294059</v>
+        <v>14101919.824155236</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4840,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8218052274638872</v>
+        <v>5.821652572516971</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.2318381184061018</v>
+        <v>0.23183213942147476</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4893,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,11 +4904,11 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>4.4986950465252065</v>
+        <v>4.4985790275171595</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -5065,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>25.696602430940541</v>
+        <v>25.695938127508406</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5083,7 +5085,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5138,233 +5140,287 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0.99527791325798076</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>0.99530358162026156</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>11.696223227556001</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>11.695920859129904</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>12.691501140813982</v>
+        <v>12.691224440750165</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50610197690833592</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
+        <v>0.50609997666659368</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>1.4123173390160657</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>1.1544373617063142</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C98</f>
-        <v>20.398791494357866</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <f>Scenarios!C92</f>
+        <v>14.870334564530328</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
       <c r="B139" s="80" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C99</f>
-        <v>21.811108833373932</v>
-      </c>
-      <c r="D139" s="101" t="str">
+        <f>Scenarios!C93</f>
+        <v>16.024771926236642</v>
+      </c>
+      <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="2:4">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.3763694539300918</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>1.4123537628858516</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
+        <f>Scenarios!C98</f>
+        <v>20.398264148875619</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
+        <f>Scenarios!C99</f>
+        <v>21.810617911761469</v>
+      </c>
+      <c r="D145" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1512065109778169</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+        <v>0.15120367259864953</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
@@ -5389,7 +5445,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -6071,7 +6127,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -6089,7 +6145,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7447,7 +7503,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8771,7 +8827,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8798,11 +8854,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.776584277530221</v>
+        <v>10.776306355020452</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.4986950465252065</v>
+        <v>4.4985790275171595</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -8993,7 +9049,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14101925.91294059</v>
+        <v>14101919.824155236</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9060,11 +9116,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2213574.3038548827</v>
+        <v>-2213577.3482475597</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2031131.0435297049</v>
+        <v>-2031134.0879223819</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9076,11 +9132,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.205818060124539</v>
+        <v>8.2058067744414647</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9428932012354192</v>
+        <v>8.9428797970595273</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9093,7 +9149,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4062262.0870594098</v>
+        <v>4062268.1758447639</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9208,11 +9264,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2066055.2003011198</v>
+        <v>-2066001.9178108799</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.79931014935645794</v>
+        <v>-0.799289535562971</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9225,11 +9281,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15048189.961088508</v>
+        <v>15047795.378901381</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.8218052274638872</v>
+        <v>5.821652572516971</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9242,11 +9298,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>599254.68298707192</v>
+        <v>599239.22852012794</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23183811840610175</v>
+        <v>0.23183213942147471</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9259,11 +9315,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13581389.44377446</v>
+        <v>13581032.68961063</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.2543331965135307</v>
+        <v>5.2541951763754753</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9843,24 +9899,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158361.48316697706</v>
+        <v>-158361.339186661</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158361.48316697706</v>
+        <v>-158361.339186661</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69501.020061997275</v>
+        <v>-69500.852271505253</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20426.068289500385</v>
+        <v>-20425.918200684697</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80008.322533214305</v>
+        <v>-80008.273895505394</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9898,24 +9954,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226462.4407351576</v>
+        <v>3226462.5847154735</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3629041.7908330234</v>
+        <v>3629041.9348133393</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3326068.253938003</v>
+        <v>3326068.421728495</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239831.3567104992</v>
+        <v>4239831.5067993151</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800587.4314667853</v>
+        <v>4800587.4801044939</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -9953,7 +10009,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806615.61018378939</v>
+        <v>-806615.64617886837</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10065,26 +10121,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419846.8305513682</v>
+        <v>2419846.9385366049</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532350.7908330234</v>
+        <v>2532350.9348133393</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256809.253938003</v>
+        <v>2256809.421728495</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888502.3567104992</v>
+        <v>2888502.5067993151</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483231.4314667853</v>
+        <v>3483231.4801044939</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10173,26 +10229,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419846.8305513682</v>
+        <v>2419846.9385366049</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532350.7908330234</v>
+        <v>2532350.9348133393</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256809.253938003</v>
+        <v>2256809.421728495</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888502.3567104992</v>
+        <v>2888502.5067993151</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483231.4314667853</v>
+        <v>3483231.4801044939</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11034,19 +11090,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30234974157542677</v>
+        <v>0.3023497295738577</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.3216382767655489</v>
+        <v>0.32163826053097161</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.3188600054069809</v>
+        <v>0.31885999411455324</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447288679100218</v>
+        <v>0.27447288400955283</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11172,24 +11228,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96059.516833022921</v>
+        <v>96059.660813338982</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96059.516833022921</v>
+        <v>96059.660813338982</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111944.97993800273</v>
+        <v>111945.14772849475</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100134.93171049962</v>
+        <v>100135.0817993153</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32449.677466785695</v>
+        <v>32449.726104494606</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11284,24 +11340,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158361.48316697706</v>
+        <v>-158361.339186661</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158361.48316697706</v>
+        <v>-158361.339186661</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69501.020061997275</v>
+        <v>-69500.852271505253</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20426.068289500385</v>
+        <v>-20425.918200684697</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80008.322533214305</v>
+        <v>-80008.273895505394</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -11927,7 +11983,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12259,7 +12315,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12371,26 +12427,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0530067403274709E-3</v>
+        <v>6.0530012370080639E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5225085333562374E-3</v>
+        <v>5.5225035123592867E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5182905855974979E-3</v>
+        <v>2.5182845058994438E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9160427489296213E-4</v>
+        <v>7.9159845825970559E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5445386548756106E-3</v>
+        <v>3.5445365001217817E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12428,26 +12484,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12332417271307709</v>
+        <v>0.1233241782163965</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.1265548532192643</v>
+        <v>0.12655485824026122</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.120516308443748</v>
+        <v>0.12051631452344605</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16431300332636611</v>
+        <v>0.1643130091429994</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267622140034431</v>
+        <v>0.21267622355509813</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12485,7 +12541,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0831043178269273E-2</v>
+        <v>3.0831044554099126E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12600,26 +12656,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.249312953480783E-2</v>
+        <v>9.2493133662297361E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8310165907457536E-2</v>
+        <v>8.8310170928454487E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.177292207526865E-2</v>
+        <v>8.1772928154966701E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1119427772982519</v>
+        <v>0.11194278311488517</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431455205908456</v>
+        <v>0.15431455421383838</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12707,26 +12763,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.249312953480783E-2</v>
+        <v>9.2493133662297361E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8310165907457536E-2</v>
+        <v>8.8310170928454487E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.177292207526865E-2</v>
+        <v>8.1772928154966701E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1119427772982519</v>
+        <v>0.11194278311488517</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431455205908456</v>
+        <v>0.15431455421383838</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12776,12 +12832,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12832,12 +12888,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1416537.6462585912</v>
+        <v>1416574.1789707153</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1416537.6462585912</v>
+        <v>1416574.1789707153</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12887,12 +12943,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.58538318556957158</v>
+        <v>0.58539825656385702</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55937654900986977</v>
+        <v>0.55939094360755792</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -12942,12 +12998,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7484709986796393E-2</v>
+        <v>3.7485676722924174E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7484709986796393E-2</v>
+        <v>3.7485676722924174E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13079,26 +13135,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093268507262255</v>
+        <v>-0.11093268067142703</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1090595190373991E-2</v>
+        <v>9.1090583436463035E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.2155187378682546</v>
+        <v>-0.21551872606386369</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11680988686523119</v>
+        <v>-0.11680986454869746</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633548181957257</v>
+        <v>1.4633548431534908</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13694,15 +13750,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.077240684749861</v>
+        <v>2.0772405303100427</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3548903607116709</v>
+        <v>1.3548902903105238</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733567172859908</v>
+        <v>1.8733566911275863</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13798,24 +13854,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12332417271307709</v>
+        <v>0.1233241782163965</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.1265548532192643</v>
+        <v>0.12655485824026122</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.120516308443748</v>
+        <v>0.12051631452344605</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16431300332636611</v>
+        <v>0.1643130091429994</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267622140034431</v>
+        <v>0.21267622355509813</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14084,50 +14140,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.99900375414950782</v>
+        <v>0.99897803494091586</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0454496189286648</v>
+        <v>1.0454227167650891</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.93169571256281025</v>
+        <v>0.93167175388286361</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1924823760708823</v>
+        <v>1.1924516845306412</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4380088990235842</v>
+        <v>1.4379718336001228</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57773304092887012</v>
+        <v>0.57771814149389367</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.56923659008325456</v>
+        <v>0.56922190976733134</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24482508101072406</v>
+        <v>0.24481876709907854</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18721318130897616</v>
+        <v>0.1872083531782929</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.5540528384442283E-2</v>
+        <v>9.5538064443851337E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>4.9676748221878196E-3</v>
+        <v>4.9675467084350075E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14141,50 +14197,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8331310133345272E-2</v>
+        <v>6.8329550953551019E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.1508181869265719E-2</v>
+        <v>7.1506341775997892E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.3727476919480872E-2</v>
+        <v>6.3725838158882608E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.1565142002112331E-2</v>
+        <v>8.1563042717554129E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8359021821038589E-2</v>
+        <v>9.8356486566355872E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.9516623866543789E-2</v>
+        <v>3.9515604753344299E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8935471277924391E-2</v>
+        <v>3.8934467152348246E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6745901573920936E-2</v>
+        <v>1.6745469705819326E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2805279159300695E-2</v>
+        <v>1.2804948917803892E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.5349198621369557E-3</v>
+        <v>6.5347513299487923E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3978623954773052E-4</v>
+        <v>3.3977747663714141E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14984,7 +15040,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419846.8305513682</v>
+        <v>2419846.9385366049</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15016,7 +15072,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30248085.3818921</v>
+        <v>30248086.731707562</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15050,7 +15106,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14101925.91294059</v>
+        <v>14101919.824155236</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15082,7 +15138,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42975446.494832695</v>
+        <v>42975441.755862802</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15096,7 +15152,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0671017599999999</v>
+        <v>1.06707424</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15110,7 +15166,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15163,7 +15219,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>25.699250198389777</v>
+        <v>25.698585826791245</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15198,7 +15254,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2581246.4413967836</v>
+        <v>2581246.5565844495</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15210,7 +15266,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2390043.0012933179</v>
+        <v>2390043.107948564</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15220,7 +15276,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2753411.127970201</v>
+        <v>2753411.2508406858</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15232,7 +15288,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2360606.2482597744</v>
+        <v>2360606.353601411</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15242,7 +15298,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2937058.9022595221</v>
+        <v>2937059.0333252563</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15254,7 +15310,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2331532.0503889155</v>
+        <v>2331532.154433121</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15264,7 +15320,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3132955.6664141109</v>
+        <v>3132955.8062217031</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15276,7 +15332,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2302815.9423021781</v>
+        <v>2302816.0450649322</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15286,7 +15342,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3341918.4069359815</v>
+        <v>3341918.5560684991</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15298,7 +15354,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2274453.5136184371</v>
+        <v>2274453.6151155229</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15308,7 +15364,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3564818.6019180319</v>
+        <v>3564818.7609974318</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15320,7 +15376,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2246440.4082766366</v>
+        <v>2246440.5085236426</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15330,7 +15386,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3802585.8555391929</v>
+        <v>3802586.0252289139</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15342,7 +15398,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2218772.3238667632</v>
+        <v>2218772.4228790854</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15352,7 +15408,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4056211.7749741282</v>
+        <v>4056211.9559818613</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15364,7 +15420,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2191445.0109690512</v>
+        <v>2191445.1087618973</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15374,7 +15430,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4326754.1058861427</v>
+        <v>4326754.2989667794</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15386,7 +15442,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2164454.2725013425</v>
+        <v>2164454.3690897315</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15396,7 +15452,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4615341.1437503155</v>
+        <v>4615341.3497090973</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15408,7 +15464,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2137795.9630744648</v>
+        <v>2137796.0584732313</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15418,7 +15474,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4923176.4394042995</v>
+        <v>4923176.6591001768</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15430,7 +15486,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2111465.9883555681</v>
+        <v>2111466.0825793641</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15440,7 +15496,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5251543.8184512286</v>
+        <v>5251544.052800443</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15452,7 +15508,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2085460.3044392883</v>
+        <v>2085460.3975025858</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15462,7 +15518,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>5601812.7354481565</v>
+        <v>5601812.9854280585</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15474,7 +15530,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2059774.9172266661</v>
+        <v>2059775.0091437572</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15484,7 +15540,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5975443.9852096196</v>
+        <v>5975444.2518627504</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15496,7 +15552,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2034405.881811705</v>
+        <v>2034405.9725967075</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15506,7 +15562,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>6373995.7950453116</v>
+        <v>6373996.0794837466</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15518,7 +15574,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2009349.3018754972</v>
+        <v>2009349.3915423544</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15528,7 +15584,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>6799130.323339493</v>
+        <v>6799130.6267494811</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15540,7 +15596,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1984601.3290878003</v>
+        <v>1984601.4176502838</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15550,7 +15606,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7252620.5915744528</v>
+        <v>7252620.9152213642</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15562,7 +15618,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1960158.1625159911</v>
+        <v>1960158.2499877026</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15572,7 +15628,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>7736357.8787079714</v>
+        <v>7736358.2239415739</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15584,7 +15640,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1936016.0480412953</v>
+        <v>1936016.1344356691</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15594,7 +15650,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8252359.6087430194</v>
+        <v>8252359.9770031068</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15606,7 +15662,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1912171.2777822127</v>
+        <v>1912171.3631125176</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15616,7 +15672,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>8802777.7643847391</v>
+        <v>8802778.1572071388</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15628,7 +15684,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1888620.189525034</v>
+        <v>1888620.2738043757</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15858,7 +15914,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>32265580.517459795</v>
+        <v>32265581.957305618</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15870,7 +15926,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6922522.4608722497</v>
+        <v>6922522.7697885903</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15881,7 +15937,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>49522904.596084177</v>
+        <v>49522906.806035042</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15902,7 +15958,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>49522904.596084177</v>
+        <v>49522906.806035042</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15932,19 +15988,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30248085.381892096</v>
+        <v>30248086.731707558</v>
       </c>
       <c r="C56" s="124">
-        <v>31224046.956926864</v>
+        <v>31224048.350294434</v>
       </c>
       <c r="D56" s="124">
-        <v>32743194.159870327</v>
+        <v>32743195.621029567</v>
       </c>
       <c r="E56" s="124">
-        <v>34332479.89838355</v>
+        <v>34332481.430464387</v>
       </c>
       <c r="F56" s="124">
-        <v>35433215.602695256</v>
+        <v>35433217.183896236</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -15953,19 +16009,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30248085.381892089</v>
+        <v>30248086.731707551</v>
       </c>
       <c r="C57" s="124">
-        <v>32200907.238346003</v>
+        <v>32200908.675305784</v>
       </c>
       <c r="D57" s="124">
-        <v>35504346.22447937</v>
+        <v>35504347.808854535</v>
       </c>
       <c r="E57" s="124">
-        <v>39330041.775509387</v>
+        <v>39330043.530605555</v>
       </c>
       <c r="F57" s="124">
-        <v>42217045.657543108</v>
+        <v>42217047.541471303</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -15974,19 +16030,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30248085.381892081</v>
+        <v>30248086.731707543</v>
       </c>
       <c r="C58" s="124">
-        <v>33410042.694577131</v>
+        <v>33410044.185494367</v>
       </c>
       <c r="D58" s="124">
-        <v>39200979.380941287</v>
+        <v>39200981.130278051</v>
       </c>
       <c r="E58" s="124">
-        <v>46595997.106631316</v>
+        <v>46595999.185969457</v>
       </c>
       <c r="F58" s="124">
-        <v>52658115.960653305</v>
+        <v>52658118.310512409</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -15995,19 +16051,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30248085.381892081</v>
+        <v>30248086.731707543</v>
       </c>
       <c r="C59" s="124">
-        <v>34641957.818393737</v>
+        <v>34641959.364284962</v>
       </c>
       <c r="D59" s="124">
-        <v>43295502.395353138</v>
+        <v>43295504.327407271</v>
       </c>
       <c r="E59" s="124">
-        <v>55405782.906804353</v>
+        <v>55405785.379277624</v>
       </c>
       <c r="F59" s="124">
-        <v>66147858.175142676</v>
+        <v>66147861.126979135</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16016,19 +16072,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30248085.381892078</v>
+        <v>30248086.731707543</v>
       </c>
       <c r="C60" s="124">
-        <v>35787707.242525235</v>
+        <v>35787708.839545324</v>
       </c>
       <c r="D60" s="124">
-        <v>47453412.004648842</v>
+        <v>47453414.122248963</v>
       </c>
       <c r="E60" s="124">
-        <v>65266273.783282302</v>
+        <v>65266276.695778228</v>
       </c>
       <c r="F60" s="124">
-        <v>82325862.171103328</v>
+        <v>82325865.844880357</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16037,19 +16093,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30248085.381892078</v>
+        <v>30248086.731707547</v>
       </c>
       <c r="C61" s="124">
-        <v>36798417.617725708</v>
+        <v>36798419.259848557</v>
       </c>
       <c r="D61" s="124">
-        <v>51474301.381575741</v>
+        <v>51474303.678607337</v>
       </c>
       <c r="E61" s="124">
-        <v>75841856.879731447</v>
+        <v>75841860.264160872</v>
       </c>
       <c r="F61" s="124">
-        <v>101005776.79165429</v>
+        <v>101005781.29901917</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16099,23 +16155,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16126,23 +16182,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.144793756202368</v>
+        <v>18.144323873003135</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.771954839162504</v>
+        <v>18.771468809790999</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.428071746706287</v>
+        <v>19.427568825698952</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>19.882496831406062</v>
+        <v>19.881982211290005</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16153,23 +16209,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.741880123382373</v>
+        <v>17.741420613136921</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.548078408807804</v>
+        <v>18.547598143102938</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>19.911862226479904</v>
+        <v>19.911346850355944</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.49125319018038</v>
+        <v>21.490697152862236</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>22.683116939564353</v>
+        <v>22.682530217884658</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16180,23 +16236,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.741880123382369</v>
+        <v>17.741420613136917</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.047254986762923</v>
+        <v>19.04676186982854</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.437971381156256</v>
+        <v>21.437416715570652</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>24.490912739549255</v>
+        <v>24.490279476425574</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>26.993583328781792</v>
+        <v>26.992885634762171</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16207,23 +16263,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.741880123382369</v>
+        <v>17.741420613136917</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.555835867977592</v>
+        <v>19.55532965770125</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.128344429237561</v>
+        <v>23.127746245239898</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>28.127923552180135</v>
+        <v>28.127196654733908</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>32.562656108364855</v>
+        <v>32.561815039364021</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16234,23 +16290,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.741880123382369</v>
+        <v>17.741420613136917</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.028844308665224</v>
+        <v>20.028325920854307</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>24.844885846924843</v>
+        <v>24.844243470814199</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>32.198704925195365</v>
+        <v>32.197873226065624</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.241544425824152</v>
+        <v>39.240531409800013</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16260,23 +16316,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.741880123382369</v>
+        <v>17.741420613136921</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.446103552694762</v>
+        <v>20.445574422604356</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.504860160941483</v>
+        <v>26.504175049029833</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>36.564703252976095</v>
+        <v>36.563759151844614</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>46.953315517083951</v>
+        <v>46.952103962617393</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16311,7 +16367,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>46.953315517083951</v>
+        <v>46.952103962617393</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16333,7 +16389,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.127923552180135</v>
+        <v>28.127196654733908</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16356,7 +16412,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.128344429237561</v>
+        <v>23.127746245239898</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16379,7 +16435,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.555835867977592</v>
+        <v>19.55532965770125</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16402,7 +16458,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.741880123382369</v>
+        <v>17.741420613136921</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16523,7 +16579,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16532,7 +16588,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16552,7 +16608,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>26.244628890947503</v>
+        <v>26.243978721197557</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16586,7 +16642,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532350.7908330234</v>
+        <v>2532350.9348133393</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16608,7 +16664,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419846.8305513682</v>
+        <v>2419846.9385366049</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16692,7 +16748,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10081888240033665</v>
+        <v>-0.10081886954414521</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16758,7 +16814,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.741880123382376</v>
+        <v>17.741420613136924</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16805,7 +16861,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.128344429237561</v>
+        <v>23.127746245239898</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16863,7 +16919,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.555835867977592</v>
+        <v>19.55532965770125</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16921,7 +16977,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.127923552180135</v>
+        <v>28.127196654733908</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16948,7 +17004,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.663737497721208</v>
+        <v>23.663125530105667</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17022,7 +17078,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.741880123382369</v>
+        <v>17.741420613136921</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17080,7 +17136,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>46.953315517083951</v>
+        <v>46.952103962617393</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17106,7 +17162,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>25.696602430940541</v>
+        <v>25.695938127508406</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17168,7 +17224,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>25.699250198389777</v>
+        <v>25.698585826791245</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17231,7 +17287,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.20447579444148378</v>
+        <v>0.20447570936321155</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17264,7 +17320,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.5480264600069632</v>
+        <v>0.54804059368915137</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17291,7 +17347,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.99527791325798076</v>
+        <v>0.99530358162026156</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17303,7 +17359,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>11.696223227556001</v>
+        <v>11.695920859129904</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17313,7 +17369,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.691501140813982</v>
+        <v>12.691224440750165</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17324,7 +17380,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.50610197690833592</v>
+        <v>0.50609997666659368</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17354,7 +17410,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23834947369112891</v>
+        <v>0.23834012469037225</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17362,12 +17418,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17380,7 +17436,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1544075893665195</v>
+        <v>1.1544373617063142</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17392,7 +17448,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>14.870718999386886</v>
+        <v>14.870334564530328</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17402,7 +17458,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>16.025126588753405</v>
+        <v>16.024771926236642</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17469,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37637177397981569</v>
+        <v>0.3763694539300918</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17425,7 +17481,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17440,7 +17496,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.4123173390160657</v>
+        <v>1.4123537628858516</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17452,7 +17508,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>20.398791494357866</v>
+        <v>20.398264148875619</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17464,7 +17520,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>21.811108833373932</v>
+        <v>21.810617911761469</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17474,7 +17530,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.1512065109778169</v>
+        <v>0.15120367259864953</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE0174C-B217-43F4-843E-7E0CE8A098E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C136B6C-236B-4705-AA9F-7CEDA6208D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>14.62</v>
+        <v>15.26</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>37789.745385720002</v>
+        <v>39444.016045559998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.23834012469037225</v>
+        <v>0.2202784312360544</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.8329550953551019E-2</v>
+        <v>6.5463829288395545E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.7485676722924174E-2</v>
+        <v>3.5913538249616732E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.7485676722924174E-2</v>
+        <v>3.5913538249616732E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.7485676722924174E-2</v>
+        <v>3.5913538249616732E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14197,50 +14197,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8329550953551019E-2</v>
+        <v>6.5463829288395545E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>7.1506341775997892E-2</v>
+        <v>6.8507386419730615E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.3725838158882608E-2</v>
+        <v>6.1053194880921598E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.1563042717554129E-2</v>
+        <v>7.8142312223502042E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.8356486566355872E-2</v>
+        <v>9.4231443879431373E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.9515604753344299E-2</v>
+        <v>3.7858331683741392E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8934467152348246E-2</v>
+        <v>3.7301566826168503E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6745469705819326E-2</v>
+        <v>1.6043169534670939E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2804948917803892E-2</v>
+        <v>1.2267913052312772E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.5347513299487923E-3</v>
+        <v>6.2606857433716474E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3977747663714141E-4</v>
+        <v>3.2552730723689433E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14254,43 +14254,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9728454617704891E-2</v>
+        <v>7.6384666219583591E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4334042674028969E-2</v>
+        <v>8.0797097240780061E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10753634242626094</v>
+        <v>0.10302629923145053</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10613694162426496</v>
+        <v>0.10168558889559332</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4945632278375273E-2</v>
+        <v>4.3060625420042374E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.9670629814999935E-2</v>
+        <v>3.8006855039010426E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8927436337538378E-2</v>
+        <v>1.8133625114994174E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3632137362710756E-2</v>
+        <v>1.3060409452348052E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8546539354690771E-2</v>
+        <v>1.7768702841781069E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6302041564767809E-3</v>
+        <v>1.5618338641999042E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-14.62</v>
+        <v>-15.26</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>14.62</v>
+        <v>15.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17397,7 +17397,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>14.62</v>
+        <v>15.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.23834012469037225</v>
+        <v>0.2202784312360544</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C136B6C-236B-4705-AA9F-7CEDA6208D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB756C09-DCA4-42D7-A8C3-E8991A89651A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3754,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4089,7 +4092,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4121,10 +4124,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4187,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4217,7 +4220,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4240,7 +4243,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4300,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4600,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4639,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4651,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4673,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5149,7 +5152,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5203,14 +5206,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5264,7 +5267,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5320,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6145,7 +6148,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11983,7 +11986,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12315,7 +12318,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17418,12 +17421,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB756C09-DCA4-42D7-A8C3-E8991A89651A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA8F9AE-8387-4F5D-A84D-F4456661DE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>39444.016045559998</v>
+        <v>39599.103919919995</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.06707424</v>
+        <v>1.0739449931617173</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>12.691224440750165</v>
+        <v>12.76034731937011</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.2202784312360544</v>
+        <v>0.22093639979403168</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96059.660813338982</v>
+        <v>96023.943166571378</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158361.339186661</v>
+        <v>-158397.05683342862</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806615.64617886837</v>
+        <v>-806606.7167671764</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532350.9348133393</v>
+        <v>2532315.2171665714</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419846.9385366049</v>
+        <v>2419820.1503015291</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.5463829288395545E-2</v>
+        <v>6.5626579329258014E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5913538249616732E-2</v>
+        <v>3.5544021344529921E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.487225436761449</v>
+        <v>12.567489941552909</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.799289535562971</v>
+        <v>0.80443605761151837</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14101919.824155236</v>
+        <v>14103430.28815804</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.821652572516971</v>
+        <v>5.8597650165276187</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23183213942147476</v>
+        <v>0.23332487661370402</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>4.4985790275171595</v>
+        <v>4.5275447966435411</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>46.95 HKD</v>
+        <v>47.25 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>28.13 HKD</v>
+        <v>28.31 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.13 HKD</v>
+        <v>23.28 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.56 HKD</v>
+        <v>19.68 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>17.74 HKD</v>
+        <v>17.86 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>25.695938127508406</v>
+        <v>25.861790776733326</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0.99530358162026156</v>
+        <v>0.9889359508069242</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>11.695920859129904</v>
+        <v>11.771411368563186</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>12.691224440750165</v>
+        <v>12.76034731937011</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50609997666659368</v>
+        <v>0.5065945962701851</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1544373617063142</v>
+        <v>1.1470516443712049</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>14.870334564530328</v>
+        <v>14.966314106905861</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>16.024771926236642</v>
+        <v>16.113365751277065</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3763694539300918</v>
+        <v>0.37694315562348735</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>1.4123537628858516</v>
+        <v>1.4033179797278683</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>20.398264148875619</v>
+        <v>20.52992332908897</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>21.810617911761469</v>
+        <v>21.933241308816839</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.15120367259864953</v>
+        <v>0.15190554675165124</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5419,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5435,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.776306355020452</v>
+        <v>10.845693599304779</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.4985790275171595</v>
+        <v>4.5275447966435411</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14101919.824155236</v>
+        <v>14103430.28815804</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9119,11 +9119,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2213577.3482475597</v>
+        <v>-2212822.1162461578</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2031134.0879223819</v>
+        <v>-2030378.85592098</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9135,11 +9135,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2058067744414647</v>
+        <v>8.2086074007674039</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9428797970595273</v>
+        <v>8.9462062447260475</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9152,7 +9152,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4062268.1758447639</v>
+        <v>4060757.71184196</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9267,11 +9267,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2066001.9178108799</v>
+        <v>-2079304.6372251478</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.799289535562971</v>
+        <v>-0.80443605761151826</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15047795.378901381</v>
+        <v>15146308.344372643</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.821652572516971</v>
+        <v>5.8597650165276178</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9301,11 +9301,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>599239.22852012794</v>
+        <v>603097.65248881048</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23183213942147471</v>
+        <v>0.23332487661370399</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9318,11 +9318,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13581032.68961063</v>
+        <v>13670101.359636307</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.2541951763754753</v>
+        <v>5.2886538355298036</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9902,24 +9902,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158361.339186661</v>
+        <v>-158397.05683342862</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158361.339186661</v>
+        <v>-158397.05683342862</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69500.852271505253</v>
+        <v>-69542.476583001437</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20425.918200684697</v>
+        <v>-20463.151202034802</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80008.273895505394</v>
+        <v>-80020.339603888002</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9957,24 +9957,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226462.5847154735</v>
+        <v>3226426.8670687056</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3629041.9348133393</v>
+        <v>3629006.2171665714</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3326068.421728495</v>
+        <v>3326026.797416999</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239831.5067993151</v>
+        <v>4239794.2737979647</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800587.4801044939</v>
+        <v>4800575.4143961119</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806615.64617886837</v>
+        <v>-806606.7167671764</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10124,26 +10124,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419846.9385366049</v>
+        <v>2419820.1503015291</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532350.9348133393</v>
+        <v>2532315.2171665714</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256809.421728495</v>
+        <v>2256767.797416999</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888502.5067993151</v>
+        <v>2888465.2737979647</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483231.4801044939</v>
+        <v>3483219.4143961119</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10232,26 +10232,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419846.9385366049</v>
+        <v>2419820.1503015291</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532350.9348133393</v>
+        <v>2532315.2171665714</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256809.421728495</v>
+        <v>2256767.797416999</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888502.5067993151</v>
+        <v>2888465.2737979647</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483231.4801044939</v>
+        <v>3483219.4143961119</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11093,19 +11093,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.3023497295738577</v>
+        <v>0.30235270686979016</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32163826053097161</v>
+        <v>0.32164228794350269</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31885999411455324</v>
+        <v>0.31886279548686669</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447288400955283</v>
+        <v>0.27447357401411399</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11231,24 +11231,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96059.660813338982</v>
+        <v>96023.943166571378</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96059.660813338982</v>
+        <v>96023.943166571378</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111945.14772849475</v>
+        <v>111903.52341699856</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100135.0817993153</v>
+        <v>100097.8487979652</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32449.726104494606</v>
+        <v>32437.660396112002</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11343,24 +11343,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158361.339186661</v>
+        <v>-158397.05683342862</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158361.339186661</v>
+        <v>-158397.05683342862</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69500.852271505253</v>
+        <v>-69542.476583001437</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20425.918200684697</v>
+        <v>-20463.151202034802</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80008.273895505394</v>
+        <v>-80020.339603888002</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12430,26 +12430,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0530012370080639E-3</v>
+        <v>6.0543664626444334E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5225035123592867E-3</v>
+        <v>5.5237490867573093E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5182845058994438E-3</v>
+        <v>2.519792715587292E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9159845825970559E-4</v>
+        <v>7.9304140864144834E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5445365001217817E-3</v>
+        <v>3.545071036635066E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12487,26 +12487,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.1233241782163965</v>
+        <v>0.12332281299076012</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655485824026122</v>
+        <v>0.12655361266586321</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12051631452344605</v>
+        <v>0.1205148063137582</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1643130091429994</v>
+        <v>0.16431156619261764</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267622355509813</v>
+        <v>0.21267568901858486</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0831044554099126E-2</v>
+        <v>3.0830703247690029E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12659,26 +12659,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2493133662297361E-2</v>
+        <v>9.2492109743070081E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8310170928454487E-2</v>
+        <v>8.8308925354056447E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.1772928154966701E-2</v>
+        <v>8.1771419945278853E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11194278311488517</v>
+        <v>0.11194134016450341</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431455421383838</v>
+        <v>0.15431401967732511</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12766,26 +12766,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2493133662297361E-2</v>
+        <v>9.2492109743070081E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8310170928454487E-2</v>
+        <v>8.8308925354056447E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.1772928154966701E-2</v>
+        <v>8.1771419945278853E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11194278311488517</v>
+        <v>0.11194134016450341</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431455421383838</v>
+        <v>0.15431401967732511</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1416574.1789707153</v>
+        <v>1407511.3949538951</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1416574.1789707153</v>
+        <v>1407511.3949538951</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.58539825656385702</v>
+        <v>0.58165950671107025</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55939094360755792</v>
+        <v>0.55581998062973026</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13001,12 +13001,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5913538249616732E-2</v>
+        <v>3.5544021344529921E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5913538249616732E-2</v>
+        <v>3.5544021344529921E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13138,26 +13138,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093268067142703</v>
+        <v>-0.11093377250044745</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1090583436463035E-2</v>
+        <v>9.1093499302190573E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21551872606386369</v>
+        <v>-0.21552165444160154</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11680986454869746</v>
+        <v>-0.11681540069477081</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633548431534908</v>
+        <v>1.4633486518026819</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13753,15 +13753,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.0772405303100427</v>
+        <v>2.0772788433819436</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3548902903105238</v>
+        <v>1.3549077551671957</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733566911275863</v>
+        <v>1.8733631803471393</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13857,24 +13857,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.1233241782163965</v>
+        <v>0.12332281299076012</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655485824026122</v>
+        <v>0.12655361266586321</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12051631452344605</v>
+        <v>0.1205148063137582</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.1643130091429994</v>
+        <v>0.16431156619261764</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267622355509813</v>
+        <v>0.21267568901858486</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14143,50 +14143,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.99897803494091586</v>
+        <v>1.0053991953242325</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0454227167650891</v>
+        <v>1.0521392184164307</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.93167175388286361</v>
+        <v>0.93765337365008783</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1924516845306412</v>
+        <v>1.2001142571015424</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4379718336001228</v>
+        <v>1.4472257353238485</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57771814149389367</v>
+        <v>0.58143799396381246</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.56922190976733134</v>
+        <v>0.57288705609890489</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24481876709907854</v>
+        <v>0.24639512350900719</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.1872083531782929</v>
+        <v>0.18841376357644821</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.5538064443851337E-2</v>
+        <v>9.61532216969605E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>4.9675467084350075E-3</v>
+        <v>4.9995320998665899E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14200,50 +14200,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5463829288395545E-2</v>
+        <v>6.5626579329258014E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8507386419730615E-2</v>
+        <v>6.8677494674701745E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1053194880921598E-2</v>
+        <v>6.1204528306141502E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8142312223502042E-2</v>
+        <v>7.8336439758586313E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.4231443879431373E-2</v>
+        <v>9.4466431809650683E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7858331683741392E-2</v>
+        <v>3.7952871668656164E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7301566826168503E-2</v>
+        <v>3.7394716455542092E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6043169534670939E-2</v>
+        <v>1.608323260502658E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2267913052312772E-2</v>
+        <v>1.2298548536321684E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2606857433716474E-3</v>
+        <v>6.276319954109693E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2552730723689433E-4</v>
+        <v>3.2634021539599151E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14257,43 +14257,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6384666219583591E-2</v>
+        <v>7.6085509563371123E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0797097240780061E-2</v>
+        <v>8.0480659523126871E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10302629923145053</v>
+        <v>0.10262280197597487</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10168558889559332</v>
+        <v>0.10128734246388733</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3060625420042374E-2</v>
+        <v>4.2891980672966484E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8006855039010426E-2</v>
+        <v>3.7858003126325E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8133625114994174E-2</v>
+        <v>1.8062605695483753E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3060409452348052E-2</v>
+        <v>1.3009259023683504E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7768702841781069E-2</v>
+        <v>1.7699112621774094E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5618338641999042E-3</v>
+        <v>1.5557170213897219E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419846.9385366049</v>
+        <v>2419820.1503015291</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30248086.731707562</v>
+        <v>30247751.878769115</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14101919.824155236</v>
+        <v>14103430.28815804</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42975441.755862802</v>
+        <v>42976617.366927162</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.06707424</v>
+        <v>1.0739449931617173</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>25.698585826791245</v>
+        <v>25.864455494710416</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2581246.5565844495</v>
+        <v>2581217.9816202871</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2390043.107948564</v>
+        <v>2390016.6496484135</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2753411.2508406858</v>
+        <v>2753380.7699756878</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2360606.353601411</v>
+        <v>2360580.2211725716</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2937059.0333252563</v>
+        <v>2937026.519439124</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2331532.154433121</v>
+        <v>2331506.3438620283</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3132955.8062217031</v>
+        <v>3132921.1237154324</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2302816.0450649322</v>
+        <v>2302790.5523874532</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3341918.5560684991</v>
+        <v>3341881.5602988661</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2274453.6151155229</v>
+        <v>2274428.4364163494</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3564818.7609974318</v>
+        <v>3564779.2976737591</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2246440.5085236426</v>
+        <v>2246415.6399356881</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3802586.0252289139</v>
+        <v>3802543.9297696026</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2218772.4228790854</v>
+        <v>2218747.8605828932</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4056211.9559818613</v>
+        <v>4056167.0528280027</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2191445.1087618973</v>
+        <v>2191420.8489850517</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4326754.2989667794</v>
+        <v>4326706.4008499887</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2164454.3690897315</v>
+        <v>2164430.4081062796</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4615341.3497090973</v>
+        <v>4615290.2568705119</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2137796.0584732313</v>
+        <v>2137772.392603111</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4923176.6591001768</v>
+        <v>4923122.1584573612</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2111466.0825793641</v>
+        <v>2111442.7081878376</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5251544.052800443</v>
+        <v>5251485.9170587324</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2085460.3975025858</v>
+        <v>2085437.3109996833</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>5601812.9854280585</v>
+        <v>5601750.9721326241</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2059775.0091437572</v>
+        <v>2059752.2069837239</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5975444.2518627504</v>
+        <v>5975378.102387445</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2034405.9725967075</v>
+        <v>2034383.4512774595</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>6373996.0794837466</v>
+        <v>6373925.5179525064</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2009349.3915423544</v>
+        <v>2009327.1476049412</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>6799130.6267494811</v>
+        <v>6799055.3588857818</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1984601.4176502838</v>
+        <v>1984579.4476783562</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7252620.9152213642</v>
+        <v>7252540.6271209475</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1960158.2499877026</v>
+        <v>1960136.5506069895</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>7736358.2239415739</v>
+        <v>7736272.5807633065</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1936016.1344356691</v>
+        <v>1935994.7023134574</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8252359.9770031068</v>
+        <v>8252268.6215725318</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1912171.3631125176</v>
+        <v>1912150.1949571418</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>8802778.1572071388</v>
+        <v>8802680.7085268777</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1888620.2738043757</v>
+        <v>1888599.3663647119</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>32265581.957305618</v>
+        <v>32265224.770253588</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6922522.7697885903</v>
+        <v>6922446.1359468689</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>49522906.806035042</v>
+        <v>49522358.576621011</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +15961,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>49522906.806035042</v>
+        <v>49522358.576621011</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15991,19 +15991,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30248086.731707558</v>
+        <v>30247751.878769107</v>
       </c>
       <c r="C56" s="124">
-        <v>31224048.350294434</v>
+        <v>31223702.693247329</v>
       </c>
       <c r="D56" s="124">
-        <v>32743195.621029567</v>
+        <v>32742833.146689784</v>
       </c>
       <c r="E56" s="124">
-        <v>34332481.430464387</v>
+        <v>34332101.362382948</v>
       </c>
       <c r="F56" s="124">
-        <v>35433217.183896236</v>
+        <v>35432824.930429168</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16012,19 +16012,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30248086.731707551</v>
+        <v>30247751.8787691</v>
       </c>
       <c r="C57" s="124">
-        <v>32200908.675305784</v>
+        <v>32200552.204201151</v>
       </c>
       <c r="D57" s="124">
-        <v>35504347.808854535</v>
+        <v>35503954.767955884</v>
       </c>
       <c r="E57" s="124">
-        <v>39330043.530605555</v>
+        <v>39329608.13841819</v>
       </c>
       <c r="F57" s="124">
-        <v>42217047.541471303</v>
+        <v>42216580.189517871</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16033,19 +16033,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30248086.731707543</v>
+        <v>30247751.8787691</v>
       </c>
       <c r="C58" s="124">
-        <v>33410044.185494367</v>
+        <v>33409674.328995079</v>
       </c>
       <c r="D58" s="124">
-        <v>39200981.130278051</v>
+        <v>39200547.166839711</v>
       </c>
       <c r="E58" s="124">
-        <v>46595999.185969457</v>
+        <v>46595483.358063191</v>
       </c>
       <c r="F58" s="124">
-        <v>52658118.310512409</v>
+        <v>52657535.373621032</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16054,19 +16054,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30248086.731707543</v>
+        <v>30247751.8787691</v>
       </c>
       <c r="C59" s="124">
-        <v>34641959.364284962</v>
+        <v>34641575.870215103</v>
       </c>
       <c r="D59" s="124">
-        <v>43295504.327407271</v>
+        <v>43295025.036701247</v>
       </c>
       <c r="E59" s="124">
-        <v>55405785.379277624</v>
+        <v>55405172.025110602</v>
       </c>
       <c r="F59" s="124">
-        <v>66147861.126979135</v>
+        <v>66147128.855683215</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16075,19 +16075,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30248086.731707543</v>
+        <v>30247751.8787691</v>
       </c>
       <c r="C60" s="124">
-        <v>35787708.839545324</v>
+        <v>35787312.661778077</v>
       </c>
       <c r="D60" s="124">
-        <v>47453414.122248963</v>
+        <v>47452888.802571751</v>
       </c>
       <c r="E60" s="124">
-        <v>65266276.695778228</v>
+        <v>65265554.183814839</v>
       </c>
       <c r="F60" s="124">
-        <v>82325865.844880357</v>
+        <v>82324954.479532436</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16096,19 +16096,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30248086.731707547</v>
+        <v>30247751.8787691</v>
       </c>
       <c r="C61" s="124">
-        <v>36798419.259848557</v>
+        <v>36798011.893295817</v>
       </c>
       <c r="D61" s="124">
-        <v>51474303.678607337</v>
+        <v>51473733.846802957</v>
       </c>
       <c r="E61" s="124">
-        <v>75841860.264160872</v>
+        <v>75841020.678173438</v>
       </c>
       <c r="F61" s="124">
-        <v>101005781.29901917</v>
+        <v>101004663.14292002</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16158,23 +16158,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16185,23 +16185,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.741420613136924</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.144323873003135</v>
+        <v>18.261636790036654</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.771468809790999</v>
+        <v>18.892812844708843</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.427568825698952</v>
+        <v>19.553130093911509</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>19.881982211290005</v>
+        <v>20.010464325734556</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16212,23 +16212,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.741420613136921</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.547598143102938</v>
+        <v>18.667503197977538</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>19.911346850355944</v>
+        <v>20.040017712751354</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.490697152862236</v>
+        <v>21.629519651468971</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>22.682530217884658</v>
+        <v>22.82901349680186</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16239,23 +16239,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.741420613136917</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.04676186982854</v>
+        <v>19.169875414013948</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.437416715570652</v>
+        <v>21.575896741949602</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>24.490279476425574</v>
+        <v>24.648382478215456</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>26.992885634762171</v>
+        <v>27.167074711477518</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16266,23 +16266,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.741420613136917</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.55532965770125</v>
+        <v>19.681712137956826</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.127746245239898</v>
+        <v>23.277091252260099</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>28.127196654733908</v>
+        <v>28.30867677562545</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>32.561815039364021</v>
+        <v>32.771799686772205</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16293,23 +16293,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.741420613136917</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.028325920854307</v>
+        <v>20.157748693048426</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>24.844243470814199</v>
+        <v>25.004621657341264</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>32.197873226065624</v>
+        <v>32.405518554017675</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.240531409800013</v>
+        <v>39.493445038095935</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16319,23 +16319,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.741420613136921</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.445574422604356</v>
+        <v>20.577679155217744</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.504175049029833</v>
+        <v>26.67522282639499</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>36.563759151844614</v>
+        <v>36.799467212673825</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>46.952103962617393</v>
+        <v>47.254585491745253</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>46.952103962617393</v>
+        <v>47.254585491745253</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.127196654733908</v>
+        <v>28.30867677562545</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.127746245239898</v>
+        <v>23.277091252260099</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.55532965770125</v>
+        <v>19.681712137956826</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.741420613136921</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.26</v>
+        <v>-15.32</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>26.243978721197557</v>
+        <v>26.406325183731525</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532350.9348133393</v>
+        <v>2532315.2171665714</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419846.9385366049</v>
+        <v>2419820.1503015291</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10081886954414521</v>
+        <v>-0.10082205884198292</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.741420613136924</v>
+        <v>17.856143777082718</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.127746245239898</v>
+        <v>23.277091252260099</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.55532965770125</v>
+        <v>19.681712137956826</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.127196654733908</v>
+        <v>28.30867677562545</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.663125530105667</v>
+        <v>23.815911810240781</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.741420613136921</v>
+        <v>17.85614377708271</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>46.952103962617393</v>
+        <v>47.254585491745253</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>25.695938127508406</v>
+        <v>25.861790776733326</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>25.698585826791245</v>
+        <v>25.864455494710416</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.20447570936321155</v>
+        <v>0.20449681467099967</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.54804059368915137</v>
+        <v>0.54453440699819844</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.99530358162026156</v>
+        <v>0.9889359508069242</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>11.695920859129904</v>
+        <v>11.771411368563186</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.691224440750165</v>
+        <v>12.76034731937011</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.50609997666659368</v>
+        <v>0.5065945962701851</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.26</v>
+        <v>15.32</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.2202784312360544</v>
+        <v>0.22093639979403168</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1544373617063142</v>
+        <v>1.1470516443712049</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>14.870334564530328</v>
+        <v>14.966314106905861</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>16.024771926236642</v>
+        <v>16.113365751277065</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.3763694539300918</v>
+        <v>0.37694315562348735</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.4123537628858516</v>
+        <v>1.4033179797278683</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>20.398264148875619</v>
+        <v>20.52992332908897</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>21.810617911761469</v>
+        <v>21.933241308816839</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.15120367259864953</v>
+        <v>0.15190554675165124</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA8F9AE-8387-4F5D-A84D-F4456661DE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566EF734-5220-4560-BD8E-B8443BD2523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>12.76034731937011</v>
+        <v>11.864263383794571</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.22093639979403168</v>
+        <v>0.19063377748254529</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
@@ -4991,11 +4991,11 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>28.31 HKD</v>
+        <v>24.77 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
-        <v>0.21249999999999994</v>
+        <v>0.22499999999999992</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
-        <v>0.46750000000000003</v>
+        <v>0.495</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>25.861790776733326</v>
+        <v>23.893094370273865</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>11.771411368563186</v>
+        <v>10.875327432987646</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>12.76034731937011</v>
+        <v>11.864263383794571</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5065945962701851</v>
+        <v>0.50344383193182107</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>14.966314106905861</v>
+        <v>13.827022205019597</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>16.113365751277065</v>
+        <v>14.974073849390802</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37694315562348735</v>
+        <v>0.37328863238323329</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>20.52992332908897</v>
+        <v>18.967108648860901</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>21.933241308816839</v>
+        <v>20.370426628588771</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.15190554675165124</v>
+        <v>0.14743455523566484</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5435,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -15202,7 +15202,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>25.864455494710416</v>
+        <v>23.889634822475621</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,11 +15257,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2581217.9816202871</v>
+        <v>2551088.2828502995</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2390016.6496484135</v>
+        <v>2362118.7804169436</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,11 +15279,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2753380.7699756878</v>
+        <v>2689477.3258604091</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2360580.2211725716</v>
+        <v>2305793.3177815578</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,11 +15301,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2937026.519439124</v>
+        <v>2835373.5677996967</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2331506.3438620283</v>
+        <v>2250810.9534557872</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,11 +15323,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>3132921.1237154324</v>
+        <v>2989184.2521502804</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2302790.5523874532</v>
+        <v>2197139.6608394966</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,11 +15345,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3341881.5602988661</v>
+        <v>3151338.7141565024</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2274428.4364163494</v>
+        <v>2144748.1770168687</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,11 +15367,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3564779.2976737591</v>
+        <v>3322289.5792381158</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2246415.6399356881</v>
+        <v>2093605.9845461098</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,11 +15389,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3802543.9297696026</v>
+        <v>3502514.0264138635</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2218747.8605828932</v>
+        <v>2043683.2936833932</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,11 +15411,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>4056167.0528280027</v>
+        <v>3692515.1202620701</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>2191420.8489850517</v>
+        <v>1994951.0250306674</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,11 +15433,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>4326706.4008499887</v>
+        <v>3892823.2151361872</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>2164430.4081062796</v>
+        <v>1947380.7925972433</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,11 +15455,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4615290.2568705119</v>
+        <v>4103997.4355549039</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>2137772.392603111</v>
+        <v>1900944.887265275</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,11 +15477,11 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4923122.1584573612</v>
+        <v>4326627.2368990676</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>2111442.7081878376</v>
+        <v>1855616.2606495174</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,11 +15499,11 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>5251485.9170587324</v>
+        <v>4561334.0507718325</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>2085437.3109996833</v>
+        <v>1811368.509341947</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,11 +15521,11 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>5601750.9721326241</v>
+        <v>4808773.0196147542</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>2059752.2069837239</v>
+        <v>1768175.8595320815</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,11 +15543,11 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5975378.102387445</v>
+        <v>5069634.8254217189</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>2034383.4512774595</v>
+        <v>1726013.1519940263</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,11 +15565,11 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>6373925.5179525064</v>
+        <v>5344647.6176552232</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>2009327.1476049412</v>
+        <v>1684855.8274315144</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,11 +15587,11 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>6799055.3588857818</v>
+        <v>5634579.0457464447</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1984579.4476783562</v>
+        <v>1644679.912172395</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,11 +15609,11 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>7252540.6271209475</v>
+        <v>5940238.4018524764</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1960136.5506069895</v>
+        <v>1605462.0042042423</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,11 +15631,11 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>7736272.5807633065</v>
+        <v>6262478.8798518432</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1935994.7023134574</v>
+        <v>1567179.2595429523</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,11 +15653,11 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>8252268.6215725318</v>
+        <v>6602199.9568838822</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1912150.1949571418</v>
+        <v>1529809.3789263824</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,11 +15675,11 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>8802680.7085268777</v>
+        <v>6960349.9040796384</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1888599.3663647119</v>
+        <v>1493330.5948252832</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>32265224.770253588</v>
+        <v>31888603.535628743</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6922446.1359468689</v>
+        <v>6841642.7251878064</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>49522358.576621011</v>
+        <v>44769310.35644149</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +15961,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>49522358.576621011</v>
+        <v>44769310.35644149</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
@@ -16000,7 +16000,7 @@
         <v>32742833.146689784</v>
       </c>
       <c r="E56" s="124">
-        <v>34332101.362382948</v>
+        <v>33264574.901373662</v>
       </c>
       <c r="F56" s="124">
         <v>35432824.930429168</v>
@@ -16021,7 +16021,7 @@
         <v>35503954.767955884</v>
       </c>
       <c r="E57" s="124">
-        <v>39329608.13841819</v>
+        <v>36716747.065274939</v>
       </c>
       <c r="F57" s="124">
         <v>42216580.189517871</v>
@@ -16042,7 +16042,7 @@
         <v>39200547.166839711</v>
       </c>
       <c r="E58" s="124">
-        <v>46595483.358063191</v>
+        <v>41465343.065468207</v>
       </c>
       <c r="F58" s="124">
         <v>52657535.373621032</v>
@@ -16063,7 +16063,7 @@
         <v>43295025.036701247</v>
       </c>
       <c r="E59" s="124">
-        <v>55405172.025110602</v>
+        <v>46882200.366573624</v>
       </c>
       <c r="F59" s="124">
         <v>66147128.855683215</v>
@@ -16084,7 +16084,7 @@
         <v>47452888.802571751</v>
       </c>
       <c r="E60" s="124">
-        <v>65265554.183814839</v>
+        <v>52558902.11913906</v>
       </c>
       <c r="F60" s="124">
         <v>82324954.479532436</v>
@@ -16105,7 +16105,7 @@
         <v>51473733.846802957</v>
       </c>
       <c r="E61" s="124">
-        <v>75841020.678173438</v>
+        <v>58234882.474028051</v>
       </c>
       <c r="F61" s="124">
         <v>101004663.14292002</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.553130093911509</v>
+        <v>19.109588765126258</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>21.629519651468971</v>
+        <v>20.543914830753316</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>24.648382478215456</v>
+        <v>22.516885671962019</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>28.30867677562545</v>
+        <v>24.767509120584407</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>32.405518554017675</v>
+        <v>27.126094064764565</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>36.799467212673825</v>
+        <v>29.484379278965484</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -16384,7 +16384,7 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
@@ -16392,11 +16392,11 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>28.30867677562545</v>
+        <v>24.767509120584407</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.21249999999999994</v>
+        <v>0.22499999999999992</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
-        <v>0.46750000000000003</v>
+        <v>0.495</v>
       </c>
       <c r="H76" s="121"/>
     </row>
@@ -16442,7 +16442,7 @@
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H77" s="121"/>
     </row>
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>26.406325183731525</v>
+        <v>24.437628777272064</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16968,7 +16968,7 @@
         <v>135</v>
       </c>
       <c r="C38" s="165">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
       <c r="E38" s="349"/>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>28.30867677562545</v>
+        <v>24.767509120584407</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.815911810240781</v>
+        <v>22.930619896480522</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17153,7 +17153,7 @@
         <v>148</v>
       </c>
       <c r="C58" s="166">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
       <c r="E58" s="349"/>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>25.861790776733326</v>
+        <v>23.893094370273865</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17214,7 +17214,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>6.6698275613022898E-2</v>
+        <v>5.4247061515052243E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>25.864455494710416</v>
+        <v>23.889634822475621</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.20449681467099967</v>
+        <v>0.22134654279479099</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>11.771411368563186</v>
+        <v>10.875327432987646</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>12.76034731937011</v>
+        <v>11.864263383794571</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.5065945962701851</v>
+        <v>0.50344383193182107</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17413,7 +17413,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.22093639979403168</v>
+        <v>0.19063377748254529</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>14.966314106905861</v>
+        <v>13.827022205019597</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>16.113365751277065</v>
+        <v>14.974073849390802</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37694315562348735</v>
+        <v>0.37328863238323329</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>20.52992332908897</v>
+        <v>18.967108648860901</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>21.933241308816839</v>
+        <v>20.370426628588771</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.15190554675165124</v>
+        <v>0.14743455523566484</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566EF734-5220-4560-BD8E-B8443BD2523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACEC29E-A397-416B-A9A0-F35100CE13ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>39599.103919919995</v>
+        <v>39909.279668639996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0739449931617173</v>
+        <v>1.0737034399999998</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>11.864263383794571</v>
+        <v>11.862033069653084</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19063377748254529</v>
+        <v>0.18737363316325828</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96023.943166571378</v>
+        <v>96025.191128996186</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158397.05683342862</v>
+        <v>-158395.8088710038</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806606.7167671764</v>
+        <v>-806607.02875778265</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532315.2171665714</v>
+        <v>2532316.4651289964</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419820.1503015291</v>
+        <v>2419821.086273348</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.5626579329258014E-2</v>
+        <v>6.5101907277916274E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5544021344529921E-2</v>
+        <v>3.5275706733689696E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.567489941552909</v>
+        <v>12.564668104637839</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.80443605761151837</v>
+        <v>0.80425512276443312</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14103430.28815804</v>
+        <v>14103377.513059732</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8597650165276187</v>
+        <v>5.8584251079128187</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23332487661370402</v>
+        <v>0.23327239686659199</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>4.5275447966435411</v>
+        <v>4.5265264551387059</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>47.25 HKD</v>
+        <v>47.24 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>24.77 HKD</v>
+        <v>24.76 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.28 HKD</v>
+        <v>23.27 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>17.86 HKD</v>
+        <v>17.85 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>23.893094370273865</v>
+        <v>23.887705575274836</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0.9889359508069242</v>
+        <v>0.98915843366089862</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>10.875327432987646</v>
+        <v>10.872874635992185</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>11.864263383794571</v>
+        <v>11.862033069653084</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50344383193182107</v>
+        <v>0.50342518111362788</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1470516443712049</v>
+        <v>1.1473096988218372</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>13.827022205019597</v>
+        <v>13.823903689395159</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>14.974073849390802</v>
+        <v>14.971213388216997</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37328863238323329</v>
+        <v>0.37326699958521459</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>1.4033179797278683</v>
+        <v>1.4036336869169019</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>18.967108648860901</v>
+        <v>18.962830849650423</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>20.370426628588771</v>
+        <v>20.366464536567324</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14743455523566484</v>
+        <v>0.14740808938771421</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5419,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5435,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.845693599304779</v>
+        <v>10.843254171218041</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.5275447966435411</v>
+        <v>4.5265264551387059</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14103430.28815804</v>
+        <v>14103377.513059732</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9119,11 +9119,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2212822.1162461578</v>
+        <v>-2212848.5037953123</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2030378.85592098</v>
+        <v>-2030405.2434701344</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9135,11 +9135,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2086074007674039</v>
+        <v>8.2085095156067585</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9462062447260475</v>
+        <v>8.9460899780557419</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9152,7 +9152,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4060757.71184196</v>
+        <v>4060810.4869402689</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9267,11 +9267,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2079304.6372251478</v>
+        <v>-2078836.9572112798</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.80443605761151826</v>
+        <v>-0.80425512276443323</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15146308.344372643</v>
+        <v>15142844.951390877</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.8597650165276178</v>
+        <v>5.8584251079128187</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9301,11 +9301,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>603097.65248881048</v>
+        <v>602962.00294836785</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23332487661370399</v>
+        <v>0.23327239686659196</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9318,11 +9318,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13670101.359636307</v>
+        <v>13666969.997127965</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.2886538355298036</v>
+        <v>5.2874423820149783</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9902,24 +9902,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158397.05683342862</v>
+        <v>-158395.8088710038</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158397.05683342862</v>
+        <v>-158395.8088710038</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69542.476583001437</v>
+        <v>-69541.022243720814</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20463.151202034802</v>
+        <v>-20461.850293636497</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80020.339603888002</v>
+        <v>-80019.918032142581</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9957,24 +9957,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226426.8670687056</v>
+        <v>3226428.1150311306</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3629006.2171665714</v>
+        <v>3629007.4651289964</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3326026.797416999</v>
+        <v>3326028.2517562793</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239794.2737979647</v>
+        <v>4239795.5747063635</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800575.4143961119</v>
+        <v>4800575.8359678574</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806606.7167671764</v>
+        <v>-806607.02875778265</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10124,26 +10124,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419820.1503015291</v>
+        <v>2419821.086273348</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532315.2171665714</v>
+        <v>2532316.4651289964</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256767.797416999</v>
+        <v>2256769.2517562793</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888465.2737979647</v>
+        <v>2888466.5747063635</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483219.4143961119</v>
+        <v>3483219.8359678574</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10232,26 +10232,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419820.1503015291</v>
+        <v>2419821.086273348</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532315.2171665714</v>
+        <v>2532316.4651289964</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256767.797416999</v>
+        <v>2256769.2517562793</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888465.2737979647</v>
+        <v>2888466.5747063635</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483219.4143961119</v>
+        <v>3483219.8359678574</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11093,19 +11093,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30235270686979016</v>
+        <v>0.30235260284309473</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32164228794350269</v>
+        <v>0.32164214722537882</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31886279548686669</v>
+        <v>0.31886269760704133</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447357401411399</v>
+        <v>0.27447354990553091</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11231,24 +11231,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96023.943166571378</v>
+        <v>96025.191128996186</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96023.943166571378</v>
+        <v>96025.191128996186</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111903.52341699856</v>
+        <v>111904.97775627919</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100097.8487979652</v>
+        <v>100099.1497063635</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32437.660396112002</v>
+        <v>32438.081967857423</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11343,24 +11343,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158397.05683342862</v>
+        <v>-158395.8088710038</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158397.05683342862</v>
+        <v>-158395.8088710038</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69542.476583001437</v>
+        <v>-69541.022243720814</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20463.151202034802</v>
+        <v>-20461.850293636497</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80020.339603888002</v>
+        <v>-80019.918032142581</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12430,26 +12430,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0543664626444334E-3</v>
+        <v>6.0543187621252288E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5237490867573093E-3</v>
+        <v>5.5237055668116595E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.519792715587292E-3</v>
+        <v>2.5197400192539807E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9304140864144834E-4</v>
+        <v>7.9299099244608726E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.545071036635066E-3</v>
+        <v>3.5450523601111726E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12487,26 +12487,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12332281299076012</v>
+        <v>0.12332286069127933</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655361266586321</v>
+        <v>0.12655365618580885</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1205148063137582</v>
+        <v>0.1205148590100915</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16431156619261764</v>
+        <v>0.16431161660881302</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267568901858486</v>
+        <v>0.21267570769510877</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0830703247690029E-2</v>
+        <v>3.0830715172819833E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12659,26 +12659,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2492109743070081E-2</v>
+        <v>9.2492145518459495E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8308925354056447E-2</v>
+        <v>8.8308968874002108E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.1771419945278853E-2</v>
+        <v>8.177147264161215E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11194134016450341</v>
+        <v>0.1119413905806988</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431401967732511</v>
+        <v>0.15431403835384902</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12766,26 +12766,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2492109743070081E-2</v>
+        <v>9.2492145518459495E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8308925354056447E-2</v>
+        <v>8.8308968874002108E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.1771419945278853E-2</v>
+        <v>8.177147264161215E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11194134016450341</v>
+        <v>0.1119413905806988</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431401967732511</v>
+        <v>0.15431403835384902</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1407511.3949538951</v>
+        <v>1407828.0455437494</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1407511.3949538951</v>
+        <v>1407828.0455437494</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.58165950671107025</v>
+        <v>0.58179013875438157</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55581998062973026</v>
+        <v>0.55594475055945836</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13001,12 +13001,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5544021344529921E-2</v>
+        <v>3.5275706733689696E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5544021344529921E-2</v>
+        <v>3.5275706733689696E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13138,26 +13138,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093377250044745</v>
+        <v>-0.11093373435195064</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1093499302190573E-2</v>
+        <v>9.1093397421603939E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21552165444160154</v>
+        <v>-0.21552155212421276</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11681540069477081</v>
+        <v>-0.11681520726324146</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633486518026819</v>
+        <v>1.4633488681263724</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13753,15 +13753,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.0772788433819436</v>
+        <v>2.0772775047124203</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3549077551671957</v>
+        <v>1.3549071449434551</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733631803471393</v>
+        <v>1.8733629536152581</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13857,24 +13857,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12332281299076012</v>
+        <v>0.12332286069127933</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655361266586321</v>
+        <v>0.12655365618580885</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.1205148063137582</v>
+        <v>0.1205148590100915</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16431156619261764</v>
+        <v>0.16431161660881302</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267568901858486</v>
+        <v>0.21267570769510877</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14143,50 +14143,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0053991953242325</v>
+        <v>1.0051734483710271</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0521392184164307</v>
+        <v>1.0519030882322462</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.93765337365008783</v>
+        <v>0.93744307950431427</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2001142571015424</v>
+        <v>1.1998448661646506</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4472257353238485</v>
+        <v>1.4469003984696525</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58143799396381246</v>
+        <v>0.581307216143087</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57288705609890489</v>
+        <v>0.57275820156669999</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24639512350900719</v>
+        <v>0.24633970398426958</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18841376357644821</v>
+        <v>0.18837138529767902</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.61532216969605E-2</v>
+        <v>9.6131594784168772E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>4.9995320998665899E-3</v>
+        <v>4.9984075983385591E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14200,50 +14200,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5626579329258014E-2</v>
+        <v>6.5101907277916274E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8677494674701745E-2</v>
+        <v>6.8128438357010768E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1204528306141502E-2</v>
+        <v>6.0715225356497038E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8336439758586313E-2</v>
+        <v>7.7710159725689801E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.4466431809650683E-2</v>
+        <v>9.3711165703993043E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7952871668656164E-2</v>
+        <v>3.7649431097350194E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7394716455542092E-2</v>
+        <v>3.7095738443439122E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.608323260502658E-2</v>
+        <v>1.5954644040431967E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2298548536321684E-2</v>
+        <v>1.2200219255031026E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.276319954109693E-3</v>
+        <v>6.2261395585601542E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2634021539599151E-4</v>
+        <v>3.2373106206855956E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14257,43 +14257,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6085509563371123E-2</v>
+        <v>7.5494171406142854E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0480659523126871E-2</v>
+        <v>7.9855162169320176E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10262280197597487</v>
+        <v>0.10182521543212013</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10128734246388733</v>
+        <v>0.10050013513903847</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2891980672966484E-2</v>
+        <v>4.2558623310223226E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7858003126325E-2</v>
+        <v>3.7563769941405381E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8062605695483753E-2</v>
+        <v>1.792222274966393E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3009259023683504E-2</v>
+        <v>1.2908150792929486E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7699112621774094E-2</v>
+        <v>1.7561554751656678E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5557170213897219E-3</v>
+        <v>1.5436259564566412E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419820.1503015291</v>
+        <v>2419821.086273348</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30247751.878769115</v>
+        <v>30247763.57841685</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14103430.28815804</v>
+        <v>14103377.513059732</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42976617.366927162</v>
+        <v>42976576.291476585</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0739449931617173</v>
+        <v>1.0737034399999998</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>23.889634822475621</v>
+        <v>23.884246804264929</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551088.2828502995</v>
+        <v>2551089.2695958391</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362118.7804169436</v>
+        <v>2362119.6940702209</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689477.3258604091</v>
+        <v>2689478.3661339944</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305793.3177815578</v>
+        <v>2305794.2096484862</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835373.5677996967</v>
+        <v>2835374.6645050677</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250810.9534557872</v>
+        <v>2250811.8240558696</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989184.2521502804</v>
+        <v>2989185.4083486949</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197139.6608394966</v>
+        <v>2197140.5106798471</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151338.7141565024</v>
+        <v>3151339.9330752832</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144748.1770168687</v>
+        <v>2144749.0065925093</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322289.5792381158</v>
+        <v>3322290.8642796585</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093605.9845461098</v>
+        <v>2093606.7943402592</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502514.0264138635</v>
+        <v>3502515.3811651343</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043683.2936833932</v>
+        <v>2043684.0841677475</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692515.1202620701</v>
+        <v>3692516.5485046166</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994951.0250306674</v>
+        <v>1994951.7966656748</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892823.2151361872</v>
+        <v>3892824.7208566945</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947380.7925972433</v>
+        <v>1947381.5458323718</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103997.4355549039</v>
+        <v>4103999.0229563243</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900944.887265275</v>
+        <v>1900945.622539276</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326627.2368990676</v>
+        <v>4326628.9104123507</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855616.2606495174</v>
+        <v>1855616.9783906792</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561334.0507718325</v>
+        <v>4561335.8150682934</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811368.509341947</v>
+        <v>1811369.2099683459</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808773.0196147542</v>
+        <v>4808774.8796191132</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768175.8595320815</v>
+        <v>1768176.5434518242</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069634.8254217189</v>
+        <v>5069636.7863258496</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1726013.1519940263</v>
+        <v>1726013.8196054886</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344647.6176552232</v>
+        <v>5344649.6849326408</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684855.8274315144</v>
+        <v>1684856.4791235721</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634579.0457464447</v>
+        <v>5634581.2251675874</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644679.912172395</v>
+        <v>1644680.5483246513</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940238.4018524764</v>
+        <v>5940240.6995008122</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605462.0042042423</v>
+        <v>1605462.6251872489</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262478.8798518432</v>
+        <v>6262481.3021408496</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567179.2595429523</v>
+        <v>1567179.8657184243</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602199.9568838822</v>
+        <v>6602202.510574949</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529809.3789263824</v>
+        <v>1529809.9706474103</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960349.9040796384</v>
+        <v>6960352.5963009419</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493330.5948252832</v>
+        <v>1493331.1724365379</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888603.535628743</v>
+        <v>31888615.869947989</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841642.7251878064</v>
+        <v>6841645.37149389</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44769310.35644149</v>
+        <v>44769327.672940329</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +15961,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44769310.35644149</v>
+        <v>44769327.672940329</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15991,19 +15991,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30247751.878769107</v>
+        <v>30247763.578416843</v>
       </c>
       <c r="C56" s="124">
-        <v>31223702.693247329</v>
+        <v>31223714.770386942</v>
       </c>
       <c r="D56" s="124">
-        <v>32742833.146689784</v>
+        <v>32742845.811419886</v>
       </c>
       <c r="E56" s="124">
-        <v>33264574.901373662</v>
+        <v>33264587.767910317</v>
       </c>
       <c r="F56" s="124">
-        <v>35432824.930429168</v>
+        <v>35432838.635631844</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16012,19 +16012,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30247751.8787691</v>
+        <v>30247763.578416839</v>
       </c>
       <c r="C57" s="124">
-        <v>32200552.204201151</v>
+        <v>32200564.65918025</v>
       </c>
       <c r="D57" s="124">
-        <v>35503954.767955884</v>
+        <v>35503968.500671156</v>
       </c>
       <c r="E57" s="124">
-        <v>36716747.065274939</v>
+        <v>36716761.267090946</v>
       </c>
       <c r="F57" s="124">
-        <v>42216580.189517871</v>
+        <v>42216596.518636107</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16033,19 +16033,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30247751.8787691</v>
+        <v>30247763.578416832</v>
       </c>
       <c r="C58" s="124">
-        <v>33409674.328995079</v>
+        <v>33409687.25165531</v>
       </c>
       <c r="D58" s="124">
-        <v>39200547.166839711</v>
+        <v>39200562.329374589</v>
       </c>
       <c r="E58" s="124">
-        <v>41465343.065468207</v>
+        <v>41465359.10401246</v>
       </c>
       <c r="F58" s="124">
-        <v>52657535.373621032</v>
+        <v>52657555.741237685</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16054,19 +16054,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30247751.8787691</v>
+        <v>30247763.578416828</v>
       </c>
       <c r="C59" s="124">
-        <v>34641575.870215103</v>
+        <v>34641589.269367412</v>
       </c>
       <c r="D59" s="124">
-        <v>43295025.036701247</v>
+        <v>43295041.782955445</v>
       </c>
       <c r="E59" s="124">
-        <v>46882200.366573624</v>
+        <v>46882218.500325561</v>
       </c>
       <c r="F59" s="124">
-        <v>66147128.855683215</v>
+        <v>66147154.440993145</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16075,19 +16075,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30247751.8787691</v>
+        <v>30247763.578416824</v>
       </c>
       <c r="C60" s="124">
-        <v>35787312.661778077</v>
+        <v>35787326.504094459</v>
       </c>
       <c r="D60" s="124">
-        <v>47452888.802571751</v>
+        <v>47452907.157062538</v>
       </c>
       <c r="E60" s="124">
-        <v>52558902.11913906</v>
+        <v>52558922.448604964</v>
       </c>
       <c r="F60" s="124">
-        <v>82324954.479532436</v>
+        <v>82324986.322327629</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16096,19 +16096,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30247751.8787691</v>
+        <v>30247763.578416828</v>
       </c>
       <c r="C61" s="124">
-        <v>36798011.893295817</v>
+        <v>36798026.12654455</v>
       </c>
       <c r="D61" s="124">
-        <v>51473733.846802957</v>
+        <v>51473753.756532319</v>
       </c>
       <c r="E61" s="124">
-        <v>58234882.474028051</v>
+        <v>58234904.998928867</v>
       </c>
       <c r="F61" s="124">
-        <v>101004663.14292002</v>
+        <v>101004702.21091367</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16158,23 +16158,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16185,23 +16185,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.85614377708271</v>
+        <v>17.852110486652812</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.261636790036654</v>
+        <v>18.257512452376318</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.892812844708843</v>
+        <v>18.888546786156009</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.109588765126258</v>
+        <v>19.105274032868703</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.010464325734556</v>
+        <v>20.005947315701199</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16212,23 +16212,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.85614377708271</v>
+        <v>17.852110486652812</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.667503197977538</v>
+        <v>18.663287729246644</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.040017712751354</v>
+        <v>20.03549406695868</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.543914830753316</v>
+        <v>20.539278042599229</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>22.82901349680186</v>
+        <v>22.823863624825908</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16239,23 +16239,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.85614377708271</v>
+        <v>17.852110486652805</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.169875414013948</v>
+        <v>19.165547145314974</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.575896741949602</v>
+        <v>21.57102823810159</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.516885671962019</v>
+        <v>22.511805883496976</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.167074711477518</v>
+        <v>27.160950794458984</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16266,23 +16266,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.85614377708271</v>
+        <v>17.852110486652805</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.681712137956826</v>
+        <v>19.677268944179826</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.277091252260099</v>
+        <v>23.271840771303591</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.767509120584407</v>
+        <v>24.761923989178271</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>32.771799686772205</v>
+        <v>32.764417314810984</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16293,23 +16293,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.85614377708271</v>
+        <v>17.852110486652805</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.157748693048426</v>
+        <v>20.153198612571668</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.004621657341264</v>
+        <v>24.99898328595544</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.126094064764565</v>
+        <v>27.119979349321063</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.493445038095935</v>
+        <v>39.484553423869919</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16319,23 +16319,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.85614377708271</v>
+        <v>17.852110486652805</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.577679155217744</v>
+        <v>20.573034785802992</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.67522282639499</v>
+        <v>26.66920934716574</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.484379278965484</v>
+        <v>29.477735046784378</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.254585491745253</v>
+        <v>47.24395123258877</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.254585491745253</v>
+        <v>47.24395123258877</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.767509120584407</v>
+        <v>24.761923989178271</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.277091252260099</v>
+        <v>23.271840771303591</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.681712137956826</v>
+        <v>19.677268944179826</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.85614377708271</v>
+        <v>17.852110486652805</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.32</v>
+        <v>-15.44</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>24.437628777272064</v>
+        <v>24.432362487243005</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532315.2171665714</v>
+        <v>2532316.4651289964</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419820.1503015291</v>
+        <v>2419821.086273348</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10082205884198292</v>
+        <v>-0.10082194740824768</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.856143777082718</v>
+        <v>17.852110486652816</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.277091252260099</v>
+        <v>23.271840771303591</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.681712137956826</v>
+        <v>19.677268944179826</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>24.767509120584407</v>
+        <v>24.761923989178271</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>22.930619896480522</v>
+        <v>22.925447210347507</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.85614377708271</v>
+        <v>17.852110486652805</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.254585491745253</v>
+        <v>47.24395123258877</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>23.893094370273865</v>
+        <v>23.887705575274836</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>23.889634822475621</v>
+        <v>23.884246804264929</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.22134654279479099</v>
+        <v>0.22134576154052185</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.54453440699819844</v>
+        <v>0.5446569119681689</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.9889359508069242</v>
+        <v>0.98915843366089862</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.875327432987646</v>
+        <v>10.872874635992185</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>11.864263383794571</v>
+        <v>11.862033069653084</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.50344383193182107</v>
+        <v>0.50342518111362788</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19063377748254529</v>
+        <v>0.18737363316325828</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1470516443712049</v>
+        <v>1.1473096988218372</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.827022205019597</v>
+        <v>13.823903689395159</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.974073849390802</v>
+        <v>14.971213388216997</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37328863238323329</v>
+        <v>0.37326699958521459</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.4033179797278683</v>
+        <v>1.4036336869169019</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>18.967108648860901</v>
+        <v>18.962830849650423</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.370426628588771</v>
+        <v>20.366464536567324</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.14743455523566484</v>
+        <v>0.14740808938771421</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACEC29E-A397-416B-A9A0-F35100CE13ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12847152-F0CD-403D-9500-00A39AA669C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>15.44</v>
+        <v>15.38</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>39909.279668639996</v>
+        <v>39754.191794279999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>1.0737034399999998</v>
+        <v>1.0742246600000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>11.862033069653084</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18737363316325828</v>
+        <v>0.18912881948046301</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96025.191128996186</v>
+        <v>96022.498994366397</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158395.8088710038</v>
+        <v>-158398.50100563362</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806607.02875778265</v>
+        <v>-806606.35572412517</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532316.4651289964</v>
+        <v>2532313.7729943665</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419821.086273348</v>
+        <v>2419819.0671723755</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.5101907277916274E-2</v>
+        <v>6.5387552793081283E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5275706733689696E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.564668104637839</v>
+        <v>12.570757024469875</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.80425512276443312</v>
+        <v>0.80464554142145772</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14103377.513059732</v>
+        <v>14103491.360774152</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8584251079128187</v>
+        <v>5.8613163437933213</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23327239686659199</v>
+        <v>0.23338563692354369</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>4.5265264551387059</v>
+        <v>4.5287238180520148</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>47.24 HKD</v>
+        <v>47.27 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>24.76 HKD</v>
+        <v>24.77 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.27 HKD</v>
+        <v>23.28 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.68 HKD</v>
+        <v>19.69 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>17.85 HKD</v>
+        <v>17.86 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>23.887705575274836</v>
+        <v>23.899333440997744</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0.98915843366089862</v>
+        <v>0.98867848828448812</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>10.872874635992185</v>
+        <v>10.878167246699016</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>11.862033069653084</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50342518111362788</v>
+        <v>0.50346540985002086</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1473096988218372</v>
+        <v>1.1467530175395249</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>13.823903689395159</v>
+        <v>13.830632778355175</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>14.971213388216997</v>
+        <v>14.977385795894701</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37326699958521459</v>
+        <v>0.37331366027966395</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>1.4036336869169019</v>
+        <v>1.4029526357573658</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>18.962830849650423</v>
+        <v>18.97206142435552</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>20.366464536567324</v>
+        <v>20.375014060112886</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14740808938771421</v>
+        <v>0.14746517469140452</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5435,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.843254171218041</v>
+        <v>10.848517934682489</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.5265264551387059</v>
+        <v>4.5287238180520148</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14103377.513059732</v>
+        <v>14103491.360774152</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9119,11 +9119,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2212848.5037953123</v>
+        <v>-2212791.5799381016</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2030405.2434701344</v>
+        <v>-2030348.3196129238</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9135,11 +9135,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2085095156067585</v>
+        <v>8.2087206787491969</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9460899780557419</v>
+        <v>8.9463407950922011</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9152,7 +9152,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4060810.4869402689</v>
+        <v>4060696.6392258476</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9267,11 +9267,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2078836.9572112798</v>
+        <v>-2079846.11053842</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.80425512276443323</v>
+        <v>-0.80464554142145761</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9284,11 +9284,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15142844.951390877</v>
+        <v>15150318.211840551</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.8584251079128187</v>
+        <v>5.8613163437933204</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9301,11 +9301,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>602962.00294836785</v>
+        <v>603254.70561045199</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23327239686659196</v>
+        <v>0.23338563692354367</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9318,11 +9318,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13666969.997127965</v>
+        <v>13673726.806912584</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.2874423820149783</v>
+        <v>5.2900564392954061</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -9902,24 +9902,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158395.8088710038</v>
+        <v>-158398.50100563362</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158395.8088710038</v>
+        <v>-158398.50100563362</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69541.022243720814</v>
+        <v>-69544.159579479499</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20461.850293636497</v>
+        <v>-20464.656644596791</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80019.918032142581</v>
+        <v>-80020.827456875428</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -9957,24 +9957,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226428.1150311306</v>
+        <v>3226425.4228965007</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3629007.4651289964</v>
+        <v>3629004.7729943665</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3326028.2517562793</v>
+        <v>3326025.1144205206</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239795.5747063635</v>
+        <v>4239792.7683554031</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800575.8359678574</v>
+        <v>4800574.926543124</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806607.02875778265</v>
+        <v>-806606.35572412517</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10124,26 +10124,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419821.086273348</v>
+        <v>2419819.0671723755</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532316.4651289964</v>
+        <v>2532313.7729943665</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256769.2517562793</v>
+        <v>2256766.1144205206</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888466.5747063635</v>
+        <v>2888463.7683554031</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483219.8359678574</v>
+        <v>3483218.926543124</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10232,26 +10232,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419821.086273348</v>
+        <v>2419819.0671723755</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532316.4651289964</v>
+        <v>2532313.7729943665</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256769.2517562793</v>
+        <v>2256766.1144205206</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888466.5747063635</v>
+        <v>2888463.7683554031</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483219.8359678574</v>
+        <v>3483218.926543124</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11093,19 +11093,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30235260284309473</v>
+        <v>0.3023528272520794</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32164214722537882</v>
+        <v>0.32164245078606191</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31886269760704133</v>
+        <v>0.31886290875583534</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447354990553091</v>
+        <v>0.2744736019131529</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11231,24 +11231,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96025.191128996186</v>
+        <v>96022.498994366397</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96025.191128996186</v>
+        <v>96022.498994366397</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111904.97775627919</v>
+        <v>111901.8404205205</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100099.1497063635</v>
+        <v>100096.34335540321</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32438.081967857423</v>
+        <v>32437.172543124572</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11343,24 +11343,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158395.8088710038</v>
+        <v>-158398.50100563362</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158395.8088710038</v>
+        <v>-158398.50100563362</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69541.022243720814</v>
+        <v>-69544.159579479499</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20461.850293636497</v>
+        <v>-20464.656644596791</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80019.918032142581</v>
+        <v>-80020.827456875428</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12430,26 +12430,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0543187621252288E-3</v>
+        <v>6.054421662835264E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5237055668116595E-3</v>
+        <v>5.5237994490876319E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5197400192539807E-3</v>
+        <v>2.5198536970546504E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9299099244608726E-4</v>
+        <v>7.9309975147819924E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5450523601111726E-3</v>
+        <v>3.5450926495587854E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12487,26 +12487,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12332286069127933</v>
+        <v>0.1233227577905693</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655365618580885</v>
+        <v>0.12655356230353287</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.1205148590100915</v>
+        <v>0.12051474533229084</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16431161660881302</v>
+        <v>0.16431150784978091</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267570769510877</v>
+        <v>0.21267566740566113</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0830715172819833E-2</v>
+        <v>3.0830689447642324E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12659,26 +12659,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2492145518459495E-2</v>
+        <v>9.2492068342926975E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8308968874002108E-2</v>
+        <v>8.8308874991726127E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.177147264161215E-2</v>
+        <v>8.1771358963811491E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.1119413905806988</v>
+        <v>0.11194128182166668</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431403835384902</v>
+        <v>0.15431399806440138</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12766,26 +12766,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2492145518459495E-2</v>
+        <v>9.2492068342926975E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8308968874002108E-2</v>
+        <v>8.8308874991726127E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.177147264161215E-2</v>
+        <v>8.1771358963811491E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.1119413905806988</v>
+        <v>0.11194128182166668</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431403835384902</v>
+        <v>0.15431399806440138</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1407828.0455437494</v>
+        <v>1407144.9592572188</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1407828.0455437494</v>
+        <v>1407144.9592572188</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -12946,12 +12946,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.58179013875438157</v>
+        <v>0.5815083360350185</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55594475055945836</v>
+        <v>0.55567559370548403</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13001,12 +13001,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5275706733689696E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5275706733689696E-2</v>
+        <v>3.5396140526234639E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13138,26 +13138,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093373435195064</v>
+        <v>-0.11093381664684043</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1093397421603939E-2</v>
+        <v>9.1093617200973087E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21552155212421276</v>
+        <v>-0.21552177284582918</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11681520726324146</v>
+        <v>-0.11681562453844208</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633488681263724</v>
+        <v>1.4633484014676914</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13753,15 +13753,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.0772775047124203</v>
+        <v>2.0772803925247438</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3549071449434551</v>
+        <v>1.3549084613335061</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733629536152581</v>
+        <v>1.8733634427268071</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13857,24 +13857,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12332286069127933</v>
+        <v>0.1233227577905693</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655365618580885</v>
+        <v>0.12655356230353287</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.1205148590100915</v>
+        <v>0.12051474533229084</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16431161660881302</v>
+        <v>0.16431150784978091</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267570769510877</v>
+        <v>0.21267566740566113</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14143,50 +14143,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0051734483710271</v>
+        <v>1.0056605619575902</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0519030882322462</v>
+        <v>1.0524126066079345</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.93744307950431427</v>
+        <v>0.93789684924129824</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.1998448661646506</v>
+        <v>1.2004261541226664</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4469003984696525</v>
+        <v>1.4476024057376935</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.581307216143087</v>
+        <v>0.58158940667718662</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57275820156669999</v>
+        <v>0.57303624205600001</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24633970398426958</v>
+        <v>0.24645928745185233</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18837138529767902</v>
+        <v>0.18846282854894111</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.6131594784168772E-2</v>
+        <v>9.6178261031073436E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>4.9984075983385591E-3</v>
+        <v>5.0008340318502256E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14200,50 +14200,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5101907277916274E-2</v>
+        <v>6.5387552793081283E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8128438357010768E-2</v>
+        <v>6.8427347633805882E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.0715225356497038E-2</v>
+        <v>6.0981589677587655E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.7710159725689801E-2</v>
+        <v>7.8051115352579081E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.3711165703993043E-2</v>
+        <v>9.4122393090877332E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7649431097350194E-2</v>
+        <v>3.7814655830766361E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7095738443439122E-2</v>
+        <v>3.7258533293628091E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5954644040431967E-2</v>
+        <v>1.6024661082695211E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2200219255031026E-2</v>
+        <v>1.2253759983676275E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2261395585601542E-3</v>
+        <v>6.2534630059215496E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2373106206855956E-4</v>
+        <v>3.2515175759754392E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14257,43 +14257,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5494171406142854E-2</v>
+        <v>7.5788687029313753E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9855162169320176E-2</v>
+        <v>8.0166690760357845E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10182521543212013</v>
+        <v>0.10222245294355883</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10050013513903847</v>
+        <v>0.10089220328652496</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2558623310223226E-2</v>
+        <v>4.2724651749664923E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7563769941405381E-2</v>
+        <v>3.7710312606976534E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.792222274966393E-2</v>
+        <v>1.7992140393680828E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2908150792929486E-2</v>
+        <v>1.2958507688090459E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7561554751656678E-2</v>
+        <v>1.7630065368373152E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5436259564566412E-3</v>
+        <v>1.5496479042711663E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419821.086273348</v>
+        <v>2419819.0671723755</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30247763.57841685</v>
+        <v>30247738.339654692</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14103377.513059732</v>
+        <v>14103491.360774152</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42976576.291476585</v>
+        <v>42976664.900428846</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0737034399999998</v>
+        <v>1.0742246600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15169,7 +15169,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>23.884246804264929</v>
+        <v>23.895872993844932</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551089.2695958391</v>
+        <v>2551087.1409645719</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15269,7 +15269,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362119.6940702209</v>
+        <v>2362117.7231153441</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,7 +15279,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689478.3661339944</v>
+        <v>2689476.1220307359</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15291,7 +15291,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305794.2096484862</v>
+        <v>2305792.2856916459</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,7 +15301,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835374.6645050677</v>
+        <v>2835372.2986658015</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15313,7 +15313,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250811.8240558696</v>
+        <v>2250809.9459763826</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989185.4083486949</v>
+        <v>2989182.9141696007</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197140.5106798471</v>
+        <v>2197138.6773837549</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151339.9330752832</v>
+        <v>3151337.3035943024</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15357,7 +15357,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144749.0065925093</v>
+        <v>2144747.2170119369</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,7 +15367,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322290.8642796585</v>
+        <v>3322288.0921570612</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093606.7943402592</v>
+        <v>2093605.0474327963</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,7 +15389,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502515.3811651343</v>
+        <v>3502512.4586630315</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043684.0841677475</v>
+        <v>2043682.3789158405</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692516.5485046166</v>
+        <v>3692513.4674653625</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994951.7966656748</v>
+        <v>1994950.1320760339</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,7 +15433,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892824.7208566945</v>
+        <v>3892821.4726801147</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947381.5458323718</v>
+        <v>1947379.9209353926</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103999.0229563243</v>
+        <v>4103995.5985757094</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900945.622539276</v>
+        <v>1900944.0363884745</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326628.9104123507</v>
+        <v>4326625.3002691502</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855616.9783906792</v>
+        <v>1855615.4300621408</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,7 +15499,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561335.8150682934</v>
+        <v>4561332.0090854326</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15511,7 +15511,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811369.2099683459</v>
+        <v>1811367.6985601869</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808774.8796191132</v>
+        <v>4808770.8671728661</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768176.5434518242</v>
+        <v>1768175.0680836663</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069636.7863258496</v>
+        <v>5069632.556216184</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15555,7 +15555,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1726013.8196054886</v>
+        <v>1726012.3794179468</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344649.6849326408</v>
+        <v>5344645.2253519557</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15577,7 +15577,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684856.4791235721</v>
+        <v>1684855.0732777535</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,7 +15587,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634581.2251675874</v>
+        <v>5634576.5236677546</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644680.5483246513</v>
+        <v>1644679.1760016668</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940240.6995008122</v>
+        <v>5940235.7429584283</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605462.6251872489</v>
+        <v>1605461.2855877359</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262481.3021408496</v>
+        <v>6262476.0767206065</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567179.8657184243</v>
+        <v>1567178.5580620817</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602202.510574949</v>
+        <v>6602197.0016910136</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529809.9706474103</v>
+        <v>1529808.6941725432</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960352.5963009419</v>
+        <v>6960346.7885762397</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493331.1724365379</v>
+        <v>1493329.926399614</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888615.869947989</v>
+        <v>31888589.262057148</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841645.37149389</v>
+        <v>6841639.6628186069</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44769327.672940329</v>
+        <v>44769290.317371547</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +15961,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44769327.672940329</v>
+        <v>44769290.317371547</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -15991,19 +15991,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30247763.578416843</v>
+        <v>30247738.339654684</v>
       </c>
       <c r="C56" s="124">
-        <v>31223714.770386942</v>
+        <v>31223688.7172902</v>
       </c>
       <c r="D56" s="124">
-        <v>32742845.811419886</v>
+        <v>32742818.490758788</v>
       </c>
       <c r="E56" s="124">
-        <v>33264587.767910317</v>
+        <v>33264560.01190725</v>
       </c>
       <c r="F56" s="124">
-        <v>35432838.635631844</v>
+        <v>35432809.070438221</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16012,19 +16012,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30247763.578416839</v>
+        <v>30247738.33965468</v>
       </c>
       <c r="C57" s="124">
-        <v>32200564.65918025</v>
+        <v>32200537.790999055</v>
       </c>
       <c r="D57" s="124">
-        <v>35503968.500671156</v>
+        <v>35503938.876126707</v>
       </c>
       <c r="E57" s="124">
-        <v>36716761.267090946</v>
+        <v>36716730.630591087</v>
       </c>
       <c r="F57" s="124">
-        <v>42216596.518636107</v>
+        <v>42216561.293068573</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16033,19 +16033,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30247763.578416832</v>
+        <v>30247738.339654677</v>
       </c>
       <c r="C58" s="124">
-        <v>33409687.25165531</v>
+        <v>33409659.374581091</v>
       </c>
       <c r="D58" s="124">
-        <v>39200562.329374589</v>
+        <v>39200529.620388806</v>
       </c>
       <c r="E58" s="124">
-        <v>41465359.10401246</v>
+        <v>41465324.50527814</v>
       </c>
       <c r="F58" s="124">
-        <v>52657555.741237685</v>
+        <v>52657511.803724028</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16054,19 +16054,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30247763.578416828</v>
+        <v>30247738.339654677</v>
       </c>
       <c r="C59" s="124">
-        <v>34641589.269367412</v>
+        <v>34641560.364392996</v>
       </c>
       <c r="D59" s="124">
-        <v>43295041.782955445</v>
+        <v>43295005.65753217</v>
       </c>
       <c r="E59" s="124">
-        <v>46882218.500325561</v>
+        <v>46882179.381758712</v>
       </c>
       <c r="F59" s="124">
-        <v>66147154.440993145</v>
+        <v>66147099.247745737</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16075,19 +16075,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30247763.578416824</v>
+        <v>30247738.339654673</v>
       </c>
       <c r="C60" s="124">
-        <v>35787326.504094459</v>
+        <v>35787296.643115826</v>
       </c>
       <c r="D60" s="124">
-        <v>47452907.157062538</v>
+        <v>47452867.562312521</v>
       </c>
       <c r="E60" s="124">
-        <v>52558922.448604964</v>
+        <v>52558878.593391038</v>
       </c>
       <c r="F60" s="124">
-        <v>82324986.322327629</v>
+        <v>82324917.630282193</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16096,19 +16096,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30247763.578416828</v>
+        <v>30247738.339654677</v>
       </c>
       <c r="C61" s="124">
-        <v>36798026.12654455</v>
+        <v>36797995.422237217</v>
       </c>
       <c r="D61" s="124">
-        <v>51473753.756532319</v>
+        <v>51473710.806784153</v>
       </c>
       <c r="E61" s="124">
-        <v>58234904.998928867</v>
+        <v>58234856.40766979</v>
       </c>
       <c r="F61" s="124">
-        <v>101004702.21091367</v>
+        <v>101004617.93249589</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16158,23 +16158,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16185,23 +16185,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.852110486652812</v>
+        <v>17.860813463765279</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.257512452376318</v>
+        <v>18.26641188991643</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.888546786156009</v>
+        <v>18.897752027035903</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.105274032868703</v>
+        <v>19.114584301181047</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.005947315701199</v>
+        <v>20.015694056140649</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16212,23 +16212,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.852110486652812</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.663287729246644</v>
+        <v>18.672383808123413</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.03549406695868</v>
+        <v>20.045255125945843</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.539278042599229</v>
+        <v>20.549283238575516</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>22.823863624825908</v>
+        <v>22.834975945824809</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16239,23 +16239,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.852110486652805</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.165547145314974</v>
+        <v>19.174886622369375</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.57102823810159</v>
+        <v>21.581533426928843</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.511805883496976</v>
+        <v>22.522766979286104</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.160950794458984</v>
+        <v>27.174164896090726</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16266,23 +16266,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.852110486652805</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.677268944179826</v>
+        <v>19.686856404944074</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.271840771303591</v>
+        <v>23.283170184939465</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.761923989178271</v>
+        <v>24.773975506826858</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>32.764417314810984</v>
+        <v>32.780346892740212</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16293,23 +16293,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.852110486652805</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.153198612571668</v>
+        <v>20.163016711946696</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>24.99898328595544</v>
+        <v>25.011149684080095</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.119979349321063</v>
+        <v>27.133173595924198</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.484553423869919</v>
+        <v>39.503739623437504</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16319,23 +16319,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.852110486652805</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.573034785802992</v>
+        <v>20.583056340516443</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.66920934716574</v>
+        <v>26.682185147695883</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.477735046784378</v>
+        <v>29.492071877123568</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.24395123258877</v>
+        <v>47.266897686769447</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.24395123258877</v>
+        <v>47.266897686769447</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.761923989178271</v>
+        <v>24.773975506826858</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.271840771303591</v>
+        <v>23.283170184939465</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.677268944179826</v>
+        <v>19.686856404944074</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.852110486652805</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.44</v>
+        <v>-15.38</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16582,7 +16582,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>24.432362487243005</v>
+        <v>24.443726082291231</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16645,7 +16645,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532316.4651289964</v>
+        <v>2532313.7729943665</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16667,7 +16667,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419821.086273348</v>
+        <v>2419819.0671723755</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10082194740824768</v>
+        <v>-0.10082218779585594</v>
       </c>
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
@@ -16802,7 +16802,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.44</v>
+        <v>15.38</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.852110486652816</v>
+        <v>17.860813463765282</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16864,7 +16864,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.271840771303591</v>
+        <v>23.283170184939465</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.677268944179826</v>
+        <v>19.686856404944074</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>24.761923989178271</v>
+        <v>24.773975506826858</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>22.925447210347507</v>
+        <v>22.936608759412231</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.852110486652805</v>
+        <v>17.860813463765275</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.24395123258877</v>
+        <v>47.266897686769447</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>23.887705575274836</v>
+        <v>23.899333440997744</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17227,7 +17227,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>23.884246804264929</v>
+        <v>23.895872993844932</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.22134576154052185</v>
+        <v>0.22134744687986405</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.5446569119681689</v>
+        <v>0.54439264129348874</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.98915843366089862</v>
+        <v>0.98867848828448812</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17362,7 +17362,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.872874635992185</v>
+        <v>10.878167246699016</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17372,7 +17372,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>11.862033069653084</v>
+        <v>11.866845734983505</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.50342518111362788</v>
+        <v>0.50346540985002086</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.44</v>
+        <v>15.38</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18737363316325828</v>
+        <v>0.18912881948046301</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1473096988218372</v>
+        <v>1.1467530175395249</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.823903689395159</v>
+        <v>13.830632778355175</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.971213388216997</v>
+        <v>14.977385795894701</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37326699958521459</v>
+        <v>0.37331366027966395</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.4036336869169019</v>
+        <v>1.4029526357573658</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>18.962830849650423</v>
+        <v>18.97206142435552</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.366464536567324</v>
+        <v>20.375014060112886</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17533,7 +17533,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.14740808938771421</v>
+        <v>0.14746517469140452</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12847152-F0CD-403D-9500-00A39AA669C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16622DC1-6B62-4AC5-BD1B-6BBFA530070E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,27 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2367,7 +2388,7 @@
     <t>2331.HK</t>
   </si>
   <si>
-    <t>CNY</t>
+    <t/>
   </si>
   <si>
     <t>CNS_02</t>
@@ -3056,7 +3077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3757,6 +3778,13 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4069,13 +4097,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4092,7 +4119,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4110,9 +4137,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>2331.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>425</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4124,340 +4150,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>2584797906</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>15.38</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>2584797906</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>39754.191794279999</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>CNY/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1.0742246600000001</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1.0742246600000001</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>CNY/HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>11.866845734983505</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.18912881948046301</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>3205414.6239021346</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="188">
+      <c r="C42" s="188">
         <f>Normalized_FCF!C11</f>
         <v>179409.3</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>96022.498994366397</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-254421</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-158398.50100563362</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4465,405 +4483,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>96022.498994366397</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-254421</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-158398.50100563362</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-806606.35572412517</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2532313.7729943665</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2532313.7729943665</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>2419819.0671723755</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>6.5387552793081283E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.5396140526234639E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>12.570757024469875</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>1936137</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.80464554142145772</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.36794481423679237</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>7.4171010848313429E-2</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>0.60402076709908736</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>18164188</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>14103491.360774152</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8613163437933213</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>561572.19999999995</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4872,591 +4898,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23338563692354369</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>14103491.360774152</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.8613163437933213</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>17.860813463765282</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>561572.19999999995</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>4.5287238180520148</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.23338563692354369</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>17.860813463765282</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>4.5287238180520148</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>47.27 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>20</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>24.77 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.05</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>20</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>23.28 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.495</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>20</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>19.69 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>17.86 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>23.899333440997744</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0.54439264129348874</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>2331.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>0.98867848828448812</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>10.878167246699016</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>11.866845734983505</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.50346540985002086</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>1.1467530175395249</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>13.830632778355175</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>14.977385795894701</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.37331366027966395</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>1.4029526357573658</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>18.97206142435552</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>20.375014060112886</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.14746517469140452</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5480,7 +5603,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6148,7 +6271,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9358,7 +9481,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11986,7 +12109,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12318,7 +12441,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -15053,7 +15176,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15063,7 +15186,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15081,10 +15204,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15099,8 +15222,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15115,8 +15238,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15131,8 +15254,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15158,7 +15281,7 @@
         <v>1.0742246600000001</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>CNY/HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -15202,7 +15325,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15222,7 +15345,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>23.895872993844932</v>
+        <v>23.895872993844897</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15257,11 +15380,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551087.1409645719</v>
+        <v>2551087.1409645714</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15269,7 +15392,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362117.7231153441</v>
+        <v>2362117.7231153436</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15279,11 +15402,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689476.1220307359</v>
+        <v>2689476.122030735</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15291,7 +15414,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305792.2856916459</v>
+        <v>2305792.285691645</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15301,11 +15424,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835372.2986658015</v>
+        <v>2835372.2986657997</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15313,7 +15436,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250809.9459763826</v>
+        <v>2250809.9459763812</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15323,11 +15446,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989182.9141696007</v>
+        <v>2989182.9141695979</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15335,7 +15458,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197138.6773837549</v>
+        <v>2197138.677383753</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15345,11 +15468,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151337.3035943024</v>
+        <v>3151337.3035942987</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15357,7 +15480,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144747.2170119369</v>
+        <v>2144747.2170119346</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15367,11 +15490,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322288.0921570612</v>
+        <v>3322288.092157057</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15379,7 +15502,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093605.0474327963</v>
+        <v>2093605.0474327938</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15389,11 +15512,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502512.4586630315</v>
+        <v>3502512.4586630263</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15401,7 +15524,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043682.3789158405</v>
+        <v>2043682.3789158375</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15411,11 +15534,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692513.4674653625</v>
+        <v>3692513.4674653555</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15423,7 +15546,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994950.1320760339</v>
+        <v>1994950.1320760301</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15433,11 +15556,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892821.4726801147</v>
+        <v>3892821.4726801072</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15445,7 +15568,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947379.9209353926</v>
+        <v>1947379.9209353889</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15455,11 +15578,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103995.5985757094</v>
+        <v>4103995.5985757005</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15467,7 +15590,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900944.0363884745</v>
+        <v>1900944.0363884703</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15477,11 +15600,11 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326625.3002691502</v>
+        <v>4326625.300269139</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
@@ -15489,7 +15612,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855615.4300621408</v>
+        <v>1855615.4300621361</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15499,11 +15622,11 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561332.0090854326</v>
+        <v>4561332.0090854196</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
@@ -15511,7 +15634,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811367.6985601869</v>
+        <v>1811367.6985601815</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15521,11 +15644,11 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808770.8671728661</v>
+        <v>4808770.8671728531</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
@@ -15533,7 +15656,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768175.0680836663</v>
+        <v>1768175.0680836616</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15543,11 +15666,11 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069632.556216184</v>
+        <v>5069632.5562161691</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
@@ -15555,7 +15678,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1726012.3794179468</v>
+        <v>1726012.3794179417</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15565,11 +15688,11 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344645.2253519557</v>
+        <v>5344645.225351939</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
@@ -15577,7 +15700,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684855.0732777535</v>
+        <v>1684855.0732777482</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15587,11 +15710,11 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634576.5236677546</v>
+        <v>5634576.523667735</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
@@ -15599,7 +15722,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644679.1760016668</v>
+        <v>1644679.1760016612</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15609,11 +15732,11 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940235.7429584283</v>
+        <v>5940235.742958406</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
@@ -15621,7 +15744,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605461.2855877359</v>
+        <v>1605461.2855877299</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15631,11 +15754,11 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262476.0767206065</v>
+        <v>6262476.0767205814</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
@@ -15643,7 +15766,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567178.5580620817</v>
+        <v>1567178.5580620754</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15653,11 +15776,11 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602197.0016910136</v>
+        <v>6602197.0016909847</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
@@ -15665,7 +15788,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529808.6941725432</v>
+        <v>1529808.6941725365</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15675,11 +15798,11 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960346.7885762397</v>
+        <v>6960346.7885762081</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
@@ -15687,7 +15810,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493329.926399614</v>
+        <v>1493329.926399607</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -15917,7 +16040,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888589.262057148</v>
+        <v>31888589.26205714</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15929,7 +16052,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841639.6628186069</v>
+        <v>6841639.6628186051</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15940,7 +16063,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44769290.317371547</v>
+        <v>44769290.317371465</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15961,7 +16084,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44769290.317371547</v>
+        <v>44769290.317371465</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16626,11 +16749,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16651,8 +16774,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16673,8 +16796,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16684,8 +16807,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16698,8 +16821,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16717,8 +16840,8 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16735,8 +16858,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16753,8 +16876,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.10082218779585594</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16780,21 +16903,21 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16808,8 +16931,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16823,8 +16946,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16844,8 +16967,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16855,8 +16978,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16870,8 +16993,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16881,8 +17004,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16902,8 +17025,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16913,8 +17036,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16928,8 +17051,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16939,8 +17062,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16960,8 +17083,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16971,8 +17094,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16986,8 +17109,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16998,8 +17121,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17061,8 +17184,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17072,8 +17195,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17087,8 +17210,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17098,8 +17221,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17119,8 +17242,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17130,8 +17253,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17145,8 +17268,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17156,8 +17279,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17175,7 +17298,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17214,7 +17337,7 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>5.4247061515052243E-2</v>
+        <v>5.4247061515052201E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -17227,7 +17350,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>23.895872993844932</v>
+        <v>23.895872993844897</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17340,7 +17463,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17429,7 +17552,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17487,7 +17610,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16622DC1-6B62-4AC5-BD1B-6BBFA530070E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141E34AE-E923-430F-9567-0A51463D36E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4267,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4373,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4673,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4798,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4954,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4999,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5446,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,17 +5542,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5569,6 +5558,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8688,7 +8688,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>0</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141E34AE-E923-430F-9567-0A51463D36E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC60D79-8F8B-43D6-8BD0-A664957E32F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>15.38</v>
+        <v>15.62</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4229,8 +4229,7 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>39754.191794279999</v>
+        <v>1.08195318</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4267,13 +4266,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4322,7 +4321,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>11.866845734983505</v>
+        <v>9.5746666753051599</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4352,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18912881948046301</v>
+        <v>0.18283075466126464</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4373,22 +4372,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4399,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4425,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4460,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4482,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4552,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4574,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4596,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4646,7 +4645,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.5387552793081283E-2</v>
+        <v>6.438287848640141E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4654,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5396140526234639E-2</v>
+        <v>3.4852281772950626E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4673,22 +4672,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4745,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4798,13 +4797,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4816,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4954,13 +4953,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4999,13 +4998,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5148,13 +5147,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5166,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5204,7 +5203,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5239,7 +5238,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5249,7 +5248,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.98867848828448812</v>
+        <v>0.86499705395029525</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5258,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>10.878167246699016</v>
+        <v>8.7096696213548643</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5267,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>11.866845734983505</v>
+        <v>9.5746666753051599</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5293,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.50346540985002086</v>
+        <v>0.59937515835146904</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5446,13 +5445,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5488,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5502,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,6 +5541,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5558,17 +5568,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13124,12 +13123,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5396140526234639E-2</v>
+        <v>3.4852281772950626E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5396140526234639E-2</v>
+        <v>3.4852281772950626E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14323,50 +14322,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5387552793081283E-2</v>
+        <v>6.438287848640141E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.8427347633805882E-2</v>
+        <v>6.7375967132390177E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.0981589677587655E-2</v>
+        <v>6.0044612627483882E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8051115352579081E-2</v>
+        <v>7.6851866461118218E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.4122393090877332E-2</v>
+        <v>9.2676210354525834E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7814655830766361E-2</v>
+        <v>3.7233636791113099E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7258533293628091E-2</v>
+        <v>3.6686059030473755E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6024661082695211E-2</v>
+        <v>1.5778443498838179E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2253759983676275E-2</v>
+        <v>1.2065481981366269E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2534630059215496E-3</v>
+        <v>6.1573790672902334E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2515175759754392E-4</v>
+        <v>3.2015582790334351E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14380,43 +14379,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5788687029313753E-2</v>
+        <v>7.4624200160745557E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0166690760357845E-2</v>
+        <v>7.8934936228828648E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10222245294355883</v>
+        <v>0.10065181346171158</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10089220328652496</v>
+        <v>9.9342002979945818E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2724651749664923E-2</v>
+        <v>4.2068191031360211E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7710312606976534E-2</v>
+        <v>3.7130896792272661E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7992140393680828E-2</v>
+        <v>1.7715692653957175E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2958507688090459E-2</v>
+        <v>1.2759401295955906E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7630065368373152E-2</v>
+        <v>1.7359180881279069E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5496479042711663E-3</v>
+        <v>1.5258376931940165E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16685,7 +16684,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.38</v>
+        <v>-15.62</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16925,7 +16924,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.38</v>
+        <v>15.62</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17464,7 +17463,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17473,7 +17472,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.98867848828448812</v>
+        <v>0.86499705395029525</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17485,7 +17484,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>10.878167246699016</v>
+        <v>8.7096696213548643</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17495,7 +17494,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>11.866845734983505</v>
+        <v>9.5746666753051599</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17506,7 +17505,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.50346540985002086</v>
+        <v>0.59937515835146904</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17523,7 +17522,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.38</v>
+        <v>15.62</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17536,7 +17535,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18912881948046301</v>
+        <v>0.18283075466126464</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC60D79-8F8B-43D6-8BD0-A664957E32F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A62F2E5-6366-47F4-A8BF-D9E8F34B30A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4229,7 +4229,8 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <v>1.08195318</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>40374.543291720001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4266,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4372,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4399,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4425,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4460,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4482,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4552,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4574,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4596,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4672,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4745,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4797,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4816,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4953,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4998,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5147,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5166,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5445,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5488,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5502,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5541,17 +5542,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5568,6 +5558,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A62F2E5-6366-47F4-A8BF-D9E8F34B30A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AF99A5-57E5-4117-9686-DBAA84F13A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>15.62</v>
+        <v>15.4</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>40374.543291720001</v>
+        <v>39805.887752399998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0742246600000001</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>9.5746666753051599</v>
+        <v>9.6381682721946955</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18283075466126464</v>
+        <v>0.19139067803306431</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>96022.498994366397</v>
+        <v>95978.140040413171</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158398.50100563362</v>
+        <v>-158442.85995958681</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806606.35572412517</v>
+        <v>-806595.26598563686</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532313.7729943665</v>
+        <v>2532269.4140404132</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419819.0671723755</v>
+        <v>2419785.7979569105</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.438287848640141E-2</v>
+        <v>6.5828278957727346E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.4852281772950626E-2</v>
+        <v>3.5067414897236006E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.570757024469875</v>
+        <v>12.671943699362515</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.80464554142145772</v>
+        <v>0.8111335831119556</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14103491.360774152</v>
+        <v>14105367.257122653</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.8613163437933213</v>
+        <v>5.9093633789240911</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23338563692354369</v>
+        <v>0.23526747888298391</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>4.5287238180520148</v>
+        <v>4.565239957673402</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>47.27 HKD</v>
+        <v>47.65 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>24.77 HKD</v>
+        <v>24.97 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.28 HKD</v>
+        <v>23.47 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.69 HKD</v>
+        <v>19.85 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>17.86 HKD</v>
+        <v>18.01 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>23.899333440997744</v>
+        <v>24.092567233042224</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.86499705395029525</v>
+        <v>0.85807817268950937</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>8.7096696213548643</v>
+        <v>8.7800900995051858</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>9.5746666753051599</v>
+        <v>9.6381682721946955</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.59937515835146904</v>
+        <v>0.59995262526542881</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1467530175395249</v>
+        <v>1.1375804453006144</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>13.830632778355175</v>
+        <v>13.942457889492028</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>14.977385795894701</v>
+        <v>15.080038334792642</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37331366027966395</v>
+        <v>0.37407922580741715</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>1.4029526357573658</v>
+        <v>1.3917307909464707</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>18.97206142435552</v>
+        <v>19.125456638535017</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>20.375014060112886</v>
+        <v>20.517187429481488</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14746517469140452</v>
+        <v>0.14840177756802986</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7481,11 +7481,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>1815.2739999999999</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>1815.2739999999999</v>
       </c>
       <c r="E62" s="183">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8980,11 +8980,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.848517934682489</v>
+        <v>10.935992024846454</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.5287238180520148</v>
+        <v>4.565239957673402</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14103491.360774152</v>
+        <v>14105367.257122653</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9242,11 +9242,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2212791.5799381016</v>
+        <v>-2211853.6317638513</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2030348.3196129238</v>
+        <v>-2029410.3714386735</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9258,11 +9258,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2087206787491969</v>
+        <v>8.2122016299581713</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9463407950922011</v>
+        <v>8.9504755941121896</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9275,7 +9275,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4060696.6392258476</v>
+        <v>4058820.7428773469</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9390,11 +9390,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2079846.11053842</v>
+        <v>-2096616.3871140599</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.80464554142145761</v>
+        <v>-0.8111335831119556</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9407,11 +9407,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15150318.211840551</v>
+        <v>15274510.087636078</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.8613163437933204</v>
+        <v>5.909363378924092</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9424,11 +9424,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>603254.70561045199</v>
+        <v>608118.88676663593</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23338563692354367</v>
+        <v>0.23526747888298385</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9441,11 +9441,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13673726.806912584</v>
+        <v>13786012.587288655</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.2900564392954061</v>
+        <v>5.3334972746951204</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -10025,24 +10025,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158398.50100563362</v>
+        <v>-158442.85995958681</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158398.50100563362</v>
+        <v>-158442.85995958681</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69544.159579479499</v>
+        <v>-69595.854220198933</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20464.656644596791</v>
+        <v>-20510.897568674889</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80020.827456875428</v>
+        <v>-80035.812268334019</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -10080,24 +10080,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226425.4228965007</v>
+        <v>3226381.0639425474</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3629004.7729943665</v>
+        <v>3628960.4140404132</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3326025.1144205206</v>
+        <v>3325973.4197798013</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239792.7683554031</v>
+        <v>4239746.5274313251</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800574.926543124</v>
+        <v>4800559.9417316653</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806606.35572412517</v>
+        <v>-806595.26598563686</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10247,26 +10247,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419819.0671723755</v>
+        <v>2419785.7979569105</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532313.7729943665</v>
+        <v>2532269.4140404132</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256766.1144205206</v>
+        <v>2256714.4197798013</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888463.7683554031</v>
+        <v>2888417.5274313251</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483218.926543124</v>
+        <v>3483203.9417316653</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10355,26 +10355,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419819.0671723755</v>
+        <v>2419785.7979569105</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532313.7729943665</v>
+        <v>2532269.4140404132</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256766.1144205206</v>
+        <v>2256714.4197798013</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888463.7683554031</v>
+        <v>2888417.5274313251</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483218.926543124</v>
+        <v>3483203.9417316653</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11216,19 +11216,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.3023528272520794</v>
+        <v>0.30235652494120507</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32164245078606191</v>
+        <v>0.32164745271142298</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31886290875583534</v>
+        <v>0.31886638794588973</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2744736019131529</v>
+        <v>0.27447445885816629</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11354,24 +11354,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>96022.498994366397</v>
+        <v>95978.140040413171</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>96022.498994366397</v>
+        <v>95978.140040413171</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111901.8404205205</v>
+        <v>111850.14577980107</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100096.34335540321</v>
+        <v>100050.10243132511</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32437.172543124572</v>
+        <v>32422.187731665977</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11466,24 +11466,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158398.50100563362</v>
+        <v>-158442.85995958681</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158398.50100563362</v>
+        <v>-158442.85995958681</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69544.159579479499</v>
+        <v>-69595.854220198933</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20464.656644596791</v>
+        <v>-20510.897568674889</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80020.827456875428</v>
+        <v>-80035.812268334019</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12553,26 +12553,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.054421662835264E-3</v>
+        <v>6.0561171827426489E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5237994490876319E-3</v>
+        <v>5.5253463700739615E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5198536970546504E-3</v>
+        <v>2.5217267936931383E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9309975147819924E-4</v>
+        <v>7.9489180037651999E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5450926495587854E-3</v>
+        <v>3.5457565085395674E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12610,26 +12610,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.1233227577905693</v>
+        <v>0.1233210622706619</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655356230353287</v>
+        <v>0.12655201538254654</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12051474533229084</v>
+        <v>0.12051287223565235</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16431150784978091</v>
+        <v>0.16430971580088258</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267566740566113</v>
+        <v>0.21267500354668034</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0830689447642324E-2</v>
+        <v>3.0830265567665476E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12782,26 +12782,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2492068342926975E-2</v>
+        <v>9.2490796702996425E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8308874991726127E-2</v>
+        <v>8.8307328070739793E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.1771358963811491E-2</v>
+        <v>8.1769485867173003E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11194128182166668</v>
+        <v>0.11193948977276837</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431399806440138</v>
+        <v>0.15431333420542059</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12889,26 +12889,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2492068342926975E-2</v>
+        <v>9.2490796702996425E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8308874991726127E-2</v>
+        <v>8.8307328070739793E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.1771358963811491E-2</v>
+        <v>8.1769485867173003E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11194128182166668</v>
+        <v>0.11193948977276837</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431399806440138</v>
+        <v>0.15431333420542059</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12958,12 +12958,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1407144.9592572188</v>
+        <v>1395889.5811662162</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1407144.9592572188</v>
+        <v>1395889.5811662162</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.5815083360350185</v>
+        <v>0.57686493670010075</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55567559370548403</v>
+        <v>0.551240548666177</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13124,12 +13124,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.4852281772950626E-2</v>
+        <v>3.5067414897236006E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.4852281772950626E-2</v>
+        <v>3.5067414897236006E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13261,26 +13261,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093381664684043</v>
+        <v>-0.11093517265724095</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1093617200973087E-2</v>
+        <v>9.1097238618542908E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21552177284582918</v>
+        <v>-0.21552540977140411</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11681562453844208</v>
+        <v>-0.1168225001056945</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633484014676914</v>
+        <v>1.46334071221965</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13876,15 +13876,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.0772803925247438</v>
+        <v>2.0773279768635611</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3549084613335061</v>
+        <v>1.3549301521793407</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733634427268071</v>
+        <v>1.8733715019729644</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13980,24 +13980,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.1233227577905693</v>
+        <v>0.1233210622706619</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655356230353287</v>
+        <v>0.12655201538254654</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12051474533229084</v>
+        <v>0.12051287223565235</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16431150784978091</v>
+        <v>0.16430971580088258</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267566740566113</v>
+        <v>0.21267500354668034</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14266,50 +14266,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0056605619575902</v>
+        <v>1.0137554959490014</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0524126066079345</v>
+        <v>1.0608798670834827</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.93789684924129824</v>
+        <v>0.94543766963619214</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2004261541226664</v>
+        <v>1.210086093364646</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4476024057376935</v>
+        <v>1.4592684784013181</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58158940667718662</v>
+        <v>0.58627889555524304</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57303624205600001</v>
+        <v>0.57765676480451078</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24645928745185233</v>
+        <v>0.24844654525629281</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18846282854894111</v>
+        <v>0.18998244759333999</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.6178261031073436E-2</v>
+        <v>9.695376842553044E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0008340318502256E-3</v>
+        <v>5.041156904488764E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14323,50 +14323,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.438287848640141E-2</v>
+        <v>6.5828278957727346E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.7375967132390177E-2</v>
+        <v>6.888830305736901E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.0044612627483882E-2</v>
+        <v>6.1392056469882605E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.6851866461118218E-2</v>
+        <v>7.8577019049652336E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.2676210354525834E-2</v>
+        <v>9.4757693402682988E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.7233636791113099E-2</v>
+        <v>3.8070058152937861E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.6686059030473755E-2</v>
+        <v>3.7510179532760438E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5778443498838179E-2</v>
+        <v>1.6132892549109924E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2065481981366269E-2</v>
+        <v>1.2336522570996102E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.1573790672902334E-3</v>
+        <v>6.295699248411067E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2015582790334351E-4</v>
+        <v>3.2734785094082884E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14380,43 +14380,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.4624200160745557E-2</v>
+        <v>7.5690260163041923E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8934936228828648E-2</v>
+        <v>8.0062578174954782E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10065181346171158</v>
+        <v>0.10208969651116459</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9342002979945818E-2</v>
+        <v>0.10076117445108791</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2068191031360211E-2</v>
+        <v>4.2669165188951072E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7130896792272661E-2</v>
+        <v>3.7661338175019418E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7715692653957175E-2</v>
+        <v>1.7968773977585135E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2759401295955906E-2</v>
+        <v>1.2941678457326704E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7359180881279069E-2</v>
+        <v>1.7607169179583056E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5258376931940165E-3</v>
+        <v>1.5476353745253596E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419819.0671723755</v>
+        <v>2419785.7979569105</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30247738.339654692</v>
+        <v>30247322.47446138</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14103491.360774152</v>
+        <v>14105367.257122653</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42976664.900428846</v>
+        <v>42978124.931584038</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0742246600000001</v>
+        <v>1.0828863799999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>23.895872993844897</v>
+        <v>24.089078931469764</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551087.1409645714</v>
+        <v>2551052.0669919285</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362117.7231153436</v>
+        <v>2362085.2472147485</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689476.122030735</v>
+        <v>2689439.1453981404</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305792.285691645</v>
+        <v>2305760.5841890778</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835372.2986657997</v>
+        <v>2835333.3161595426</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250809.9459763812</v>
+        <v>2250779.0004060785</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989182.9141695979</v>
+        <v>2989141.8169769258</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197138.677383753</v>
+        <v>2197108.4697202728</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151337.3035942987</v>
+        <v>3151293.9769996875</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144747.2170119346</v>
+        <v>2144717.7296596575</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322288.092157057</v>
+        <v>3322242.4152220027</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093605.0474327938</v>
+        <v>2093576.2632156734</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502512.4586630263</v>
+        <v>3502464.3038884662</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043682.3789158375</v>
+        <v>2043654.2810673956</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692513.4674653555</v>
+        <v>3692462.7004357777</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994950.1320760301</v>
+        <v>1994922.7042295907</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892821.4726801072</v>
+        <v>3892767.9516883525</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947379.9209353889</v>
+        <v>1947353.1471145439</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103995.5985757005</v>
+        <v>4103939.1742274137</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900944.0363884703</v>
+        <v>1900917.9009977744</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326625.300269139</v>
+        <v>4326565.8150657602</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855615.4300621361</v>
+        <v>1855589.9178780227</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561332.0090854196</v>
+        <v>4561269.2969845543</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811367.6985601815</v>
+        <v>1811342.7947220944</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808770.8671728531</v>
+        <v>4808704.753124794</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768175.0680836616</v>
+        <v>1768150.7580853985</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069632.5562161691</v>
+        <v>5069562.8556752782</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1726012.3794179417</v>
+        <v>1725988.6490992066</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344645.225351939</v>
+        <v>5344571.743761519</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684855.0732777482</v>
+        <v>1684831.9088159006</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634576.523667735</v>
+        <v>5634499.0559169585</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644679.1760016612</v>
+        <v>1644656.5639036661</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940235.742958406</v>
+        <v>5940154.0728097875</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605461.2855877299</v>
+        <v>1605439.2126822984</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262476.0767205814</v>
+        <v>6262389.9762063874</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567178.5580620754</v>
+        <v>1567157.011491992</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602197.0016909847</v>
+        <v>6602106.2304769009</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529808.6941725365</v>
+        <v>1529787.6613871697</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15798,7 +15798,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960346.7885762081</v>
+        <v>6960251.0932904892</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493329.926399607</v>
+        <v>1493309.395147599</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888589.26205714</v>
+        <v>31888150.837399106</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841639.6628186051</v>
+        <v>6841545.5995941423</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44769290.317371465</v>
+        <v>44768674.800622314</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16084,7 +16084,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44769290.317371465</v>
+        <v>44768674.800622314</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16114,19 +16114,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30247738.339654684</v>
+        <v>30247322.474461377</v>
       </c>
       <c r="C56" s="124">
-        <v>31223688.7172902</v>
+        <v>31223259.434108812</v>
       </c>
       <c r="D56" s="124">
-        <v>32742818.490758788</v>
+        <v>32742368.321612637</v>
       </c>
       <c r="E56" s="124">
-        <v>33264560.01190725</v>
+        <v>33264102.669525992</v>
       </c>
       <c r="F56" s="124">
-        <v>35432809.070438221</v>
+        <v>35432321.917586386</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16135,19 +16135,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30247738.33965468</v>
+        <v>30247322.474461369</v>
       </c>
       <c r="C57" s="124">
-        <v>32200537.790999055</v>
+        <v>32200095.077473737</v>
       </c>
       <c r="D57" s="124">
-        <v>35503938.876126707</v>
+        <v>35503450.74533695</v>
       </c>
       <c r="E57" s="124">
-        <v>36716730.630591087</v>
+        <v>36716225.825566977</v>
       </c>
       <c r="F57" s="124">
-        <v>42216561.293068573</v>
+        <v>42215980.872865714</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16156,19 +16156,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30247738.339654677</v>
+        <v>30247322.474461362</v>
       </c>
       <c r="C58" s="124">
-        <v>33409659.374581091</v>
+        <v>33409200.037281282</v>
       </c>
       <c r="D58" s="124">
-        <v>39200529.620388806</v>
+        <v>39199990.66651246</v>
       </c>
       <c r="E58" s="124">
-        <v>41465324.50527814</v>
+        <v>41464754.413557634</v>
       </c>
       <c r="F58" s="124">
-        <v>52657511.803724028</v>
+        <v>52656787.834676169</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16177,19 +16177,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30247738.339654677</v>
+        <v>30247322.474461362</v>
       </c>
       <c r="C59" s="124">
-        <v>34641560.364392996</v>
+        <v>34641084.090132892</v>
       </c>
       <c r="D59" s="124">
-        <v>43295005.65753217</v>
+        <v>43294410.410188548</v>
       </c>
       <c r="E59" s="124">
-        <v>46882179.381758712</v>
+        <v>46881534.815663472</v>
       </c>
       <c r="F59" s="124">
-        <v>66147099.247745737</v>
+        <v>66146189.815248445</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16198,19 +16198,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30247738.339654673</v>
+        <v>30247322.474461358</v>
       </c>
       <c r="C60" s="124">
-        <v>35787296.643115826</v>
+        <v>35786804.616542816</v>
       </c>
       <c r="D60" s="124">
-        <v>47452867.562312521</v>
+        <v>47452215.150032289</v>
       </c>
       <c r="E60" s="124">
-        <v>52558878.593391038</v>
+        <v>52558155.980415449</v>
       </c>
       <c r="F60" s="124">
-        <v>82324917.630282193</v>
+        <v>82323785.774822459</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16219,19 +16219,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30247738.339654677</v>
+        <v>30247322.474461354</v>
       </c>
       <c r="C61" s="124">
-        <v>36797995.422237217</v>
+        <v>36797489.499932945</v>
       </c>
       <c r="D61" s="124">
-        <v>51473710.806784153</v>
+        <v>51473003.113387227</v>
       </c>
       <c r="E61" s="124">
-        <v>58234856.40766979</v>
+        <v>58234055.757732093</v>
       </c>
       <c r="F61" s="124">
-        <v>101004617.93249589</v>
+        <v>101003229.2566058</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16281,23 +16281,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16308,23 +16308,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>17.860813463765279</v>
+        <v>18.005440974057635</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.26641188991643</v>
+        <v>18.414304212025929</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>18.897752027035903</v>
+        <v>19.050726239526146</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.114584301181047</v>
+        <v>19.269303876881118</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.015694056140649</v>
+        <v>20.177666997699287</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16335,23 +16335,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>17.860813463765275</v>
+        <v>18.005440974057631</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.672383808123413</v>
+        <v>18.823543948425808</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.045255125945843</v>
+        <v>20.207466015493935</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.549283238575516</v>
+        <v>20.715551236909501</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>22.834975945824809</v>
+        <v>23.019642330542588</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16362,23 +16362,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>17.860813463765275</v>
+        <v>18.005440974057624</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.174886622369375</v>
+        <v>19.330091593766578</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.581533426928843</v>
+        <v>21.756110388996159</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.522766979286104</v>
+        <v>22.704920278504396</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.174164896090726</v>
+        <v>27.393759018314977</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16389,23 +16389,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>17.860813463765275</v>
+        <v>18.005440974057624</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.686856404944074</v>
+        <v>19.846182410567252</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.283170184939465</v>
+        <v>23.471444250934816</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.773975506826858</v>
+        <v>24.974249616506164</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>32.780346892740212</v>
+        <v>33.045067248331293</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16416,23 +16416,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>17.860813463765275</v>
+        <v>18.005440974057624</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.163016711946696</v>
+        <v>20.326175508076258</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.011149684080095</v>
+        <v>25.213332896474526</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.133173595924198</v>
+        <v>27.352437764005245</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.503739623437504</v>
+        <v>39.822579054999302</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16442,23 +16442,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>17.860813463765275</v>
+        <v>18.005440974057624</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.583056340516443</v>
+        <v>20.749596191045136</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.682185147695883</v>
+        <v>26.897819142876266</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.492071877123568</v>
+        <v>29.73032369034166</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.266897686769447</v>
+        <v>47.648225650212439</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.266897686769447</v>
+        <v>47.648225650212439</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.773975506826858</v>
+        <v>24.974249616506164</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16538,7 +16538,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.283170184939465</v>
+        <v>23.471444250934816</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.686856404944074</v>
+        <v>19.846182410567252</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>17.860813463765275</v>
+        <v>18.005440974057624</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16685,7 +16685,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.62</v>
+        <v>-15.4</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>24.443726082291231</v>
+        <v>24.632605422459658</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532313.7729943665</v>
+        <v>2532269.4140404132</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419819.0671723755</v>
+        <v>2419785.7979569105</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10082218779585594</v>
+        <v>-0.10082614875724705</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.62</v>
+        <v>15.4</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>17.860813463765282</v>
+        <v>18.005440974057638</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.283170184939465</v>
+        <v>23.471444250934816</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.686856404944074</v>
+        <v>19.846182410567252</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>24.773975506826858</v>
+        <v>24.974249616506164</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>22.936608759412231</v>
+        <v>23.12209322425414</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>17.860813463765275</v>
+        <v>18.005440974057624</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.266897686769447</v>
+        <v>47.648225650212439</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>23.899333440997744</v>
+        <v>24.092567233042224</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>23.895872993844897</v>
+        <v>24.089078931469764</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.22134744687986405</v>
+        <v>0.22137521597866044</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.54439264129348874</v>
+        <v>0.54003818941743453</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.86499705395029525</v>
+        <v>0.85807817268950937</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7096696213548643</v>
+        <v>8.7800900995051858</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.5746666753051599</v>
+        <v>9.6381682721946955</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.59937515835146904</v>
+        <v>0.59995262526542881</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.62</v>
+        <v>15.4</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18283075466126464</v>
+        <v>0.19139067803306431</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1467530175395249</v>
+        <v>1.1375804453006144</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.830632778355175</v>
+        <v>13.942457889492028</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.977385795894701</v>
+        <v>15.080038334792642</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37331366027966395</v>
+        <v>0.37407922580741715</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.4029526357573658</v>
+        <v>1.3917307909464707</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>18.97206142435552</v>
+        <v>19.125456638535017</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.375014060112886</v>
+        <v>20.517187429481488</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.14746517469140452</v>
+        <v>0.14840177756802986</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AF99A5-57E5-4117-9686-DBAA84F13A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F708BFF-BB16-4622-88B3-D040606167C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4267,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>9.6381682721946955</v>
+        <v>9.6376594075295827</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19139067803306431</v>
+        <v>0.19136836795872036</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4373,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>95978.140040413171</v>
+        <v>95978.492381801712</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158442.85995958681</v>
+        <v>-158442.50761819829</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806595.26598563686</v>
+        <v>-806595.35407098406</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4575,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532269.4140404132</v>
+        <v>2532269.766381802</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419785.7979569105</v>
+        <v>2419786.0622129524</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.5828278957727346E-2</v>
+        <v>6.58240703842322E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5067414897236006E-2</v>
+        <v>3.5069660821668069E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4673,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.671943699362515</v>
+        <v>12.671133548964699</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4798,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.8111335831119556</v>
+        <v>0.8110816366519874</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14105367.257122653</v>
+        <v>14105352.356953345</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9093633789240911</v>
+        <v>5.9089786906766859</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23526747888298391</v>
+        <v>0.23525241192862759</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4954,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>4.565239957673402</v>
+        <v>4.564947591459446</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -4999,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.85 HKD</v>
+        <v>19.84 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>18.01 HKD</v>
+        <v>18 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>24.092567233042224</v>
+        <v>24.091020108051087</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.85807817268950937</v>
+        <v>0.85813312908530615</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>8.7800900995051858</v>
+        <v>8.7795262784442762</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>9.6381682721946955</v>
+        <v>9.6376594075295827</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.59995262526542881</v>
+        <v>0.59994805681521424</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1375804453006144</v>
+        <v>1.1376533026732782</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>13.942457889492028</v>
+        <v>13.941562562529564</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>15.080038334792642</v>
+        <v>15.079215865202842</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37407922580741715</v>
+        <v>0.37407316927341527</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>1.3917307909464707</v>
+        <v>1.3918199256088173</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>19.125456638535017</v>
+        <v>19.124228480836162</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>20.517187429481488</v>
+        <v>20.51604840644498</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14840177756802986</v>
+        <v>0.14839436792514116</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5446,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,6 +5542,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5558,17 +5569,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8980,11 +8980,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.935992024846454</v>
+        <v>10.93529166416141</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.565239957673402</v>
+        <v>4.564947591459446</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14105367.257122653</v>
+        <v>14105352.356953345</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9242,11 +9242,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2211853.6317638513</v>
+        <v>-2211861.081848505</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2029410.3714386735</v>
+        <v>-2029417.8215233271</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9258,11 +9258,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2122016299581713</v>
+        <v>8.2121739692710527</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9504755941121896</v>
+        <v>8.9504427365112758</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9275,7 +9275,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4058820.7428773469</v>
+        <v>4058835.6430466543</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9390,11 +9390,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2096616.3871140599</v>
+        <v>-2096482.1160131099</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.8111335831119556</v>
+        <v>-0.8110816366519874</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9407,11 +9407,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15274510.087636078</v>
+        <v>15273515.746259721</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.909363378924092</v>
+        <v>5.9089786906766868</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9424,11 +9424,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>608118.88676663593</v>
+        <v>608079.94173456589</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23526747888298385</v>
+        <v>0.23525241192862753</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9441,11 +9441,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13786012.587288655</v>
+        <v>13785113.571981177</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.3334972746951204</v>
+        <v>5.3331494659533263</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -10025,24 +10025,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158442.85995958681</v>
+        <v>-158442.50761819829</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158442.85995958681</v>
+        <v>-158442.50761819829</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69595.854220198933</v>
+        <v>-69595.443611745213</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20510.897568674889</v>
+        <v>-20510.530278873281</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80035.812268334019</v>
+        <v>-80035.693244578812</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -10080,24 +10080,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226381.0639425474</v>
+        <v>3226381.4162839362</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3628960.4140404132</v>
+        <v>3628960.766381802</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3325973.4197798013</v>
+        <v>3325973.830388255</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239746.5274313251</v>
+        <v>4239746.8947211262</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800559.9417316653</v>
+        <v>4800560.0607554205</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806595.26598563686</v>
+        <v>-806595.35407098406</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10247,26 +10247,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419785.7979569105</v>
+        <v>2419786.0622129524</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532269.4140404132</v>
+        <v>2532269.766381802</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256714.4197798013</v>
+        <v>2256714.830388255</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888417.5274313251</v>
+        <v>2888417.8947211262</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483203.9417316653</v>
+        <v>3483204.0607554205</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10355,26 +10355,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419785.7979569105</v>
+        <v>2419786.0622129524</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532269.4140404132</v>
+        <v>2532269.766381802</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256714.4197798013</v>
+        <v>2256714.830388255</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888417.5274313251</v>
+        <v>2888417.8947211262</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483203.9417316653</v>
+        <v>3483204.0607554205</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11216,19 +11216,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30235652494120507</v>
+        <v>0.30235649557025263</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32164745271142298</v>
+        <v>0.32164741298071792</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31886638794588973</v>
+        <v>0.31886636031052384</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447445885816629</v>
+        <v>0.27447445205146542</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11354,24 +11354,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>95978.140040413171</v>
+        <v>95978.492381801712</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>95978.140040413171</v>
+        <v>95978.492381801712</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111850.14577980107</v>
+        <v>111850.55638825479</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100050.10243132511</v>
+        <v>100050.46972112672</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32422.187731665977</v>
+        <v>32422.306755421181</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11466,24 +11466,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158442.85995958681</v>
+        <v>-158442.50761819829</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158442.85995958681</v>
+        <v>-158442.50761819829</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69595.854220198933</v>
+        <v>-69595.443611745213</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20510.897568674889</v>
+        <v>-20510.530278873281</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80035.812268334019</v>
+        <v>-80035.693244578812</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12553,26 +12553,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0561171827426489E-3</v>
+        <v>6.0561037152961645E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5253463700739615E-3</v>
+        <v>5.5253340829427358E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5217267936931383E-3</v>
+        <v>2.5217119157618152E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9489180037651999E-4</v>
+        <v>7.9487756620414004E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5457565085395674E-3</v>
+        <v>3.5457512355343622E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12610,26 +12610,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.1233210622706619</v>
+        <v>0.1233210757381084</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655201538254654</v>
+        <v>0.1265520276696778</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12051287223565235</v>
+        <v>0.12051288711358367</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16430971580088258</v>
+        <v>0.16430973003505495</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267500354668034</v>
+        <v>0.21267500881968554</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0830265567665476E-2</v>
+        <v>3.0830268934527099E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12782,26 +12782,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2490796702996425E-2</v>
+        <v>9.2490806803581307E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8307328070739793E-2</v>
+        <v>8.8307340357871036E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.1769485867173003E-2</v>
+        <v>8.176950074510432E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11193948977276837</v>
+        <v>0.11193950400694072</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431333420542059</v>
+        <v>0.15431333947842579</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12889,26 +12889,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2490796702996425E-2</v>
+        <v>9.2490806803581307E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8307328070739793E-2</v>
+        <v>8.8307340357871036E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.1769485867173003E-2</v>
+        <v>8.176950074510432E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11193948977276837</v>
+        <v>0.11193950400694072</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431333420542059</v>
+        <v>0.15431333947842579</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12958,12 +12958,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1395889.5811662162</v>
+        <v>1395978.982182059</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1395889.5811662162</v>
+        <v>1395978.982182059</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13069,12 +13069,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.57686493670010075</v>
+        <v>0.57690181953746877</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.551240548666177</v>
+        <v>0.55127577666288052</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13124,12 +13124,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5067414897236006E-2</v>
+        <v>3.5069660821668069E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5067414897236006E-2</v>
+        <v>3.5069660821668069E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13261,26 +13261,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093517265724095</v>
+        <v>-0.1109351618863742</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1097238618542908E-2</v>
+        <v>9.1097209853325367E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21552540977140411</v>
+        <v>-0.21552538088313777</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.1168225001056945</v>
+        <v>-0.11682244549317111</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.46334071221965</v>
+        <v>1.4633407732950379</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13876,15 +13876,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.0773279768635611</v>
+        <v>2.077327598894481</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3549301521793407</v>
+        <v>1.3549299798870877</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733715019729644</v>
+        <v>1.873371437958423</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13980,24 +13980,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.1233210622706619</v>
+        <v>0.1233210757381084</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655201538254654</v>
+        <v>0.1265520276696778</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12051287223565235</v>
+        <v>0.12051288711358367</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16430971580088258</v>
+        <v>0.16430973003505495</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267500354668034</v>
+        <v>0.21267500881968554</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14266,50 +14266,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0137554959490014</v>
+        <v>1.013690683917176</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0608798670834827</v>
+        <v>1.0608120740222917</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.94543766963619214</v>
+        <v>0.94537729411096327</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.210086093364646</v>
+        <v>1.2100087511293358</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4592684784013181</v>
+        <v>1.4591750740729377</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58627889555524304</v>
+        <v>0.58624134919566395</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57765676480451078</v>
+        <v>0.57761977062176073</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24844654525629281</v>
+        <v>0.2484306342907181</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18998244759333999</v>
+        <v>0.18997028077419448</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.695376842553044E-2</v>
+        <v>9.6947559331054325E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.041156904488764E-3</v>
+        <v>5.0408340596937943E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14323,50 +14323,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.5828278957727346E-2</v>
+        <v>6.58240703842322E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.888830305736901E-2</v>
+        <v>6.888390091053842E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1392056469882605E-2</v>
+        <v>6.1388135981231377E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.8577019049652336E-2</v>
+        <v>7.857199682658024E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.4757693402682988E-2</v>
+        <v>9.4751628186554387E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.8070058152937861E-2</v>
+        <v>3.8067620077640515E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7510179532760438E-2</v>
+        <v>3.7507777313101343E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6132892549109924E-2</v>
+        <v>1.613185936952715E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2336522570996102E-2</v>
+        <v>1.2335732517804836E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.295699248411067E-3</v>
+        <v>6.2952960604580731E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2734785094082884E-4</v>
+        <v>3.2732688699310349E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15166,7 +15166,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419785.7979569105</v>
+        <v>2419786.0622129524</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30247322.47446138</v>
+        <v>30247325.777661905</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14105367.257122653</v>
+        <v>14105352.356953345</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42978124.931584038</v>
+        <v>42978113.334615253</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15278,7 +15278,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0828863799999999</v>
+        <v>1.08281703</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15345,7 +15345,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>24.089078931469764</v>
+        <v>24.087532029494838</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551052.0669919285</v>
+        <v>2551052.345583084</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362085.2472147485</v>
+        <v>2362085.505169522</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15402,7 +15402,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689439.1453981404</v>
+        <v>2689439.4391020476</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15414,7 +15414,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305760.5841890778</v>
+        <v>2305760.8359928392</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15424,7 +15424,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835333.3161595426</v>
+        <v>2835333.6257960233</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250779.0004060785</v>
+        <v>2250779.2462054999</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989141.8169769258</v>
+        <v>2989142.1434102757</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15458,7 +15458,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197108.4697202728</v>
+        <v>2197108.7096585296</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151293.9769996875</v>
+        <v>3151294.3211410879</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144717.7296596575</v>
+        <v>2144717.9638765119</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15490,7 +15490,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322242.4152220027</v>
+        <v>3322242.7780320626</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093576.2632156734</v>
+        <v>2093576.4918475535</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502464.3038884662</v>
+        <v>3502464.6863799058</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043654.2810673956</v>
+        <v>2043654.504247477</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692462.7004357777</v>
+        <v>3692463.1036762539</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994922.7042295907</v>
+        <v>1994922.9220878729</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15556,7 +15556,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892767.9516883525</v>
+        <v>3892768.37680344</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947353.1471145439</v>
+        <v>1947353.3597779274</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103939.1742274137</v>
+        <v>4103939.6224037455</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900917.9009977744</v>
+        <v>1900918.1085901328</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326565.8150657602</v>
+        <v>4326566.2875543414</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855589.9178780227</v>
+        <v>1855590.1205202763</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561269.2969845543</v>
+        <v>4561269.7951042512</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811342.7947220944</v>
+        <v>1811342.9925322796</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808704.753124794</v>
+        <v>4808705.2782660211</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768150.7580853985</v>
+        <v>1768150.9511787379</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069562.8556752782</v>
+        <v>5069563.4093038738</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15678,7 +15678,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1725988.6490992066</v>
+        <v>1725988.8375881747</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344571.743761519</v>
+        <v>5344572.3274228387</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684831.9088159006</v>
+        <v>1684832.0928102902</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15710,7 +15710,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634499.0559169585</v>
+        <v>5634499.67124019</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15722,7 +15722,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644656.5639036661</v>
+        <v>1644656.7435106519</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940154.0728097875</v>
+        <v>5940154.7215124974</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15744,7 +15744,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605439.2126822984</v>
+        <v>1605439.3880064995</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15754,7 +15754,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262389.9762063874</v>
+        <v>6262390.6600993127</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15766,7 +15766,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567157.011491992</v>
+        <v>1567157.1826355327</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602106.2304769009</v>
+        <v>6602106.9514690069</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529787.6613871697</v>
+        <v>1529787.8284497387</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15798,7 +15798,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960251.0932904892</v>
+        <v>6960251.8533942988</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15810,7 +15810,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493309.395147599</v>
+        <v>1493309.5582265088</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888150.837399106</v>
+        <v>31888154.319788549</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841545.5995941423</v>
+        <v>6841546.3467345545</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44768674.800622314</v>
+        <v>44768679.689647116</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16084,7 +16084,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44768674.800622314</v>
+        <v>44768679.689647116</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16114,19 +16114,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30247322.474461377</v>
+        <v>30247325.777661901</v>
       </c>
       <c r="C56" s="124">
-        <v>31223259.434108812</v>
+        <v>31223262.843887877</v>
       </c>
       <c r="D56" s="124">
-        <v>32742368.321612637</v>
+        <v>32742371.897288084</v>
       </c>
       <c r="E56" s="124">
-        <v>33264102.669525992</v>
+        <v>33264106.302178156</v>
       </c>
       <c r="F56" s="124">
-        <v>35432321.917586386</v>
+        <v>35432325.78702192</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16135,19 +16135,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30247322.474461369</v>
+        <v>30247325.777661897</v>
       </c>
       <c r="C57" s="124">
-        <v>32200095.077473737</v>
+        <v>32200098.593929484</v>
       </c>
       <c r="D57" s="124">
-        <v>35503450.74533695</v>
+        <v>35503454.622540206</v>
       </c>
       <c r="E57" s="124">
-        <v>36716225.825566977</v>
+        <v>36716229.835213013</v>
       </c>
       <c r="F57" s="124">
-        <v>42215980.872865714</v>
+        <v>42215985.483120069</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16156,19 +16156,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30247322.474461362</v>
+        <v>30247325.77766189</v>
       </c>
       <c r="C58" s="124">
-        <v>33409200.037281282</v>
+        <v>33409203.685779005</v>
       </c>
       <c r="D58" s="124">
-        <v>39199990.66651246</v>
+        <v>39199994.947401457</v>
       </c>
       <c r="E58" s="124">
-        <v>41464754.413557634</v>
+        <v>41464758.941773281</v>
       </c>
       <c r="F58" s="124">
-        <v>52656787.834676169</v>
+        <v>52656793.585133232</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16177,19 +16177,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30247322.474461362</v>
+        <v>30247325.77766189</v>
       </c>
       <c r="C59" s="124">
-        <v>34641084.090132892</v>
+        <v>34641087.873160213</v>
       </c>
       <c r="D59" s="124">
-        <v>43294410.410188548</v>
+        <v>43294415.13821429</v>
       </c>
       <c r="E59" s="124">
-        <v>46881534.815663472</v>
+        <v>46881539.935426071</v>
       </c>
       <c r="F59" s="124">
-        <v>66146189.815248445</v>
+        <v>66146197.038834244</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16198,19 +16198,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30247322.474461358</v>
+        <v>30247325.777661886</v>
       </c>
       <c r="C60" s="124">
-        <v>35786804.616542816</v>
+        <v>35786808.524690121</v>
       </c>
       <c r="D60" s="124">
-        <v>47452215.150032289</v>
+        <v>47452220.33211682</v>
       </c>
       <c r="E60" s="124">
-        <v>52558155.980415449</v>
+        <v>52558161.720101282</v>
       </c>
       <c r="F60" s="124">
-        <v>82323785.774822459</v>
+        <v>82323794.765104905</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16219,19 +16219,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30247322.474461354</v>
+        <v>30247325.777661886</v>
       </c>
       <c r="C61" s="124">
-        <v>36797489.499932945</v>
+        <v>36797493.518453486</v>
       </c>
       <c r="D61" s="124">
-        <v>51473003.113387227</v>
+        <v>51473008.734567441</v>
       </c>
       <c r="E61" s="124">
-        <v>58234055.757732093</v>
+        <v>58234062.117262393</v>
       </c>
       <c r="F61" s="124">
-        <v>101003229.2566058</v>
+        <v>101003240.28680262</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16281,23 +16281,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16308,23 +16308,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.005440974057635</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.414304212025929</v>
+        <v>18.41312011319356</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.050726239526146</v>
+        <v>19.049501452574347</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.269303876881118</v>
+        <v>19.268065115691101</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.177666997699287</v>
+        <v>20.176370162486766</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16335,23 +16335,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.005440974057631</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.823543948425808</v>
+        <v>18.822333685830166</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.207466015493935</v>
+        <v>20.206167275152509</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.715551236909501</v>
+        <v>20.714220013355241</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>23.019642330542588</v>
+        <v>23.018163800437701</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16362,23 +16362,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>18.005440974057624</v>
+        <v>18.00428301491802</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.330091593766578</v>
+        <v>19.328848946259342</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.756110388996159</v>
+        <v>21.754712639782454</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.704920278504396</v>
+        <v>22.703461869400815</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.393759018314977</v>
+        <v>27.392000839526446</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16389,23 +16389,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>18.005440974057624</v>
+        <v>18.00428301491802</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.846182410567252</v>
+        <v>19.844906768028594</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.471444250934816</v>
+        <v>23.469936835955256</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.974249616506164</v>
+        <v>24.972646123261612</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>33.045067248331293</v>
+        <v>33.042947766674054</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16416,23 +16416,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>18.005440974057624</v>
+        <v>18.004283014918016</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.326175508076258</v>
+        <v>20.324869178327482</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.213332896474526</v>
+        <v>25.211714118012569</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.352437764005245</v>
+        <v>27.350682226992234</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.822579054999302</v>
+        <v>39.820026269342556</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16442,23 +16442,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>18.005440974057624</v>
+        <v>18.004283014918016</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.749596191045136</v>
+        <v>20.7482627909082</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.897819142876266</v>
+        <v>26.896092670816934</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.73032369034166</v>
+        <v>29.728416128881978</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.648225650212439</v>
+        <v>47.645172550566564</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.648225650212439</v>
+        <v>47.645172550566564</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.974249616506164</v>
+        <v>24.972646123261612</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16538,7 +16538,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.471444250934816</v>
+        <v>23.469936835955256</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.846182410567252</v>
+        <v>19.844906768028594</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>18.005440974057624</v>
+        <v>18.004283014918016</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16705,7 +16705,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16734,7 +16734,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>24.632605422459658</v>
+        <v>24.631092884704774</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532269.4140404132</v>
+        <v>2532269.766381802</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419785.7979569105</v>
+        <v>2419786.0622129524</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10082614875724705</v>
+        <v>-0.10082611729521807</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>18.005440974057638</v>
+        <v>18.004283014918023</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.471444250934816</v>
+        <v>23.469936835955256</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.846182410567252</v>
+        <v>19.844906768028594</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17103,7 +17103,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>24.974249616506164</v>
+        <v>24.972646123261612</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17130,7 +17130,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.12209322425414</v>
+        <v>23.12060814419651</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17204,7 +17204,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>18.005440974057624</v>
+        <v>18.004283014918016</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17262,7 +17262,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.648225650212439</v>
+        <v>47.645172550566564</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17288,7 +17288,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.092567233042224</v>
+        <v>24.091020108051087</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.089078931469764</v>
+        <v>24.087532029494838</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.22137521597866044</v>
+        <v>0.22137499541461994</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.54003818941743453</v>
+        <v>0.54007277665368825</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.85807817268950937</v>
+        <v>0.85813312908530615</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7800900995051858</v>
+        <v>8.7795262784442762</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.6381682721946955</v>
+        <v>9.6376594075295827</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.59995262526542881</v>
+        <v>0.59994805681521424</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19139067803306431</v>
+        <v>0.19136836795872036</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1375804453006144</v>
+        <v>1.1376533026732782</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.942457889492028</v>
+        <v>13.941562562529564</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>15.080038334792642</v>
+        <v>15.079215865202842</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37407922580741715</v>
+        <v>0.37407316927341527</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.3917307909464707</v>
+        <v>1.3918199256088173</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>19.125456638535017</v>
+        <v>19.124228480836162</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.517187429481488</v>
+        <v>20.51604840644498</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17656,7 +17656,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.14840177756802986</v>
+        <v>0.14839436792514116</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F708BFF-BB16-4622-88B3-D040606167C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE40641-4C0E-4BB6-8825-5B294E4117BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="444">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2377,6 +2377,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4097,7 +4109,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4119,7 +4131,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4162,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4197,10 +4209,10 @@
         <v>427</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4209,7 +4221,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>15.4</v>
+        <v>15.28</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4230,7 +4242,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>39805.887752399998</v>
+        <v>39495.712003679997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4257,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4313,7 +4325,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>9.6376594075295827</v>
+        <v>9.6505192185354964</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,10 +4365,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19136836795872036</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.19513328682324205</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4497,7 +4513,7 @@
       </c>
       <c r="C45" s="322">
         <f>Normalized_FCF!C48</f>
-        <v>95978.492381801712</v>
+        <v>95969.603466767265</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4527,7 +4543,7 @@
       </c>
       <c r="C47" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158442.50761819829</v>
+        <v>-158451.39653323274</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4567,7 +4583,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806595.35407098406</v>
+        <v>-806593.13184222544</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4620,7 +4636,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532269.766381802</v>
+        <v>2532260.8774667676</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4633,7 +4649,7 @@
       </c>
       <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419786.0622129524</v>
+        <v>2419779.3955266764</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4646,7 +4662,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.58240703842322E-2</v>
+        <v>6.6448187927637556E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4671,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5069660821668069E-2</v>
+        <v>3.5287971550680156E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4712,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4724,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4777,7 +4793,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.671133548964699</v>
+        <v>12.691603894178773</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4844,7 +4860,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.8110816366519874</v>
+        <v>0.81239418549607889</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,7 +4918,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14105352.356953345</v>
+        <v>14105728.260390403</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4915,7 +4931,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9089786906766859</v>
+        <v>5.9186987392570272</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4962,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23525241192862759</v>
+        <v>0.23563311378081256</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4968,7 +4984,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4997,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>4.564947591459446</v>
+        <v>4.5723349078697169</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5039,7 +5055,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>47.65 HKD</v>
+        <v>47.72 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5061,7 +5077,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>24.97 HKD</v>
+        <v>25.01 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5083,7 +5099,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.47 HKD</v>
+        <v>23.51 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5105,7 +5121,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.84 HKD</v>
+        <v>19.88 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5127,7 +5143,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>18 HKD</v>
+        <v>18.03 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5156,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>24.091020108051087</v>
+        <v>24.130111840577843</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5213,7 +5229,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5265,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.85813312908530615</v>
+        <v>0.85674668188176073</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5275,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>8.7795262784442762</v>
+        <v>8.7937725366537354</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5284,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>9.6376594075295827</v>
+        <v>9.6505192185354964</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5310,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.59994805681521424</v>
+        <v>0.60006322049834337</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5311,40 +5327,40 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1376533026732782</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>1.1358152472636511</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>13.941562562529564</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>13.964185092926993</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>15.079215865202842</v>
+        <v>15.100000340190643</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>426</v>
       </c>
@@ -5357,21 +5373,21 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37407316927341527</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.37422584528605141</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5380,40 +5396,40 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>1.3918199256088173</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>1.3895712245876179</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>19.124228480836162</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>19.15526075847324</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>20.51604840644498</v>
+        <v>20.54483198306086</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>426</v>
       </c>
@@ -5426,127 +5442,196 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14839436792514116</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>0.14858115375527936</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>1.3008761008000131</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>17.295508446343717</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>18.596384547143732</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.22921710580164956</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6253,7 +6338,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -6271,7 +6356,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7629,7 +7714,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8980,11 +9065,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.93529166416141</v>
+        <v>10.952987915420218</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.564947591459446</v>
+        <v>4.5723349078697169</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9175,7 +9260,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14105352.356953345</v>
+        <v>14105728.260390403</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9242,11 +9327,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2211861.081848505</v>
+        <v>-2211673.1301299767</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2029417.8215233271</v>
+        <v>-2029229.8698047986</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9258,11 +9343,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>8.2121739692710527</v>
+        <v>8.2128718536868597</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>8.9504427365112758</v>
+        <v>8.9512717461365288</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9275,7 +9360,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4058835.6430466543</v>
+        <v>4058459.7396095973</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9390,11 +9475,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2096482.1160131099</v>
+        <v>-2099874.7895168401</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.8110816366519874</v>
+        <v>-0.81239418549607889</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9407,11 +9492,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15273515.746259721</v>
+        <v>15298640.107476404</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9089786906766868</v>
+        <v>5.9186987392570272</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9424,11 +9509,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>608079.94173456589</v>
+        <v>609063.97908490407</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23525241192862753</v>
+        <v>0.23563311378081256</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9441,11 +9526,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13785113.571981177</v>
+        <v>13807829.297044467</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>5.3331494659533263</v>
+        <v>5.3419376675417602</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -10025,24 +10110,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158442.50761819829</v>
+        <v>-158451.39653323274</v>
       </c>
       <c r="E12" s="302"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158442.50761819829</v>
+        <v>-158451.39653323274</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69595.443611745213</v>
+        <v>-69605.802495987067</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20510.530278873281</v>
+        <v>-20519.796314444771</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80035.693244578812</v>
+        <v>-80038.695991577843</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -10080,24 +10165,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226381.4162839362</v>
+        <v>3226372.5273689018</v>
       </c>
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3628960.766381802</v>
+        <v>3628951.8774667676</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3325973.830388255</v>
+        <v>3325963.4715040131</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239746.8947211262</v>
+        <v>4239737.6286855554</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800560.0607554205</v>
+        <v>4800557.0580084221</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10135,7 +10220,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806595.35407098406</v>
+        <v>-806593.13184222544</v>
       </c>
       <c r="E14" s="302"/>
       <c r="G14" s="191">
@@ -10247,26 +10332,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419786.0622129524</v>
+        <v>2419779.3955266764</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="310"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532269.766381802</v>
+        <v>2532260.8774667676</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256714.830388255</v>
+        <v>2256704.4715040131</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888417.8947211262</v>
+        <v>2888408.6286855554</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483204.0607554205</v>
+        <v>3483201.0580084221</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10355,26 +10440,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419786.0622129524</v>
+        <v>2419779.3955266764</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="299"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532269.766381802</v>
+        <v>2532260.8774667676</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256714.830388255</v>
+        <v>2256704.4715040131</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888417.8947211262</v>
+        <v>2888408.6286855554</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483204.0607554205</v>
+        <v>3483201.0580084221</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11216,19 +11301,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30235649557025263</v>
+        <v>0.30235723654626018</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32164741298071792</v>
+        <v>0.32164841531518673</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31886636031052384</v>
+        <v>0.31886705750064509</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.27447445205146542</v>
+        <v>0.2744746237719165</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11354,24 +11439,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>95978.492381801712</v>
+        <v>95969.603466767265</v>
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>95978.492381801712</v>
+        <v>95969.603466767265</v>
       </c>
       <c r="H48" s="328">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111850.55638825479</v>
+        <v>111840.19750401293</v>
       </c>
       <c r="I48" s="328">
         <f t="shared" si="19"/>
-        <v>100050.46972112672</v>
+        <v>100041.20368555523</v>
       </c>
       <c r="J48" s="328">
         <f t="shared" si="19"/>
-        <v>32422.306755421181</v>
+        <v>32419.304008422161</v>
       </c>
       <c r="K48" s="328">
         <f t="shared" si="19"/>
@@ -11466,24 +11551,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158442.50761819829</v>
+        <v>-158451.39653323274</v>
       </c>
       <c r="E50" s="302"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158442.50761819829</v>
+        <v>-158451.39653323274</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69595.443611745213</v>
+        <v>-69605.802495987067</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20510.530278873281</v>
+        <v>-20519.796314444771</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80035.693244578812</v>
+        <v>-80038.695991577843</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12109,7 +12194,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12441,7 +12526,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12553,26 +12638,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.0561037152961645E-3</v>
+        <v>6.05644347381283E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="299"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5253340829427358E-3</v>
+        <v>5.5256440643103536E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5217119157618152E-3</v>
+        <v>2.5220872581760744E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9487756620414004E-4</v>
+        <v>7.9523666778285511E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5457512355343622E-3</v>
+        <v>3.5458842636053416E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12610,26 +12695,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.1233210757381084</v>
+        <v>0.12332073597959173</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="299"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.1265520276696778</v>
+        <v>0.12655171768831017</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12051288711358367</v>
+        <v>0.12051251177116941</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16430973003505495</v>
+        <v>0.16430937093347625</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267500881968554</v>
+        <v>0.21267487579161459</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12667,7 +12752,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0830268934527099E-2</v>
+        <v>3.0830183994897932E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="299"/>
@@ -12782,26 +12867,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2490806803581307E-2</v>
+        <v>9.2490551984693803E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="299"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.8307340357871036E-2</v>
+        <v>8.830703037650342E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.176950074510432E-2</v>
+        <v>8.176912540269006E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11193950400694072</v>
+        <v>0.11193914490536204</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431333947842579</v>
+        <v>0.15431320645035485</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -12889,26 +12974,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2490806803581307E-2</v>
+        <v>9.2490551984693803E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="299"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.8307340357871036E-2</v>
+        <v>8.830703037650342E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.176950074510432E-2</v>
+        <v>8.176912540269006E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11193950400694072</v>
+        <v>0.11193914490536204</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431333947842579</v>
+        <v>0.15431320645035485</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -12958,12 +13043,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13014,12 +13099,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1395978.982182059</v>
+        <v>1393723.5615597165</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1395978.982182059</v>
+        <v>1393723.5615597165</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13069,12 +13154,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.57690181953746877</v>
+        <v>0.57597133198845418</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55127577666288052</v>
+        <v>0.55038703711837722</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13124,12 +13209,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5069660821668069E-2</v>
+        <v>3.5287971550680156E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5069660821668069E-2</v>
+        <v>3.5287971550680156E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13261,26 +13346,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.1109351618863742</v>
+        <v>-0.11093543361586022</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1097209853325367E-2</v>
+        <v>9.1097935548204223E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21552538088313777</v>
+        <v>-0.21552610968165964</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.11682244549317111</v>
+        <v>-0.1168238232659462</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633407732950379</v>
+        <v>1.4633392324770877</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -13876,15 +13961,15 @@
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.077327598894481</v>
+        <v>2.077337134390334</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3549299798870877</v>
+        <v>1.3549343265121687</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.873371437958423</v>
+        <v>1.8733730529270591</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -13980,24 +14065,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.1233210757381084</v>
+        <v>0.12332073597959173</v>
       </c>
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.1265520276696778</v>
+        <v>0.12655171768831017</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12051288711358367</v>
+        <v>0.12051251177116941</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16430973003505495</v>
+        <v>0.16430937093347625</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267500881968554</v>
+        <v>0.21267487579161459</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14266,50 +14351,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.013690683917176</v>
+        <v>1.0153283115343019</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0608120740222917</v>
+        <v>1.0625250243206967</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.94537729411096327</v>
+        <v>0.94690282300935413</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2100087511293358</v>
+        <v>1.2119629836529378</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4591750740729377</v>
+        <v>1.4615351529565481</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58624134919566395</v>
+        <v>0.58719004581320999</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57761977062176073</v>
+        <v>0.57855451519985712</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.2484306342907181</v>
+        <v>0.24883266206096968</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.18997028077419448</v>
+        <v>0.1902777039251749</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.6947559331054325E-2</v>
+        <v>9.7104446629677849E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0408340596937943E-3</v>
+        <v>5.0489914887605148E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14323,50 +14408,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.58240703842322E-2</v>
+        <v>6.6448187927637556E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.888390091053842E-2</v>
+        <v>6.953697803145921E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1388135981231377E-2</v>
+        <v>6.1970080039879201E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.857199682658024E-2</v>
+        <v>7.9316949191946193E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.4751628186554387E-2</v>
+        <v>9.565020634532384E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.8067620077640515E-2</v>
+        <v>3.8428667919712695E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7507777313101343E-2</v>
+        <v>3.7863515392660807E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.613185936952715E-2</v>
+        <v>1.6284860082524194E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2335732517804836E-2</v>
+        <v>1.2452729314474798E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.2952960604580731E-3</v>
+        <v>6.3550030516804877E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.2732688699310349E-4</v>
+        <v>3.3043138015448396E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14380,43 +14465,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.5690260163041923E-2</v>
+        <v>7.6284686289976811E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0062578174954782E-2</v>
+        <v>8.0691341877899447E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10208969651116459</v>
+        <v>0.102891448054446</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10076117445108791</v>
+        <v>0.10155249257504934</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2669165188951072E-2</v>
+        <v>4.3004263344885246E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7661338175019418E-2</v>
+        <v>3.7957107846550986E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7968773977585135E-2</v>
+        <v>1.8109890003587113E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2941678457326704E-2</v>
+        <v>1.3043314675577962E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7607169179583056E-2</v>
+        <v>1.7745445377328476E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5476353745253596E-3</v>
+        <v>1.5597895790373389E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15166,7 +15251,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419786.0622129524</v>
+        <v>2419779.3955266764</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15198,7 +15283,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30247325.777661905</v>
+        <v>30247242.444083456</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15232,7 +15317,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14105352.356953345</v>
+        <v>14105728.260390403</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15264,7 +15349,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42978113.334615253</v>
+        <v>42978405.904473864</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15278,7 +15363,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.08281703</v>
+        <v>1.0845693200000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15292,7 +15377,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15345,7 +15430,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>24.087532029494838</v>
+        <v>24.126618126995183</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15380,7 +15465,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551052.345583084</v>
+        <v>2551045.3172486676</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15392,7 +15477,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362085.505169522</v>
+        <v>2362078.9974524695</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15402,7 +15487,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689439.4391020476</v>
+        <v>2689432.0295011415</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15414,7 +15499,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305760.8359928392</v>
+        <v>2305754.4834543392</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15424,7 +15509,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835333.6257960233</v>
+        <v>2835325.8142460412</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15436,7 +15521,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250779.2462054999</v>
+        <v>2250773.0451452718</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15446,7 +15531,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989142.1434102757</v>
+        <v>2989133.9081066614</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15458,7 +15543,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197108.7096585296</v>
+        <v>2197102.6564645264</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15468,7 +15553,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151294.3211410879</v>
+        <v>3151285.6390964515</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15480,7 +15565,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144717.9638765119</v>
+        <v>2144712.0550228166</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15490,7 +15575,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322242.7780320626</v>
+        <v>3322233.6250120173</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15502,7 +15587,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093576.4918475535</v>
+        <v>2093570.7238923267</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15512,7 +15597,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502464.6863799058</v>
+        <v>3502455.0368354185</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15524,7 +15609,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043654.504247477</v>
+        <v>2043648.8738309499</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15534,7 +15619,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692463.1036762539</v>
+        <v>3692452.9306723336</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15546,7 +15631,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994922.9220878729</v>
+        <v>1994917.4259303929</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15556,7 +15641,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892768.37680344</v>
+        <v>3892757.65194395</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15568,7 +15653,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947353.3597779274</v>
+        <v>1947347.9946780447</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15578,7 +15663,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103939.6224037455</v>
+        <v>4103928.315752143</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15590,7 +15675,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900918.1085901328</v>
+        <v>1900912.8714227385</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15600,7 +15685,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326566.2875543414</v>
+        <v>4326554.3675501132</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15612,7 +15697,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855590.1205202763</v>
+        <v>1855585.0082347796</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15622,7 +15707,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561269.7951042512</v>
+        <v>4561257.2284748219</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15634,7 +15719,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811342.9925322796</v>
+        <v>1811338.0021508334</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15644,7 +15729,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808705.2782660211</v>
+        <v>4808692.0299338717</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15656,7 +15741,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768150.9511787379</v>
+        <v>1768146.0797945012</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15666,7 +15751,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069563.4093038738</v>
+        <v>5069549.4422886344</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15678,7 +15763,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1725988.8375881747</v>
+        <v>1725984.0823636216</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15688,7 +15773,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344572.3274228387</v>
+        <v>5344557.6027380656</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15700,7 +15785,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684832.0928102902</v>
+        <v>1684827.4509755573</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15710,7 +15795,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634499.67124019</v>
+        <v>5634484.1477845358</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15722,7 +15807,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644656.7435106519</v>
+        <v>1644652.2123619227</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15732,7 +15817,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940154.7215124974</v>
+        <v>5940138.3559549889</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15744,7 +15829,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605439.3880064995</v>
+        <v>1605434.964904432</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15754,7 +15839,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262390.6600993127</v>
+        <v>6262373.4067583997</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15766,7 +15851,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567157.1826355327</v>
+        <v>1567152.8650037202</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15776,7 +15861,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602106.9514690069</v>
+        <v>6602088.7621850483</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15788,7 +15873,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529787.8284497387</v>
+        <v>1529783.6137732102</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15798,7 +15883,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960251.8533942988</v>
+        <v>6960232.6773951342</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -15810,7 +15895,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493309.5582265088</v>
+        <v>1493305.4440502629</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -16040,7 +16125,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888154.319788549</v>
+        <v>31888066.465608343</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16052,7 +16137,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841546.3467345545</v>
+        <v>6841527.497777679</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16063,7 +16148,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44768679.689647116</v>
+        <v>44768556.348684393</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16084,7 +16169,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44768679.689647116</v>
+        <v>44768556.348684393</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16114,19 +16199,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30247325.777661901</v>
+        <v>30247242.444083448</v>
       </c>
       <c r="C56" s="124">
-        <v>31223262.843887877</v>
+        <v>31223176.821531951</v>
       </c>
       <c r="D56" s="124">
-        <v>32742371.897288084</v>
+        <v>32742281.68967643</v>
       </c>
       <c r="E56" s="124">
-        <v>33264106.302178156</v>
+        <v>33264014.657150343</v>
       </c>
       <c r="F56" s="124">
-        <v>35432325.78702192</v>
+        <v>35432228.168392017</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16135,19 +16220,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30247325.777661897</v>
+        <v>30247242.444083445</v>
       </c>
       <c r="C57" s="124">
-        <v>32200098.593929484</v>
+        <v>32200009.880320154</v>
       </c>
       <c r="D57" s="124">
-        <v>35503454.622540206</v>
+        <v>35503356.807945192</v>
       </c>
       <c r="E57" s="124">
-        <v>36716229.835213013</v>
+        <v>36716128.679334238</v>
       </c>
       <c r="F57" s="124">
-        <v>42215985.483120069</v>
+        <v>42215869.175015226</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16156,19 +16241,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30247325.77766189</v>
+        <v>30247242.444083445</v>
       </c>
       <c r="C58" s="124">
-        <v>33409203.685779005</v>
+        <v>33409111.640997365</v>
       </c>
       <c r="D58" s="124">
-        <v>39199994.947401457</v>
+        <v>39199886.948569477</v>
       </c>
       <c r="E58" s="124">
-        <v>41464758.941773281</v>
+        <v>41464644.703352071</v>
       </c>
       <c r="F58" s="124">
-        <v>52656793.585133232</v>
+        <v>52656648.511844084</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16177,19 +16262,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30247325.77766189</v>
+        <v>30247242.444083445</v>
       </c>
       <c r="C59" s="124">
-        <v>34641087.873160213</v>
+        <v>34640992.434448197</v>
       </c>
       <c r="D59" s="124">
-        <v>43294415.13821429</v>
+        <v>43294295.85895744</v>
       </c>
       <c r="E59" s="124">
-        <v>46881539.935426071</v>
+        <v>46881410.773379974</v>
       </c>
       <c r="F59" s="124">
-        <v>66146197.038834244</v>
+        <v>66146014.801259257</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16198,19 +16283,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30247325.777661886</v>
+        <v>30247242.444083445</v>
       </c>
       <c r="C60" s="124">
-        <v>35786808.524690121</v>
+        <v>35786709.929434538</v>
       </c>
       <c r="D60" s="124">
-        <v>47452220.33211682</v>
+        <v>47452089.597804815</v>
       </c>
       <c r="E60" s="124">
-        <v>52558161.720101282</v>
+        <v>52558016.918550044</v>
       </c>
       <c r="F60" s="124">
-        <v>82323794.765104905</v>
+        <v>82323567.957073689</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16219,19 +16304,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30247325.777661886</v>
+        <v>30247242.444083441</v>
       </c>
       <c r="C61" s="124">
-        <v>36797493.518453486</v>
+        <v>36797392.138687372</v>
       </c>
       <c r="D61" s="124">
-        <v>51473008.734567441</v>
+        <v>51472866.922691472</v>
       </c>
       <c r="E61" s="124">
-        <v>58234062.117262393</v>
+        <v>58233901.678193495</v>
       </c>
       <c r="F61" s="124">
-        <v>101003240.28680262</v>
+        <v>101002962.01554288</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16281,23 +16366,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16308,23 +16393,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.41312011319356</v>
+        <v>18.443039140489439</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.049501452574347</v>
+        <v>19.080448560401031</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.268065115691101</v>
+        <v>19.299365315340076</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.176370162486766</v>
+        <v>20.209137738183486</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16335,23 +16420,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.004283014918023</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.822333685830166</v>
+        <v>18.852913801817582</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.206167275152509</v>
+        <v>20.238982988388013</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.714220013355241</v>
+        <v>20.747856490960231</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>23.018163800437701</v>
+        <v>23.055522322680069</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16362,23 +16447,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>18.00428301491802</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.328848946259342</v>
+        <v>19.360247342805248</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.754712639782454</v>
+        <v>21.790030043815484</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.703461869400815</v>
+        <v>22.740311987470573</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.392000839526446</v>
+        <v>27.436425340022012</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16389,23 +16474,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>18.00428301491802</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.844906768028594</v>
+        <v>19.877138861237956</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.469936835955256</v>
+        <v>23.508025202134611</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.972646123261612</v>
+        <v>25.013162131589048</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>33.042947766674054</v>
+        <v>33.096501429445283</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16416,23 +16501,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>18.004283014918016</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.324869178327482</v>
+        <v>20.357876655695705</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.211714118012569</v>
+        <v>25.252616343118749</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.350682226992234</v>
+        <v>27.395039976848697</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.820026269342556</v>
+        <v>39.884528371411363</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16442,23 +16527,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>18.004283014918016</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.7482627909082</v>
+        <v>20.78195426496681</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.896092670816934</v>
+        <v>26.939716026618623</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.728416128881978</v>
+        <v>29.776615132057312</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.645172550566564</v>
+        <v>47.722316256096377</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16493,7 +16578,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.645172550566564</v>
+        <v>47.722316256096377</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16515,7 +16600,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.972646123261612</v>
+        <v>25.013162131589048</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16538,7 +16623,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.469936835955256</v>
+        <v>23.508025202134611</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16561,7 +16646,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.844906768028594</v>
+        <v>19.877138861237956</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16584,7 +16669,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>18.004283014918016</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16652,7 +16737,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16685,7 +16770,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-15.4</v>
+        <v>-15.28</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16705,7 +16790,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16714,7 +16799,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16734,7 +16819,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>24.631092884704774</v>
+        <v>24.669312045872235</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16768,7 +16853,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532269.766381802</v>
+        <v>2532260.8774667676</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16790,7 +16875,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419786.0622129524</v>
+        <v>2419779.3955266764</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -16874,7 +16959,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10082611729521807</v>
+        <v>-0.10082691102476438</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16925,7 +17010,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>15.28</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16940,7 +17025,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>18.004283014918023</v>
+        <v>18.033541561720533</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16987,7 +17072,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.469936835955256</v>
+        <v>23.508025202134611</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17045,7 +17130,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.844906768028594</v>
+        <v>19.877138861237956</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17103,7 +17188,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>24.972646123261612</v>
+        <v>25.013162131589048</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17130,7 +17215,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.12060814419651</v>
+        <v>23.158132166318889</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17204,7 +17289,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>18.004283014918016</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17262,7 +17347,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.645172550566564</v>
+        <v>47.722316256096377</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17288,7 +17373,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.091020108051087</v>
+        <v>24.130111840577843</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17350,7 +17435,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.087532029494838</v>
+        <v>24.126618126995183</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17413,7 +17498,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.22137499541461994</v>
+        <v>0.2213805598098644</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17446,7 +17531,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.54007277665368825</v>
+        <v>0.53920020529439272</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17473,7 +17558,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.85813312908530615</v>
+        <v>0.85674668188176073</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17485,7 +17570,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7795262784442762</v>
+        <v>8.7937725366537354</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17495,7 +17580,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.6376594075295827</v>
+        <v>9.6505192185354964</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17506,7 +17591,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.59994805681521424</v>
+        <v>0.60006322049834337</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17523,7 +17608,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>15.4</v>
+        <v>15.28</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17536,7 +17621,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19136836795872036</v>
+        <v>0.19513328682324205</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17562,7 +17647,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1376533026732782</v>
+        <v>1.1358152472636511</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17574,7 +17659,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.941562562529564</v>
+        <v>13.964185092926993</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17584,7 +17669,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>15.079215865202842</v>
+        <v>15.100000340190643</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17595,7 +17680,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.37407316927341527</v>
+        <v>0.37422584528605141</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17622,7 +17707,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.3918199256088173</v>
+        <v>1.3895712245876179</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17634,7 +17719,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>19.124228480836162</v>
+        <v>19.15526075847324</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17646,7 +17731,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.51604840644498</v>
+        <v>20.54483198306086</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17656,39 +17741,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.14839436792514116</v>
+        <v>0.14858115375527936</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>431</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>1.3008761008000131</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>17.295508446343717</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>18.596384547143732</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.22921710580164956</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE40641-4C0E-4BB6-8825-5B294E4117BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A3DBB6-399C-49DC-8497-6FD24C46A5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="454">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2382,13 +2359,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>Y</t>
@@ -3089,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3603,14 +3628,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3668,9 +3687,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3678,7 +3694,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3770,9 +3785,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3787,9 +3799,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3797,6 +3806,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4109,10 +4145,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4127,11 +4163,11 @@
         <v>45778</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>435</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4186,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4159,10 +4195,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>436</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4176,9 +4212,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4199,20 +4235,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4228,17 +4264,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4252,14 +4288,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4269,34 +4305,34 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4304,286 +4340,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>9.6505192185354964</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>24.13011184057784</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.19513328682324205</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>2331.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>9.6505192185354947</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>15.100000340190643</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>20.544831983060856</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>18.596384547143728</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>3205414.6239021346</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>179409.3</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>95969.603466767265</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>179409.3</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>95969.603466767265</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-254421</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-158451.39653323274</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-806593.13184222544</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4591,20 +4679,16 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="str">
@@ -4612,1059 +4696,1092 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2532260.8774667676</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-806593.13184222544</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>2419779.3955266764</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2532260.8774667676</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>2419779.3955266764</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.6448187927637556E-2</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+        <v>6.6448187927637542E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5287971550680156E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+        <v>3.5287971550680163E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.691603894178773</v>
-      </c>
-      <c r="D82" s="1" t="str">
+        <v>12.691603894178769</v>
+      </c>
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>1936137</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.81239418549607889</v>
-      </c>
-      <c r="D92" s="1" t="str">
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.81239418549607878</v>
+      </c>
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.36794481423679237</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>7.4171010848313429E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>0.60402076709908736</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>18164188</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>14105728.260390403</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9186987392570272</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>561572.19999999995</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23563311378081256</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>14105728.260390403</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.9186987392570263</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>18.033541561720533</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>561572.19999999995</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>4.5723349078697169</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.23563311378081253</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>18.033541561720529</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>4.572334907869716</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>30</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>47.72 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>20</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>25.01 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.05</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>20</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>23.51 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.495</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>20</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>19.88 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>30</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>18.03 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>24.130111840577843</v>
-      </c>
-      <c r="D122" s="236" t="str">
+        <v>24.13011184057784</v>
+      </c>
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
-        <v>0.53920020529439272</v>
-      </c>
-      <c r="D133" s="236" t="str">
+        <v>0.53920020529439283</v>
+      </c>
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>2331.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
-        <v>0.85674668188176073</v>
-      </c>
-    </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>0.85674668188176095</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>8.7937725366537354</v>
-      </c>
-    </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+        <v>8.7937725366537336</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>9.6505192185354964</v>
-      </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
+        <v>9.6505192185354947</v>
+      </c>
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C140" s="340" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.60006322049834337</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1358152472636511</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>1.1358152472636516</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>13.964185092926993</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+        <v>13.964185092926991</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>15.100000340190643</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C148" s="340" t="str">
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37422584528605141</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+        <v>0.3742258452860513</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
-        <v>1.3895712245876179</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>1.3895712245876182</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>19.15526075847324</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+        <v>19.155260758473236</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>20.54483198306086</v>
-      </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
+        <v>20.544831983060856</v>
+      </c>
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>0.14858115375527936</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
-        <v>1.3008761008000131</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>1.3008761008000136</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>17.295508446343717</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+        <v>17.295508446343714</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>18.596384547143732</v>
-      </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
+        <v>18.596384547143728</v>
+      </c>
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22921710580164956</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+        <v>0.22921710580164945</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5678,17 +5795,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6231,7 +6348,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181">
@@ -6265,7 +6382,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181">
@@ -6299,7 +6416,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181">
@@ -6338,7 +6455,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.53920020529439272</v>
+        <v>0.53920020529439283</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -6356,7 +6473,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7661,7 +7778,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7714,7 +7831,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.53920020529439272</v>
+        <v>0.53920020529439283</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8109,11 +8226,11 @@
         <f t="shared" si="40"/>
         <v>686606</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8143,11 +8260,11 @@
         <f t="shared" si="40"/>
         <v>1407257</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8279,15 +8396,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8345,7 +8462,7 @@
         <f>1004591+245432</f>
         <v>1250023</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8356,7 +8473,7 @@
         <f>8264361+7498596</f>
         <v>15762957</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8367,7 +8484,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8377,7 +8494,7 @@
       <c r="G5" s="19">
         <v>23261</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8388,7 +8505,7 @@
       <c r="C6" s="19">
         <v>2598226</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8398,7 +8515,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8409,7 +8526,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8419,7 +8536,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8430,7 +8547,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8440,7 +8557,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8451,7 +8568,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8461,7 +8578,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8472,10 +8589,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8484,10 +8601,10 @@
       <c r="C11" s="19">
         <v>893775</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8545,7 +8662,7 @@
       <c r="C15" s="19">
         <v>166519</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8554,7 +8671,7 @@
       <c r="G15" s="19">
         <v>2377970</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8565,7 +8682,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8574,7 +8691,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8585,7 +8702,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8594,7 +8711,7 @@
       <c r="G17" s="19">
         <v>450316</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8605,7 +8722,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8614,7 +8731,7 @@
       <c r="G18" s="19">
         <v>1743938</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8626,7 +8743,7 @@
         <f>4610454+1576667+150864</f>
         <v>6337985</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8635,7 +8752,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8646,7 +8763,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8655,7 +8772,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8666,7 +8783,7 @@
       <c r="C21" s="19">
         <v>234736</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8675,7 +8792,7 @@
       <c r="G21" s="19">
         <v>2913826</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8686,10 +8803,10 @@
       <c r="C22" s="19">
         <v>949424</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8698,10 +8815,10 @@
       <c r="C23" s="19">
         <v>5450</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9034,13 +9151,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9056,7 +9173,7 @@
         <f>H29</f>
         <v>10897009.050000001</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9065,29 +9182,29 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.952987915420218</v>
+        <v>10.952987915420215</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.5723349078697169</v>
-      </c>
-      <c r="F47" s="283"/>
+        <v>4.572334907869716</v>
+      </c>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9101,7 +9218,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.54859123183168057</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9112,22 +9229,22 @@
         <f>G29/G32</f>
         <v>0.73102364188421065</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9141,7 +9258,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.28379300712166428</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9155,22 +9272,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>1.1013064992204455E-2</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9192,22 +9309,22 @@
         <f>G39/G32</f>
         <v>0.17749280099481338</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9221,7 +9338,7 @@
         <f>G28/G29</f>
         <v>0</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9240,13 +9357,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9274,7 +9391,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9284,7 +9401,7 @@
         <f>G18</f>
         <v>1743938</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9294,7 +9411,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9304,26 +9421,26 @@
         <f>SUM(C66:C69)</f>
         <v>19908126</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9334,65 +9451,65 @@
         <v>-2029229.8698047986</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>8.2128718536868597</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>8.9512717461365288</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>4058459.7396095973</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9406,7 +9523,7 @@
         <f>G7*H7+G17*H17</f>
         <v>270189.59999999998</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9420,7 +9537,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9434,7 +9551,7 @@
         <f>G9*H9+G21*H21</f>
         <v>291382.60000000003</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9448,11 +9565,11 @@
         <f>SUM(D79:D81)</f>
         <v>561572.19999999995</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9463,15 +9580,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9481,58 +9598,58 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.81239418549607889</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15298640.107476404</v>
+        <v>15298640.107476402</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9186987392570272</v>
-      </c>
-      <c r="E87" s="269" t="str">
+        <v>5.9186987392570263</v>
+      </c>
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>609063.97908490407</v>
+        <v>609063.97908490396</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23563311378081256</v>
-      </c>
-      <c r="E88" s="269" t="str">
+        <v>0.23563311378081253</v>
+      </c>
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13807829.297044467</v>
-      </c>
-      <c r="D89" s="271">
+        <v>13807829.297044465</v>
+      </c>
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>5.3419376675417602</v>
-      </c>
-      <c r="E89" s="269" t="str">
+        <v>5.3419376675417594</v>
+      </c>
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9551,22 +9668,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9653,7 +9770,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9667,7 +9784,7 @@
         <v>26162449.5</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9723,7 +9840,7 @@
         <f>C25</f>
         <v>-21529127.876097865</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-23718447</v>
@@ -9778,7 +9895,7 @@
         <f>C4+C5</f>
         <v>4633321.6239021346</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>4957196</v>
@@ -9833,7 +9950,7 @@
         <f>C35</f>
         <v>-1427907</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1427907</v>
@@ -9889,7 +10006,7 @@
         <v>3205414.6239021346</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9945,7 +10062,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10000,7 +10117,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>1815.2739999999999</v>
@@ -10056,7 +10173,7 @@
         <v>179409.3</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10112,7 +10229,7 @@
         <f>C50</f>
         <v>-158451.39653323274</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-158451.39653323274</v>
@@ -10167,7 +10284,7 @@
         <f>SUM(C8:C12)</f>
         <v>3226372.5273689018</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3628951.8774667676</v>
@@ -10222,7 +10339,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-806593.13184222544</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-1096691</v>
@@ -10278,7 +10395,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10335,7 +10452,7 @@
         <v>2419779.3955266764</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10392,8 +10509,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10417,8 +10534,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10443,7 +10560,7 @@
         <v>2419779.3955266764</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10539,7 +10656,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10563,7 +10680,7 @@
         <v>-13136432.380387567</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10620,7 +10737,7 @@
         <v>-8392695.4957102966</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10677,7 +10794,7 @@
         <v>-21529127.876097865</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10726,14 +10843,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10745,8 +10862,8 @@
         <v>0.50211018583667277</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10805,8 +10922,8 @@
         <v>0.32079165583139668</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10863,7 +10980,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.82290184166806957</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.82712868897133363</v>
@@ -10911,14 +11028,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10929,8 +11046,8 @@
         <f>G33</f>
         <v>-1427907</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10987,8 +11104,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11046,7 +11163,7 @@
         <v>-1427907</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11095,14 +11212,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11115,7 +11232,7 @@
         <v>5.4578490442953362E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11173,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11229,7 +11346,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>5.4578490442953362E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>4.9795117061542438E-2</v>
@@ -11277,26 +11394,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11375,7 +11492,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11386,7 +11503,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-254421</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-254421</v>
@@ -11435,111 +11552,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>95969.603466767265</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>95969.603466767265</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>111840.19750401293</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>100041.20368555523</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>32419.304008422161</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>429525</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>429525</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>500556</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>447748</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>145097</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11553,7 +11670,7 @@
         <f>C47+C48</f>
         <v>-158451.39653323274</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-158451.39653323274</v>
@@ -11601,14 +11718,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11622,8 +11739,8 @@
         <f>G53</f>
         <v>2.3646804360316024E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11649,8 +11766,8 @@
         <f>G54</f>
         <v>0.13140650687425529</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11676,7 +11793,7 @@
         <f>-C8/C47</f>
         <v>12.598860250931073</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>13.871846270551567</v>
@@ -11724,14 +11841,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11745,7 +11862,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11800,7 +11917,7 @@
         <f>BS!$C68*C67</f>
         <v>179409.3</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>256299</v>
@@ -11855,7 +11972,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11910,7 +12027,7 @@
         <f>SUM(C58:C60)</f>
         <v>179409.3</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>256299</v>
@@ -11961,11 +12078,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12021,7 +12138,7 @@
         <f>C61+C62</f>
         <v>179409.3</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>405216</v>
@@ -12069,14 +12186,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12090,7 +12207,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12115,7 +12232,7 @@
         <f>G67*0.7</f>
         <v>0.10287596233352332</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0.1469656604764619</v>
@@ -12140,7 +12257,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12166,7 +12283,7 @@
         <v>9.0118627941173368E-3</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12194,7 +12311,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12216,7 +12333,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12240,7 +12357,7 @@
         <v>0.82290184166806957</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12297,7 +12414,7 @@
         <v>0.17709815833193046</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12354,7 +12471,7 @@
         <v>5.4578490442953362E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12411,7 +12528,7 @@
         <v>0.12251966788897709</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12468,7 +12585,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12525,8 +12642,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>443</v>
+      <c r="E78" s="296" t="s">
+        <v>453</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12584,7 +12701,7 @@
         <v>6.8575115644274815E-3</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12641,7 +12758,7 @@
         <v>6.05644347381283E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12698,7 +12815,7 @@
         <v>0.12332073597959173</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12755,7 +12872,7 @@
         <v>3.0830183994897932E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12808,12 +12925,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12870,7 +12987,7 @@
         <v>9.2490551984693803E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12922,26 +13039,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12951,7 +13068,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12977,7 +13094,7 @@
         <v>9.2490551984693803E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13026,14 +13143,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13043,12 +13160,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.53920020529439272</v>
-      </c>
-      <c r="E90" s="302"/>
+        <v>0.53920020529439283</v>
+      </c>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.53920020529439272</v>
+        <v>0.53920020529439283</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13099,12 +13216,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1393723.5615597165</v>
-      </c>
-      <c r="E91" s="302"/>
+        <v>1393723.5615597167</v>
+      </c>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1393723.5615597165</v>
+        <v>1393723.5615597167</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13154,12 +13271,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.57597133198845418</v>
-      </c>
-      <c r="E92" s="302"/>
+        <v>0.57597133198845429</v>
+      </c>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55038703711837722</v>
+        <v>0.55038703711837733</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13205,16 +13322,16 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5287971550680156E-2</v>
-      </c>
-      <c r="E93" s="302"/>
+        <v>3.5287971550680163E-2</v>
+      </c>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5287971550680156E-2</v>
+        <v>3.5287971550680163E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13259,7 +13376,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13268,7 +13385,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13292,7 +13409,7 @@
         <v>-8.7642097511117734E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13349,7 +13466,7 @@
         <v>-0.11093543361586022</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13427,7 +13544,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13442,7 +13559,7 @@
         <v>35708406</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13499,7 +13616,7 @@
         <v>1250023</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13556,7 +13673,7 @@
         <v>2598226</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13613,7 +13730,7 @@
         <v>9604717</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13670,7 +13787,7 @@
         <v>26103689</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13719,7 +13836,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13728,7 +13845,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13754,7 +13871,7 @@
         <v>4.7779279994405725E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13811,7 +13928,7 @@
         <v>9.9311266706888432E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13868,7 +13985,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13887,63 +14004,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>0</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4709732968262565</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.96304737643927274</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.6269053137360105</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.6269426147081751</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.3369811952562229</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>2.3374185439481701</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.250085896477759</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.4203453141742608</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>11.152390228065904</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13951,58 +14068,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>0</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.077337134390334</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.3549343265121687</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.8733730529270591</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.9746300057985322</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.5408832696503736</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.8191980169637287</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>2.5561117493864103</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>4.3015244745575218</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>57.096567771960444</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14011,7 +14128,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14067,7 +14184,7 @@
         <f>C81</f>
         <v>0.12332073597959173</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.12655171768831017</v>
@@ -14121,7 +14238,7 @@
         <f>C4/C101</f>
         <v>0.73266920679685343</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.80305021176246283</v>
@@ -14176,7 +14293,7 @@
         <v>1.3679448142367923</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14233,7 +14350,7 @@
         <v>0.12279546480584161</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14329,7 +14446,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14351,50 +14468,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0153283115343019</v>
+        <v>1.0153283115343017</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0625250243206967</v>
+        <v>1.0625250243206965</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.94690282300935413</v>
+        <v>0.94690282300935402</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2119629836529378</v>
+        <v>1.2119629836529375</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4615351529565481</v>
+        <v>1.4615351529565479</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58719004581320999</v>
+        <v>0.58719004581320977</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57855451519985712</v>
+        <v>0.57855451519985701</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24883266206096968</v>
+        <v>0.24883266206096963</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.1902777039251749</v>
+        <v>0.19027770392517485</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.7104446629677849E-2</v>
+        <v>9.7104446629677821E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0489914887605148E-3</v>
+        <v>5.0489914887605139E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14408,50 +14525,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6448187927637556E-2</v>
+        <v>6.6448187927637542E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.953697803145921E-2</v>
+        <v>6.9536978031459196E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1970080039879201E-2</v>
+        <v>6.1970080039879194E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9316949191946193E-2</v>
+        <v>7.9316949191946179E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.565020634532384E-2</v>
+        <v>9.5650206345323813E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.8428667919712695E-2</v>
+        <v>3.8428667919712681E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7863515392660807E-2</v>
+        <v>3.78635153926608E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6284860082524194E-2</v>
+        <v>1.6284860082524191E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2452729314474798E-2</v>
+        <v>1.2452729314474794E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.3550030516804877E-3</v>
+        <v>6.355003051680486E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3043138015448396E-4</v>
+        <v>3.3043138015448391E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14460,7 +14577,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15211,13 +15328,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15261,7 +15378,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15271,7 +15388,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15289,10 +15406,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15307,8 +15424,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15323,8 +15440,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15339,8 +15456,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15363,7 +15480,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693200000002</v>
+        <v>1.0845693199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15377,7 +15494,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15404,7 +15521,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15414,7 +15531,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15424,13 +15541,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>24.126618126995183</v>
+        <v>24.126618126995176</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16366,23 +16483,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16393,23 +16510,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.443039140489439</v>
+        <v>18.443039140489436</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.080448560401031</v>
+        <v>19.080448560401027</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.299365315340076</v>
+        <v>19.299365315340072</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.209137738183486</v>
+        <v>20.209137738183479</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16420,23 +16537,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.852913801817582</v>
+        <v>18.852913801817579</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.238982988388013</v>
+        <v>20.23898298838801</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.747856490960231</v>
+        <v>20.747856490960228</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>23.055522322680069</v>
+        <v>23.055522322680066</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16447,23 +16564,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.360247342805248</v>
+        <v>19.360247342805245</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.790030043815484</v>
+        <v>21.790030043815481</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.740311987470573</v>
+        <v>22.740311987470566</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.436425340022012</v>
+        <v>27.436425340022005</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16474,23 +16591,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.877138861237956</v>
+        <v>19.877138861237952</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.508025202134611</v>
+        <v>23.508025202134604</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>25.013162131589048</v>
+        <v>25.013162131589045</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>33.096501429445283</v>
+        <v>33.096501429445276</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16501,23 +16618,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.357876655695705</v>
+        <v>20.357876655695701</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.252616343118749</v>
+        <v>25.252616343118742</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.395039976848697</v>
+        <v>27.395039976848693</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.884528371411363</v>
+        <v>39.884528371411356</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16527,23 +16644,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.78195426496681</v>
+        <v>20.781954264966807</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.939716026618623</v>
+        <v>26.939716026618619</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.776615132057312</v>
+        <v>29.776615132057305</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.722316256096377</v>
+        <v>47.722316256096363</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16578,7 +16695,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.722316256096377</v>
+        <v>47.722316256096363</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16600,7 +16717,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>25.013162131589048</v>
+        <v>25.013162131589045</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16623,7 +16740,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.508025202134611</v>
+        <v>23.508025202134604</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16646,7 +16763,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.877138861237956</v>
+        <v>19.877138861237952</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16669,7 +16786,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16685,7 +16802,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16738,12 +16855,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16756,19 +16873,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-15.28</v>
       </c>
@@ -16785,21 +16902,21 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.53920020529439272</v>
+        <v>0.53920020529439283</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
-        <v>0.53920020529439272</v>
+        <v>0.53920020529439283</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16811,15 +16928,15 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>24.669312045872235</v>
+        <v>24.669312045872232</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16834,15 +16951,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16859,12 +16976,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16881,37 +16998,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16925,12 +17042,12 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16943,12 +17060,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16961,8 +17078,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.10082691102476438</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16978,7 +17095,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16988,25 +17105,25 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17016,23 +17133,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>18.033541561720533</v>
+        <v>18.033541561720529</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17052,8 +17169,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17063,8 +17180,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17072,14 +17189,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.508025202134611</v>
+        <v>23.508025202134604</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17089,8 +17206,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17110,8 +17227,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17121,8 +17238,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17130,14 +17247,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.877138861237956</v>
+        <v>19.877138861237952</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17147,8 +17264,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17168,8 +17285,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17179,8 +17296,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17188,14 +17305,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>25.013162131589048</v>
+        <v>25.013162131589045</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17206,8 +17323,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17215,7 +17332,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.158132166318889</v>
+        <v>23.158132166318886</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17269,8 +17386,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17280,8 +17397,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17289,14 +17406,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>18.033541561720529</v>
+        <v>18.033541561720526</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17306,12 +17423,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17327,8 +17444,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17338,8 +17455,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17347,14 +17464,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.722316256096377</v>
+        <v>47.722316256096363</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17364,8 +17481,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17373,23 +17490,23 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.130111840577843</v>
+        <v>24.13011184057784</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17398,10 +17515,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17413,8 +17530,8 @@
         <v>20</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17425,8 +17542,8 @@
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17435,29 +17552,29 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.126618126995183</v>
+        <v>24.126618126995176</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17465,38 +17582,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>0.2213805598098644</v>
       </c>
@@ -17516,10 +17633,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17531,7 +17648,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.53920020529439272</v>
+        <v>0.53920020529439283</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17540,15 +17657,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17558,7 +17675,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.85674668188176073</v>
+        <v>0.85674668188176095</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17570,7 +17687,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7937725366537354</v>
+        <v>8.7937725366537336</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17580,7 +17697,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.6505192185354964</v>
+        <v>9.6505192185354947</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17589,7 +17706,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.60006322049834337</v>
       </c>
@@ -17599,14 +17716,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>15.28</v>
       </c>
@@ -17617,9 +17734,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.19513328682324205</v>
       </c>
@@ -17629,15 +17746,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17647,7 +17764,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1358152472636511</v>
+        <v>1.1358152472636516</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17659,7 +17776,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.964185092926993</v>
+        <v>13.964185092926991</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17678,28 +17795,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.37422584528605141</v>
+        <v>0.3742258452860513</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17707,11 +17824,11 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.3895712245876179</v>
+        <v>1.3895712245876182</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17719,27 +17836,27 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>19.15526075847324</v>
+        <v>19.155260758473236</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.54483198306086</v>
+        <v>20.544831983060856</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>0.14858115375527936</v>
       </c>
@@ -17749,15 +17866,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17767,7 +17884,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.3008761008000131</v>
+        <v>1.3008761008000136</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -17777,60 +17894,60 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>17.295508446343717</v>
+        <v>17.295508446343714</v>
       </c>
       <c r="D104" s="117"/>
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>18.596384547143732</v>
+        <v>18.596384547143728</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.22921710580164956</v>
+        <v>0.22921710580164945</v>
       </c>
     </row>
     <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A3DBB6-399C-49DC-8497-6FD24C46A5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F947C95-46E1-4616-95B2-6DBC27701E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3833,29 +3833,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4315,13 +4315,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="C26" s="341">
         <f>C127</f>
-        <v>24.13011184057784</v>
+        <v>24.112370432928852</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19513328682324205</v>
+        <v>0.19487700460896318</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C29" s="339">
         <f>C144</f>
-        <v>9.6505192185354947</v>
+        <v>9.6446823610846657</v>
       </c>
       <c r="D29" s="339" t="str">
         <f>D144</f>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>15.100000340190643</v>
+        <v>14.470496975186142</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4461,7 +4461,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C31" s="148">
         <f>C160</f>
-        <v>20.544831983060856</v>
+        <v>20.531767931844968</v>
       </c>
       <c r="D31" s="148" t="str">
         <f>D160</f>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C32" s="148">
         <f>C168</f>
-        <v>18.596384547143728</v>
+        <v>18.584622775616804</v>
       </c>
       <c r="D32" s="148" t="str">
         <f>D168</f>
@@ -4517,22 +4517,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4544,13 +4544,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4570,13 +4570,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4605,13 +4605,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="C51" s="318">
         <f>Normalized_FCF!C48</f>
-        <v>95969.603466767265</v>
+        <v>95973.634053182453</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-158451.39653323274</v>
+        <v>-158447.36594681756</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C59" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>-806593.13184222544</v>
+        <v>-806594.13948882918</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4719,7 +4719,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4741,22 +4741,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C67" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2532260.8774667676</v>
+        <v>2532264.9080531825</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C68" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>2419779.3955266764</v>
+        <v>2419782.4184664874</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>6.6448187927637542E-2</v>
+        <v>6.6399547772013678E-2</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5287971550680163E-2</v>
+        <v>3.5313865427726264E-2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4817,22 +4817,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4876,22 +4876,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.691603894178769</v>
+        <v>12.682313624454611</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4928,13 +4928,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4947,13 +4947,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.81239418549607878</v>
+        <v>0.81179849779954893</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="C104" s="188">
         <f>Valuation_Model!C8</f>
-        <v>14105728.260390403</v>
+        <v>14105557.81087199</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9186987392570263</v>
+        <v>5.9142873884908846</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23563311378081253</v>
+        <v>0.23546033589874468</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5084,13 +5084,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>4.572334907869716</v>
+        <v>4.568982245212033</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5129,13 +5129,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>47.72 HKD</v>
+        <v>47.69 HKD</v>
       </c>
       <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>25.01 HKD</v>
+        <v>24.99 HKD</v>
       </c>
       <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>23.51 HKD</v>
+        <v>23.49 HKD</v>
       </c>
       <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>19.88 HKD</v>
+        <v>19.86 HKD</v>
       </c>
       <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>18.03 HKD</v>
+        <v>18.02 HKD</v>
       </c>
       <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>24.13011184057784</v>
+        <v>24.112370432928852</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5278,13 +5278,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5297,22 +5297,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C138" s="237">
         <f>Scenarios!C77</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D138" s="236" t="str">
         <f>Market_currency</f>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="C142" s="240">
         <f>Scenarios!C81</f>
-        <v>0.85674668188176095</v>
+        <v>0.85737535199980497</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>8.7937725366537336</v>
+        <v>8.7873070090848611</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>9.6505192185354947</v>
+        <v>9.6446823610846657</v>
       </c>
       <c r="D144" s="336" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.60006322049834337</v>
+        <v>0.60001102388865557</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>1.1358152472636516</v>
+        <v>1.1063878035577037</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>13.964185092926991</v>
+        <v>13.364109171628439</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>15.100000340190643</v>
+        <v>14.470496975186142</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3742258452860513</v>
+        <v>0.39987248390043673</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C158" s="240">
         <f>Scenarios!C97</f>
-        <v>1.3895712245876182</v>
+        <v>1.3905908747645801</v>
       </c>
     </row>
     <row r="159" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>19.155260758473236</v>
+        <v>19.141177057080387</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>20.544831983060856</v>
+        <v>20.531767931844968</v>
       </c>
       <c r="D160" s="336" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14858115375527936</v>
+        <v>0.14849649523441566</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C166" s="240">
         <f>Scenarios!C103</f>
-        <v>1.3008761008000136</v>
+        <v>1.3018306675922122</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>17.295508446343714</v>
+        <v>17.282792108024591</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>18.596384547143728</v>
+        <v>18.584622775616804</v>
       </c>
       <c r="D168" s="336" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22921710580164945</v>
+        <v>0.22913783912219288</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5645,13 +5645,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5688,13 +5688,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5702,22 +5702,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5741,17 +5741,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5768,6 +5757,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -9182,11 +9182,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.952987915420215</v>
+        <v>10.944956641615036</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.572334907869716</v>
+        <v>4.568982245212033</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>14105728.260390403</v>
+        <v>14105557.81087199</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9444,11 +9444,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-2211673.1301299767</v>
+        <v>-2211758.3548891824</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-2029229.8698047986</v>
+        <v>-2029315.0945640046</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>354</v>
@@ -9460,11 +9460,11 @@
       </c>
       <c r="C74" s="285">
         <f>-$C$66/C73</f>
-        <v>8.2128718536868597</v>
+        <v>8.2125553905322963</v>
       </c>
       <c r="D74" s="285">
         <f>-$C$66/D73</f>
-        <v>8.9512717461365288</v>
+        <v>8.9508958212832646</v>
       </c>
       <c r="F74" s="280" t="s">
         <v>322</v>
@@ -9477,7 +9477,7 @@
       <c r="C75" s="289"/>
       <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
-        <v>4058459.7396095973</v>
+        <v>4058630.1891280091</v>
       </c>
       <c r="F75" s="280" t="s">
         <v>355</v>
@@ -9592,11 +9592,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2099874.7895168401</v>
+        <v>-2098335.0572062195</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.81239418549607889</v>
+        <v>-0.81179849779954882</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9609,11 +9609,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15298640.107476402</v>
+        <v>15287237.657253448</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>5.9186987392570263</v>
+        <v>5.9142873884908855</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9626,11 +9626,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>609063.97908490396</v>
+        <v>608617.38317713188</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23563311378081253</v>
+        <v>0.23546033589874468</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9643,11 +9643,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13807829.297044465</v>
+        <v>13797519.98322436</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>5.3419376675417594</v>
+        <v>5.3379492265900819</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -10227,24 +10227,24 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-158451.39653323274</v>
+        <v>-158447.36594681756</v>
       </c>
       <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-158451.39653323274</v>
+        <v>-158447.36594681756</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-69605.802495987067</v>
+        <v>-69601.105367266646</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-20519.796314444771</v>
+        <v>-20515.594726629788</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-80038.695991577843</v>
+        <v>-80037.334427065682</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
@@ -10282,24 +10282,24 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>3226372.5273689018</v>
+        <v>3226376.5579553167</v>
       </c>
       <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3628951.8774667676</v>
+        <v>3628955.9080531825</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3325963.4715040131</v>
+        <v>3325968.1686327336</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>4239737.6286855554</v>
+        <v>4239741.8302733703</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>4800557.0580084221</v>
+        <v>4800558.4195729345</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-806593.13184222544</v>
+        <v>-806594.13948882918</v>
       </c>
       <c r="E14" s="298"/>
       <c r="G14" s="191">
@@ -10449,26 +10449,26 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>2419779.3955266764</v>
+        <v>2419782.4184664874</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2532260.8774667676</v>
+        <v>2532264.9080531825</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2256704.4715040131</v>
+        <v>2256709.1686327336</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>2888408.6286855554</v>
+        <v>2888412.8302733703</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>3483201.0580084221</v>
+        <v>3483202.4195729345</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
@@ -10557,26 +10557,26 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>2419779.3955266764</v>
+        <v>2419782.4184664874</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2532260.8774667676</v>
+        <v>2532264.9080531825</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2256704.4715040131</v>
+        <v>2256709.1686327336</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>2888408.6286855554</v>
+        <v>2888412.8302733703</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>3483201.0580084221</v>
+        <v>3483202.4195729345</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
@@ -11418,19 +11418,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.30235723654626018</v>
+        <v>0.30235690055791753</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.32164841531518673</v>
+        <v>0.32164796081623392</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.31886705750064509</v>
+        <v>0.31886674136663112</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2744746237719165</v>
+        <v>0.27447454590703074</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -11556,24 +11556,24 @@
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>95969.603466767265</v>
+        <v>95973.634053182453</v>
       </c>
       <c r="E48" s="298"/>
       <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>95969.603466767265</v>
+        <v>95973.634053182453</v>
       </c>
       <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>111840.19750401293</v>
+        <v>111844.89463273335</v>
       </c>
       <c r="I48" s="324">
         <f t="shared" si="19"/>
-        <v>100041.20368555523</v>
+        <v>100045.40527337021</v>
       </c>
       <c r="J48" s="324">
         <f t="shared" si="19"/>
-        <v>32419.304008422161</v>
+        <v>32420.665572934322</v>
       </c>
       <c r="K48" s="324">
         <f t="shared" si="19"/>
@@ -11668,24 +11668,24 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-158451.39653323274</v>
+        <v>-158447.36594681756</v>
       </c>
       <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-158451.39653323274</v>
+        <v>-158447.36594681756</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-69605.802495987067</v>
+        <v>-69601.105367266646</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-20519.796314444771</v>
+        <v>-20515.594726629788</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-80038.695991577843</v>
+        <v>-80037.334427065682</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
@@ -12755,26 +12755,26 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>6.05644347381283E-3</v>
+        <v>6.0562894138340359E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>5.5256440643103536E-3</v>
+        <v>5.5255035064712436E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>2.5220872581760744E-3</v>
+        <v>2.5219170630476372E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>7.9523666778285511E-4</v>
+        <v>7.9507383689300692E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.5458842636053416E-3</v>
+        <v>3.5458239434049965E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -12812,26 +12812,26 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.12332073597959173</v>
+        <v>0.12332089003957052</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.12655171768831017</v>
+        <v>0.12655185824614926</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.12051251177116941</v>
+        <v>0.12051268196629786</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.16430937093347625</v>
+        <v>0.16430953376436611</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.21267487579161459</v>
+        <v>0.21267493611181496</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>3.0830183994897932E-2</v>
+        <v>3.0830222509892629E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="295"/>
@@ -12984,26 +12984,26 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>9.2490551984693803E-2</v>
+        <v>9.2490667529677884E-2</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>8.830703037650342E-2</v>
+        <v>8.8307170934342524E-2</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>8.176912540269006E-2</v>
+        <v>8.1769295597818509E-2</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.11193914490536204</v>
+        <v>0.11193930773625188</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15431320645035485</v>
+        <v>0.15431326677055521</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
@@ -13091,26 +13091,26 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>9.2490551984693803E-2</v>
+        <v>9.2490667529677884E-2</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>8.830703037650342E-2</v>
+        <v>8.8307170934342524E-2</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>8.176912540269006E-2</v>
+        <v>8.1769295597818509E-2</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.11193914490536204</v>
+        <v>0.11193930773625188</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15431320645035485</v>
+        <v>0.15431326677055521</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
@@ -13160,12 +13160,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1393723.5615597167</v>
+        <v>1394746.2586701883</v>
       </c>
       <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1393723.5615597167</v>
+        <v>1394746.2586701883</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13271,12 +13271,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.57597133198845429</v>
+        <v>0.57639325256115159</v>
       </c>
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55038703711837733</v>
+        <v>0.55079002762885343</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13326,12 +13326,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5287971550680163E-2</v>
+        <v>3.5313865427726264E-2</v>
       </c>
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5287971550680163E-2</v>
+        <v>3.5313865427726264E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13463,26 +13463,26 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.11093543361586022</v>
+        <v>-0.11093531040277549</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>9.1097935548204223E-2</v>
+        <v>9.1097606488820926E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.21552610968165964</v>
+        <v>-0.21552577921512694</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.1168238232659462</v>
+        <v>-0.11682319852894429</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>1.4633392324770877</v>
+        <v>1.4633399311450215</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
@@ -14078,15 +14078,15 @@
       </c>
       <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>2.077337134390334</v>
+        <v>2.0773328106076989</v>
       </c>
       <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.3549343265121687</v>
+        <v>1.3549323555766097</v>
       </c>
       <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.8733730529270591</v>
+        <v>1.8733723206359201</v>
       </c>
       <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
@@ -14182,24 +14182,24 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.12332073597959173</v>
+        <v>0.12332089003957052</v>
       </c>
       <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.12655171768831017</v>
+        <v>0.12655185824614926</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.12051251177116941</v>
+        <v>0.12051268196629786</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.16430937093347625</v>
+        <v>0.16430953376436611</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.21267487579161459</v>
+        <v>0.21267493611181496</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14468,50 +14468,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0153283115343017</v>
+        <v>1.0145850899563689</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0625250243206965</v>
+        <v>1.0617476182667271</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.94690282300935402</v>
+        <v>0.94621047635912248</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2119629836529375</v>
+        <v>1.2110760739766171</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4615351529565479</v>
+        <v>1.4604640538045928</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58719004581320977</v>
+        <v>0.58675948895785501</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57855451519985701</v>
+        <v>0.57813029034371055</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24883266206096963</v>
+        <v>0.24865020561564935</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19027770392517485</v>
+        <v>0.19013818287840253</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.7104446629677821E-2</v>
+        <v>9.7033244834824617E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0489914887605139E-3</v>
+        <v>5.0452893178643725E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14525,50 +14525,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.6448187927637542E-2</v>
+        <v>6.6399547772013678E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9536978031459196E-2</v>
+        <v>6.9486100671906234E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1970080039879194E-2</v>
+        <v>6.1924769395230533E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9316949191946179E-2</v>
+        <v>7.9258905364961857E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.5650206345323813E-2</v>
+        <v>9.5580108233284874E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.8428667919712681E-2</v>
+        <v>3.8400490115042867E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.78635153926608E-2</v>
+        <v>3.7835751985844934E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6284860082524191E-2</v>
+        <v>1.627291921568386E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2452729314474794E-2</v>
+        <v>1.2443598355916397E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.355003051680486E-3</v>
+        <v>6.3503432483523964E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3043138015448391E-4</v>
+        <v>3.3018909148327044E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>2419779.3955266764</v>
+        <v>2419782.4184664874</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>30247242.444083456</v>
+        <v>30247280.230831094</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>14105728.260390403</v>
+        <v>14105557.81087199</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>42978405.904473864</v>
+        <v>42978273.241703086</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0845693199999999</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>24.126618126995176</v>
+        <v>24.108879276748851</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2551045.3172486676</v>
+        <v>2551048.5041740807</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2362078.9974524695</v>
+        <v>2362081.9483093335</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2689432.0295011415</v>
+        <v>2689435.3893078938</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2305754.4834543392</v>
+        <v>2305757.3639470967</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2835325.8142460412</v>
+        <v>2835329.356312437</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2250773.0451452718</v>
+        <v>2250775.8569517769</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2989133.9081066614</v>
+        <v>2989137.6423197505</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>2197102.6564645264</v>
+        <v>2197105.4012226234</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15670,7 +15670,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>3151285.6390964515</v>
+        <v>3151289.5758796278</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -15682,7 +15682,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>2144712.0550228166</v>
+        <v>2144714.7343312968</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15692,7 +15692,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>3322233.6250120173</v>
+        <v>3322237.7753541125</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>2093570.7238923267</v>
+        <v>2093573.3393118563</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>3502455.0368354185</v>
+        <v>3502459.4123213771</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>2043648.8738309499</v>
+        <v>2043651.4268849813</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>3692452.9306723336</v>
+        <v>3692457.5435155476</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1994917.4259303929</v>
+        <v>1994919.9181060505</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15758,7 +15758,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>3892757.65194395</v>
+        <v>3892762.5150203537</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -15770,7 +15770,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1947347.9946780447</v>
+        <v>1947350.4274269929</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>4103928.315752143</v>
+        <v>4103933.4426361518</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -15792,7 +15792,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1900912.8714227385</v>
+        <v>1900915.2461620255</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>4326554.3675501132</v>
+        <v>4326559.7725525144</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>1855585.0082347796</v>
+        <v>1855587.3263476642</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15824,7 +15824,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>4561257.2284748219</v>
+        <v>4561262.92668272</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
@@ -15836,7 +15836,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>1811338.0021508334</v>
+        <v>1811340.2649875893</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15846,7 +15846,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>4808692.0299338717</v>
+        <v>4808698.0372528043</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>1768146.0797945012</v>
+        <v>1768148.2886732055</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>5069549.4422886344</v>
+        <v>5069555.7754869675</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>1725984.0823636216</v>
+        <v>1725986.2385709211</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15890,7 +15890,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>5344557.6027380656</v>
+        <v>5344564.2794937976</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
@@ -15902,7 +15902,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>1684827.4509755573</v>
+        <v>1684829.5557674179</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>5634484.1477845358</v>
+        <v>5634491.1867346475</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>1644652.2123619227</v>
+        <v>1644654.266964362</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>5940138.3559549889</v>
+        <v>5940145.7767474595</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>1605434.964904432</v>
+        <v>1605436.9705142318</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>6262373.4067583997</v>
+        <v>6262381.230107056</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
@@ -15968,7 +15968,7 @@
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>1567152.8650037202</v>
+        <v>1567154.8227891258</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15978,7 +15978,7 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>6602088.7621850483</v>
+        <v>6602097.0099273808</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
@@ -15990,7 +15990,7 @@
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>1529783.6137732102</v>
+        <v>1529785.5248746092</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -16000,7 +16000,7 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>6960232.6773951342</v>
+        <v>6960241.3725532526</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>1493305.4440502629</v>
+        <v>1493307.3095808504</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>31888066.465608343</v>
+        <v>31888106.302176006</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>6841527.497777679</v>
+        <v>6841536.0446418598</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>44768556.348684393</v>
+        <v>44768612.276365869</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16286,7 +16286,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>44768556.348684393</v>
+        <v>44768612.276365869</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16316,19 +16316,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>30247242.444083448</v>
+        <v>30247280.230831087</v>
       </c>
       <c r="C56" s="124">
-        <v>31223176.821531951</v>
+        <v>31223215.82747788</v>
       </c>
       <c r="D56" s="124">
-        <v>32742281.68967643</v>
+        <v>32742322.593383193</v>
       </c>
       <c r="E56" s="124">
-        <v>33264014.657150343</v>
+        <v>33264056.212638572</v>
       </c>
       <c r="F56" s="124">
-        <v>35432228.168392017</v>
+        <v>35432272.43254821</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16337,19 +16337,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>30247242.444083445</v>
+        <v>30247280.230831083</v>
       </c>
       <c r="C57" s="124">
-        <v>32200009.880320154</v>
+        <v>32200050.106587049</v>
       </c>
       <c r="D57" s="124">
-        <v>35503356.807945192</v>
+        <v>35503401.160959736</v>
       </c>
       <c r="E57" s="124">
-        <v>36716128.679334238</v>
+        <v>36716174.54741928</v>
       </c>
       <c r="F57" s="124">
-        <v>42215869.175015226</v>
+        <v>42215921.913720168</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16358,19 +16358,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>30247242.444083445</v>
+        <v>30247280.230831072</v>
       </c>
       <c r="C58" s="124">
-        <v>33409111.640997365</v>
+        <v>33409153.377749823</v>
       </c>
       <c r="D58" s="124">
-        <v>39199886.948569477</v>
+        <v>39199935.919520751</v>
       </c>
       <c r="E58" s="124">
-        <v>41464644.703352071</v>
+        <v>41464696.503580414</v>
       </c>
       <c r="F58" s="124">
-        <v>52656648.511844084</v>
+        <v>52656714.293823779</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16379,19 +16379,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>30247242.444083445</v>
+        <v>30247280.230831075</v>
       </c>
       <c r="C59" s="124">
-        <v>34640992.434448197</v>
+        <v>34641035.710143216</v>
       </c>
       <c r="D59" s="124">
-        <v>43294295.85895744</v>
+        <v>43294349.944900468</v>
       </c>
       <c r="E59" s="124">
-        <v>46881410.773379974</v>
+        <v>46881469.340571389</v>
       </c>
       <c r="F59" s="124">
-        <v>66146014.801259257</v>
+        <v>66146097.434999272</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16400,19 +16400,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>30247242.444083445</v>
+        <v>30247280.230831072</v>
       </c>
       <c r="C60" s="124">
-        <v>35786709.929434538</v>
+        <v>35786754.63643153</v>
       </c>
       <c r="D60" s="124">
-        <v>47452089.597804815</v>
+        <v>47452148.877923906</v>
       </c>
       <c r="E60" s="124">
-        <v>52558016.918550044</v>
+        <v>52558082.577313013</v>
       </c>
       <c r="F60" s="124">
-        <v>82323567.957073689</v>
+        <v>82323670.800825238</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16421,19 +16421,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>30247242.444083441</v>
+        <v>30247280.230831072</v>
       </c>
       <c r="C61" s="124">
-        <v>36797392.138687372</v>
+        <v>36797438.108291812</v>
       </c>
       <c r="D61" s="124">
-        <v>51472866.922691472</v>
+        <v>51472931.225817151</v>
       </c>
       <c r="E61" s="124">
-        <v>58233901.678193495</v>
+        <v>58233974.427626796</v>
       </c>
       <c r="F61" s="124">
-        <v>101002962.01554288</v>
+        <v>101003088.19476216</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16483,23 +16483,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16510,23 +16510,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.033541561720526</v>
+        <v>18.020262851044688</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.443039140489436</v>
+        <v>18.429460677080225</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.080448560401027</v>
+        <v>19.066403512509268</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.299365315340072</v>
+        <v>19.285160020113345</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.209137738183479</v>
+        <v>20.194266488419697</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16537,23 +16537,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720526</v>
+        <v>18.020262851044688</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.852913801817579</v>
+        <v>18.8390353096501</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.23898298838801</v>
+        <v>20.224089891864217</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.747856490960228</v>
+        <v>20.732590898404112</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>23.055522322680066</v>
+        <v>23.038567515885255</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16564,23 +16564,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720526</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.360247342805245</v>
+        <v>19.345997481859225</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.790030043815481</v>
+        <v>21.774001578931635</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.740311987470566</v>
+        <v>22.723587915030407</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.436425340022005</v>
+        <v>27.416263706808259</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16591,23 +16591,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720526</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.877138861237952</v>
+        <v>19.862510635062101</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.508025202134604</v>
+        <v>23.490739162673211</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>25.013162131589045</v>
+        <v>24.994774330036513</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>33.096501429445276</v>
+        <v>33.072196613544108</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16618,23 +16618,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720526</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.357876655695701</v>
+        <v>20.34289652886061</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.252616343118742</v>
+        <v>25.23405326078765</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.395039976848693</v>
+        <v>27.37490863777191</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.884528371411356</v>
+        <v>39.855254711405728</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16644,23 +16644,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>18.033541561720526</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.781954264966807</v>
+        <v>20.76666371279801</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.939716026618619</v>
+        <v>26.919917985235706</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.776615132057305</v>
+        <v>29.754740477025763</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.722316256096363</v>
+        <v>47.687305325679802</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.722316256096363</v>
+        <v>47.687305325679802</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16717,7 +16717,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>25.013162131589045</v>
+        <v>24.994774330036513</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.508025202134604</v>
+        <v>23.490739162673211</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16763,7 +16763,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.877138861237952</v>
+        <v>19.862510635062101</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>18.033541561720526</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="I5" s="262">
         <f t="shared" si="0"/>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16936,7 +16936,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>24.669312045872232</v>
+        <v>24.651966296664508</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16970,7 +16970,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2532260.8774667676</v>
+        <v>2532264.9080531825</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>2419779.3955266764</v>
+        <v>2419782.4184664874</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.10082691102476438</v>
+        <v>-0.10082655111598315</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>18.033541561720529</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.508025202134604</v>
+        <v>23.490739162673211</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.877138861237952</v>
+        <v>19.862510635062101</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>25.013162131589045</v>
+        <v>24.994774330036513</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.158132166318886</v>
+        <v>23.141102248991814</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17406,7 +17406,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>18.033541561720526</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17464,7 +17464,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.722316256096363</v>
+        <v>47.687305325679802</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17490,7 +17490,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.13011184057784</v>
+        <v>24.112370432928852</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17552,7 +17552,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.126618126995176</v>
+        <v>24.108879276748851</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>0.2213805598098644</v>
+        <v>0.22137803669855524</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.53920020529439283</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.85674668188176095</v>
+        <v>0.85737535199980497</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17687,7 +17687,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7937725366537336</v>
+        <v>8.7873070090848611</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.6505192185354947</v>
+        <v>9.6446823610846657</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.60006322049834337</v>
+        <v>0.60001102388865557</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19513328682324205</v>
+        <v>0.19487700460896318</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.1358152472636516</v>
+        <v>1.1063878035577037</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.964185092926991</v>
+        <v>13.364109171628439</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>15.100000340190643</v>
+        <v>14.470496975186142</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17797,7 +17797,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.3742258452860513</v>
+        <v>0.39987248390043673</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.3895712245876182</v>
+        <v>1.3905908747645801</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>19.155260758473236</v>
+        <v>19.141177057080387</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17848,7 +17848,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.544831983060856</v>
+        <v>20.531767931844968</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="F99" s="325">
         <f>(1-C99/C60)</f>
-        <v>0.14858115375527936</v>
+        <v>0.14849649523441566</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17884,7 +17884,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.3008761008000136</v>
+        <v>1.3018306675922122</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>17.295508446343714</v>
+        <v>17.282792108024591</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>18.596384547143728</v>
+        <v>18.584622775616804</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>0.22921710580164945</v>
+        <v>0.22913783912219288</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F947C95-46E1-4616-95B2-6DBC27701E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7295D91-99A0-46D4-A50B-4767A2213BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3114,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3748,7 +3748,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3812,9 +3811,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3833,29 +3829,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4163,7 +4169,7 @@
         <v>45778</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4197,7 +4203,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>446</v>
       </c>
     </row>
@@ -4305,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4350,7 +4356,7 @@
       <c r="D22" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>443</v>
       </c>
     </row>
@@ -4381,7 +4387,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4391,16 +4397,16 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
-        <v>24.112370432928852</v>
+        <v>24.112370432928856</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19487700460896318</v>
+        <v>0.19487700460896362</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4411,18 +4417,18 @@
       <c r="B28" s="45" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>2331.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>433</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4430,18 +4436,18 @@
       <c r="B29" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
-        <v>9.6446823610846657</v>
-      </c>
-      <c r="D29" s="339" t="str">
+        <v>9.6446823610846675</v>
+      </c>
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>428</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4449,18 +4455,18 @@
       <c r="B30" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
-        <v>14.470496975186142</v>
-      </c>
-      <c r="D30" s="148" t="str">
+        <v>14.470496975186144</v>
+      </c>
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4468,18 +4474,18 @@
       <c r="B31" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
-        <v>20.531767931844968</v>
-      </c>
-      <c r="D31" s="148" t="str">
+        <v>20.531767931844971</v>
+      </c>
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4487,18 +4493,18 @@
       <c r="B32" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
-        <v>18.584622775616804</v>
-      </c>
-      <c r="D32" s="148" t="str">
+        <v>18.584622775616808</v>
+      </c>
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>442</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4526,13 +4532,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4639,7 +4645,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>95973.634053182453</v>
       </c>
@@ -4647,14 +4653,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-254421</v>
       </c>
@@ -4662,8 +4668,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4722,10 +4728,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4799,7 +4805,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5313865427726264E-2</v>
+        <v>3.5313865427726257E-2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4826,13 +4832,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4870,7 +4876,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4907,7 +4913,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.682313624454611</v>
+        <v>12.682313624454613</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4974,7 +4980,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.81179849779954893</v>
+        <v>0.81179849779954916</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -4982,28 +4988,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.36794481423679237</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>7.4171010848313429E-2</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>0.60402076709908736</v>
       </c>
@@ -5045,7 +5051,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9142873884908846</v>
+        <v>5.9142873884908855</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5076,7 +5082,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23546033589874468</v>
+        <v>0.23546033589874474</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5098,7 +5104,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5106,12 +5112,12 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>4.568982245212033</v>
+        <v>4.5689822452120339</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5270,7 +5276,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>24.112370432928852</v>
+        <v>24.112370432928856</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5278,13 +5284,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5297,13 +5303,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5343,7 +5349,7 @@
       </c>
       <c r="C138" s="237">
         <f>Scenarios!C77</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
       <c r="D138" s="236" t="str">
         <f>Market_currency</f>
@@ -5367,7 +5373,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5379,7 +5385,7 @@
       </c>
       <c r="C142" s="240">
         <f>Scenarios!C81</f>
-        <v>0.85737535199980497</v>
+        <v>0.85737535199980486</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5389,7 +5395,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>8.7873070090848611</v>
+        <v>8.7873070090848628</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5398,9 +5404,9 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>9.6446823610846657</v>
-      </c>
-      <c r="D144" s="336" t="str">
+        <v>9.6446823610846675</v>
+      </c>
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5409,11 +5415,11 @@
       <c r="B145" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5436,7 +5442,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5458,7 +5464,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>13.364109171628439</v>
+        <v>13.36410917162844</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5467,9 +5473,9 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>14.470496975186142</v>
-      </c>
-      <c r="D152" s="336" t="str">
+        <v>14.470496975186144</v>
+      </c>
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5478,11 +5484,11 @@
       <c r="B153" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5517,7 +5523,7 @@
       </c>
       <c r="C158" s="240">
         <f>Scenarios!C97</f>
-        <v>1.3905908747645801</v>
+        <v>1.3905908747645797</v>
       </c>
     </row>
     <row r="159" spans="2:4">
@@ -5527,7 +5533,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>19.141177057080387</v>
+        <v>19.141177057080391</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5536,9 +5542,9 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>20.531767931844968</v>
-      </c>
-      <c r="D160" s="336" t="str">
+        <v>20.531767931844971</v>
+      </c>
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5547,11 +5553,11 @@
       <c r="B161" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5586,7 +5592,7 @@
       </c>
       <c r="C166" s="240">
         <f>Scenarios!C103</f>
-        <v>1.3018306675922122</v>
+        <v>1.3018306675922118</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5596,7 +5602,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>17.282792108024591</v>
+        <v>17.282792108024594</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5605,9 +5611,9 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>18.584622775616804</v>
-      </c>
-      <c r="D168" s="336" t="str">
+        <v>18.584622775616808</v>
+      </c>
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5616,11 +5622,11 @@
       <c r="B169" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5645,7 +5651,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5659,13 +5665,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5702,22 +5708,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5741,6 +5747,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5757,17 +5774,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6455,7 +6461,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7831,7 +7837,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -8226,11 +8232,11 @@
         <f t="shared" si="40"/>
         <v>686606</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8260,11 +8266,11 @@
         <f t="shared" si="40"/>
         <v>1407257</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9182,11 +9188,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.944956641615036</v>
+        <v>10.944956641615038</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.568982245212033</v>
+        <v>4.5689822452120339</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9488,7 +9494,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
@@ -9592,11 +9598,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-2098335.0572062195</v>
+        <v>-2098335.05720622</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.81179849779954882</v>
+        <v>-0.81179849779954905</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9609,7 +9615,7 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>15287237.657253448</v>
+        <v>15287237.65725345</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
@@ -9626,11 +9632,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>608617.38317713188</v>
+        <v>608617.383177132</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23546033589874468</v>
+        <v>0.23546033589874474</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9643,7 +9649,7 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13797519.98322436</v>
+        <v>13797519.983224362</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
@@ -11559,104 +11565,104 @@
         <v>95973.634053182453</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>95973.634053182453</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>111844.89463273335</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>100045.40527337021</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>32420.665572934322</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>429525</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>429525</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>500556</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>447748</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>145097</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13160,12 +13166,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
       <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13216,12 +13222,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1394746.2586701883</v>
+        <v>1394746.258670188</v>
       </c>
       <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1394746.2586701883</v>
+        <v>1394746.258670188</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13271,12 +13277,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.57639325256115159</v>
+        <v>0.57639325256115148</v>
       </c>
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55079002762885343</v>
+        <v>0.55079002762885332</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13326,12 +13332,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5313865427726264E-2</v>
+        <v>3.5313865427726257E-2</v>
       </c>
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5313865427726264E-2</v>
+        <v>3.5313865427726257E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14020,47 +14026,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>0</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4709732968262565</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.96304737643927274</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.6269053137360105</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.6269426147081751</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.3369811952562229</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>2.3374185439481701</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.250085896477759</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.4203453141742608</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>11.152390228065904</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14072,47 +14078,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>0</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.0773328106076989</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.3549323555766097</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.8733723206359201</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.9746300057985322</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.5408832696503736</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.8191980169637287</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>2.5561117493864103</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>4.3015244745575218</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>57.096567771960444</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -14468,50 +14474,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0145850899563689</v>
+        <v>1.0145850899563691</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0617476182667271</v>
+        <v>1.0617476182667274</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.94621047635912248</v>
+        <v>0.9462104763591227</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2110760739766171</v>
+        <v>1.2110760739766175</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.4604640538045928</v>
+        <v>1.460464053804593</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58675948895785501</v>
+        <v>0.58675948895785512</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57813029034371055</v>
+        <v>0.57813029034371066</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24865020561564935</v>
+        <v>0.24865020561564941</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19013818287840253</v>
+        <v>0.19013818287840256</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.7033244834824617E-2</v>
+        <v>9.7033244834824631E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0452893178643725E-3</v>
+        <v>5.0452893178643734E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14532,43 +14538,43 @@
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9486100671906234E-2</v>
+        <v>6.9486100671906248E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1924769395230533E-2</v>
+        <v>6.1924769395230547E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9258905364961857E-2</v>
+        <v>7.9258905364961885E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.5580108233284874E-2</v>
+        <v>9.5580108233284888E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.8400490115042867E-2</v>
+        <v>3.8400490115042873E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7835751985844934E-2</v>
+        <v>3.7835751985844941E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.627291921568386E-2</v>
+        <v>1.6272919215683863E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2443598355916397E-2</v>
+        <v>1.2443598355916399E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.3503432483523964E-3</v>
+        <v>6.3503432483523973E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3018909148327044E-4</v>
+        <v>3.3018909148327055E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15406,10 +15412,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15424,8 +15430,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15440,8 +15446,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15456,8 +15462,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15480,7 +15486,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>1.0837740599999999</v>
+        <v>1.0837740600000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15494,7 +15500,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15547,7 +15553,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>24.108879276748851</v>
+        <v>24.108879276748858</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16483,23 +16489,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16510,23 +16516,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.020262851044688</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.429460677080225</v>
+        <v>18.429460677080229</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.066403512509268</v>
+        <v>19.066403512509272</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.285160020113345</v>
+        <v>19.285160020113349</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.194266488419697</v>
+        <v>20.1942664884197</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16537,23 +16543,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044688</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.8390353096501</v>
+        <v>18.839035309650104</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.224089891864217</v>
+        <v>20.224089891864224</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.732590898404112</v>
+        <v>20.732590898404116</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>23.038567515885255</v>
+        <v>23.038567515885259</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16564,23 +16570,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044681</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.345997481859225</v>
+        <v>19.345997481859229</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.774001578931635</v>
+        <v>21.774001578931642</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.723587915030407</v>
+        <v>22.723587915030411</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.416263706808259</v>
+        <v>27.416263706808262</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16591,23 +16597,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044684</v>
+        <v>18.020262851044688</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.862510635062101</v>
+        <v>19.862510635062108</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.490739162673211</v>
+        <v>23.490739162673215</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.994774330036513</v>
+        <v>24.994774330036517</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>33.072196613544108</v>
+        <v>33.072196613544115</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16618,23 +16624,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044681</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.34289652886061</v>
+        <v>20.342896528860614</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.23405326078765</v>
+        <v>25.234053260787658</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.37490863777191</v>
+        <v>27.374908637771913</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.855254711405728</v>
+        <v>39.855254711405735</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16644,23 +16650,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044681</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.76666371279801</v>
+        <v>20.766663712798017</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.919917985235706</v>
+        <v>26.91991798523571</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.754740477025763</v>
+        <v>29.75474047702577</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.687305325679802</v>
+        <v>47.687305325679809</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16695,7 +16701,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.687305325679802</v>
+        <v>47.687305325679809</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16717,7 +16723,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.994774330036513</v>
+        <v>24.994774330036517</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16740,7 +16746,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.490739162673211</v>
+        <v>23.490739162673215</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16763,7 +16769,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.862510635062101</v>
+        <v>19.862510635062108</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16786,7 +16792,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>18.020262851044681</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16907,7 +16913,7 @@
       </c>
       <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16916,7 +16922,7 @@
       </c>
       <c r="I5" s="262">
         <f t="shared" si="0"/>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16936,7 +16942,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>24.651966296664508</v>
+        <v>24.651966296664511</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16951,11 +16957,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16976,8 +16982,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16998,8 +17004,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -17009,8 +17015,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -17023,8 +17029,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -17042,8 +17048,8 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -17060,8 +17066,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17078,8 +17084,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.10082655111598315</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17105,21 +17111,21 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17133,8 +17139,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17142,14 +17148,14 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044695</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17169,8 +17175,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17180,8 +17186,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17189,14 +17195,14 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>23.490739162673211</v>
+        <v>23.490739162673215</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17206,8 +17212,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17227,8 +17233,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17238,8 +17244,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17247,14 +17253,14 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>19.862510635062101</v>
+        <v>19.862510635062108</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17264,8 +17270,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17285,8 +17291,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17296,8 +17302,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17305,14 +17311,14 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>24.994774330036513</v>
+        <v>24.994774330036517</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17323,8 +17329,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17332,7 +17338,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.141102248991814</v>
+        <v>23.141102248991817</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17386,8 +17392,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17397,8 +17403,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17406,14 +17412,14 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>18.020262851044681</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17423,8 +17429,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17444,8 +17450,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17455,8 +17461,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17464,14 +17470,14 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>47.687305325679802</v>
+        <v>47.687305325679809</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17481,8 +17487,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17490,7 +17496,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.112370432928852</v>
+        <v>24.112370432928856</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17499,7 +17505,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17552,7 +17558,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>24.108879276748851</v>
+        <v>24.108879276748858</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17613,9 +17619,9 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
-        <v>0.22137803669855524</v>
+        <v>0.22137803669855521</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17648,7 +17654,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.53959586373565727</v>
+        <v>0.53959586373565716</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17675,7 +17681,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.85737535199980497</v>
+        <v>0.85737535199980486</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17687,7 +17693,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7873070090848611</v>
+        <v>8.7873070090848628</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17697,7 +17703,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.6446823610846657</v>
+        <v>9.6446823610846675</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17706,7 +17712,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.60001102388865557</v>
       </c>
@@ -17738,7 +17744,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19487700460896318</v>
+        <v>0.19487700460896362</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17776,7 +17782,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.364109171628439</v>
+        <v>13.36410917162844</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17786,7 +17792,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.470496975186142</v>
+        <v>14.470496975186144</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17795,7 +17801,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.39987248390043673</v>
       </c>
@@ -17805,7 +17811,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17816,7 +17822,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17824,11 +17830,11 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.3905908747645801</v>
+        <v>1.3905908747645797</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17836,11 +17842,11 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>19.141177057080387</v>
+        <v>19.141177057080391</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17848,7 +17854,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.531767931844968</v>
+        <v>20.531767931844971</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17856,7 +17862,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>0.14849649523441566</v>
       </c>
@@ -17884,7 +17890,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.3018306675922122</v>
+        <v>1.3018306675922118</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -17894,7 +17900,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>17.282792108024591</v>
+        <v>17.282792108024594</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17904,7 +17910,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>18.584622775616804</v>
+        <v>18.584622775616808</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17912,7 +17918,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.22913783912219288</v>
       </c>
@@ -17921,32 +17927,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7295D91-99A0-46D4-A50B-4767A2213BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF94956-0086-4EE5-911B-42388EA940B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4912,7 +4912,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>12.682313624454613</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4966,7 +4966,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>1936137</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5037,7 +5037,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>14105557.81087199</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5068,7 +5068,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>561572.19999999995</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5103,7 +5103,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>18.020262851044695</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5162,111 +5162,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.1</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>30</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>47.69 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.06</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>20</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>24.99 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.05</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>20</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>23.49 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.495</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.02</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>20</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>19.86 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>30</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>18.02 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-2098335.05720622</v>
       </c>
       <c r="D86" s="248">
@@ -9614,7 +9614,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>15287237.65725345</v>
       </c>
       <c r="D87" s="248">
@@ -9631,7 +9631,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>608617.383177132</v>
       </c>
       <c r="D88" s="248">
@@ -15591,7 +15591,7 @@
         <v>2551048.5041740807</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15613,7 +15613,7 @@
         <v>2689435.3893078938</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15635,7 +15635,7 @@
         <v>2835329.356312437</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15657,7 +15657,7 @@
         <v>2989137.6423197505</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15679,7 +15679,7 @@
         <v>3151289.5758796278</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15701,7 +15701,7 @@
         <v>3322237.7753541125</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15723,7 +15723,7 @@
         <v>3502459.4123213771</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15745,7 +15745,7 @@
         <v>3692457.5435155476</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15767,7 +15767,7 @@
         <v>3892762.5150203537</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15789,7 +15789,7 @@
         <v>4103933.4426361518</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15811,7 +15811,7 @@
         <v>4326559.7725525144</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E31" s="125">
@@ -15833,7 +15833,7 @@
         <v>4561262.92668272</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E32" s="125">
@@ -15855,7 +15855,7 @@
         <v>4808698.0372528043</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E33" s="125">
@@ -15877,7 +15877,7 @@
         <v>5069555.7754869675</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E34" s="125">
@@ -15899,7 +15899,7 @@
         <v>5344564.2794937976</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E35" s="125">
@@ -15921,7 +15921,7 @@
         <v>5634491.1867346475</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E36" s="125">
@@ -15943,7 +15943,7 @@
         <v>5940145.7767474595</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E37" s="125">
@@ -15965,7 +15965,7 @@
         <v>6262381.230107056</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E38" s="125">
@@ -15987,7 +15987,7 @@
         <v>6602097.0099273808</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E39" s="125">
@@ -16009,7 +16009,7 @@
         <v>6960241.3725532526</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="E40" s="125">
@@ -16031,7 +16031,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -16053,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16075,7 +16075,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16097,7 +16097,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16119,7 +16119,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16141,7 +16141,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16163,7 +16163,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16185,7 +16185,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16207,7 +16207,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16229,7 +16229,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16930,7 +16930,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17147,7 +17147,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>18.020262851044695</v>
       </c>
       <c r="D22" t="str">
@@ -17194,7 +17194,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>23.490739162673215</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17252,7 +17252,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>19.862510635062108</v>
       </c>
       <c r="D33" t="str">
@@ -17310,7 +17310,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>24.994774330036517</v>
       </c>
       <c r="D39" t="str">
@@ -17411,7 +17411,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>18.020262851044684</v>
       </c>
       <c r="D51" t="str">
@@ -17469,7 +17469,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>47.687305325679809</v>
       </c>
       <c r="D57" t="str">
@@ -17557,7 +17557,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>24.108879276748858</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF94956-0086-4EE5-911B-42388EA940B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF975D9-8096-4F86-B7BC-E311AA7C8047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF975D9-8096-4F86-B7BC-E311AA7C8047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91492752-B975-4331-A6C8-242E4151C85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="462">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2410,28 +2405,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>李宁</t>
+  </si>
+  <si>
+    <t>2331.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>李宁</t>
-  </si>
-  <si>
-    <t>2331.HK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CNS_02</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2447,7 +2472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2466,6 +2491,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3114,7 +3140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3620,9 +3646,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3839,29 +3862,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3880,7 +3910,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3927,8 +3971,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4169,15 +4213,15 @@
         <v>45778</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>445</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4192,7 +4236,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4201,10 +4245,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>446</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4218,9 +4262,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4241,20 +4285,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4270,17 +4314,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4294,7 +4338,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4321,73 +4365,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>443</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>450</v>
+        <v>436</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>450</v>
+        <v>437</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4397,14 +4445,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>24.112370432928856</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.19487700460896362</v>
       </c>
@@ -4415,96 +4463,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>437</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>435</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>2331.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>433</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C29" s="345">
+        <v>427</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>9.6446823610846675</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>428</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C30" s="346">
+        <v>428</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>14.470496975186144</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C31" s="346">
+        <v>429</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>20.531767931844971</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C32" s="346">
+        <v>430</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>18.584622775616808</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>442</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4513,8 +4561,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4523,22 +4571,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4550,13 +4598,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4576,13 +4624,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4611,13 +4659,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4633,19 +4681,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>95973.634053182453</v>
       </c>
@@ -4653,14 +4701,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-254421</v>
       </c>
@@ -4668,8 +4716,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4703,13 +4751,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4725,13 +4773,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4747,22 +4795,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4791,26 +4839,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>6.6399547772013678E-2</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.5313865427726257E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.57639325256115148</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4823,22 +4879,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4847,7 +4903,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4856,7 +4912,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4867,7 +4923,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4876,42 +4932,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>12.682313624454613</v>
       </c>
@@ -4921,8 +4977,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4934,13 +4990,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4953,13 +5009,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4976,9 +5032,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.81179849779954916</v>
       </c>
@@ -4988,28 +5044,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.36794481423679237</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>7.4171010848313429E-2</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>0.60402076709908736</v>
       </c>
@@ -5047,9 +5103,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>5.9142873884908855</v>
       </c>
@@ -5078,9 +5134,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.23546033589874474</v>
       </c>
@@ -5090,20 +5146,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>451</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>18.020262851044695</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5112,10 +5168,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>4.5689822452120339</v>
       </c>
@@ -5125,8 +5181,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5135,49 +5191,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>30</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>47.69 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5195,11 +5251,11 @@
         <f>DCF!D75</f>
         <v>20</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>24.99 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.22499999999999992</v>
       </c>
@@ -5217,11 +5273,11 @@
         <f>DCF!D76</f>
         <v>20</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>23.49 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.495</v>
       </c>
@@ -5239,11 +5295,11 @@
         <f>DCF!D77</f>
         <v>20</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>19.86 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5261,11 +5317,11 @@
         <f>DCF!D78</f>
         <v>30</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>18.02 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5284,17 +5340,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5303,22 +5359,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5329,7 +5385,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5338,7 +5394,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5358,22 +5414,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>2331.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5406,20 +5462,20 @@
         <f>Scenarios!C83</f>
         <v>9.6446823610846675</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5435,14 +5491,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5475,20 +5531,20 @@
         <f>Scenarios!C93</f>
         <v>14.470496975186144</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5504,12 +5560,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5538,26 +5594,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>20.531767931844971</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5573,12 +5629,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5607,26 +5663,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>18.584622775616808</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5641,8 +5697,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5651,113 +5707,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5774,6 +5819,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5786,7 +5842,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6354,7 +6410,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181">
@@ -6388,7 +6444,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181">
@@ -6422,7 +6478,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181">
@@ -6479,7 +6535,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7784,7 +7840,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8232,11 +8288,11 @@
         <f t="shared" si="40"/>
         <v>686606</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8266,11 +8322,11 @@
         <f t="shared" si="40"/>
         <v>1407257</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8373,17 +8429,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8468,7 +8524,7 @@
         <f>1004591+245432</f>
         <v>1250023</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8479,7 +8535,7 @@
         <f>8264361+7498596</f>
         <v>15762957</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8490,7 +8546,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8500,7 +8556,7 @@
       <c r="G5" s="19">
         <v>23261</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8511,7 +8567,7 @@
       <c r="C6" s="19">
         <v>2598226</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8521,7 +8577,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8532,7 +8588,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8542,7 +8598,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8553,7 +8609,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8563,7 +8619,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8574,7 +8630,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8584,7 +8640,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8595,10 +8651,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8607,10 +8663,10 @@
       <c r="C11" s="19">
         <v>893775</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8668,7 +8724,7 @@
       <c r="C15" s="19">
         <v>166519</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8677,7 +8733,7 @@
       <c r="G15" s="19">
         <v>2377970</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8688,7 +8744,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8697,7 +8753,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8708,7 +8764,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8717,7 +8773,7 @@
       <c r="G17" s="19">
         <v>450316</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8728,7 +8784,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8737,7 +8793,7 @@
       <c r="G18" s="19">
         <v>1743938</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8749,7 +8805,7 @@
         <f>4610454+1576667+150864</f>
         <v>6337985</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8758,7 +8814,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8769,7 +8825,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8778,7 +8834,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8789,7 +8845,7 @@
       <c r="C21" s="19">
         <v>234736</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8798,7 +8854,7 @@
       <c r="G21" s="19">
         <v>2913826</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8809,10 +8865,10 @@
       <c r="C22" s="19">
         <v>949424</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8821,10 +8877,10 @@
       <c r="C23" s="19">
         <v>5450</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9157,13 +9213,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9179,7 +9235,7 @@
         <f>H29</f>
         <v>10897009.050000001</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9194,23 +9250,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>4.5689822452120339</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9224,7 +9280,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.54859123183168057</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9235,22 +9291,22 @@
         <f>G29/G32</f>
         <v>0.73102364188421065</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9264,7 +9320,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.28379300712166428</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9278,22 +9334,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>1.1013064992204455E-2</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9315,22 +9371,22 @@
         <f>G39/G32</f>
         <v>0.17749280099481338</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9344,7 +9400,7 @@
         <f>G28/G29</f>
         <v>0</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9363,13 +9419,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9397,7 +9453,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9407,7 +9463,7 @@
         <f>G18</f>
         <v>1743938</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9417,7 +9473,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9427,26 +9483,26 @@
         <f>SUM(C66:C69)</f>
         <v>19908126</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9457,65 +9513,65 @@
         <v>-2029315.0945640046</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>8.2125553905322963</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>8.9508958212832646</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>4058630.1891280091</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9529,7 +9585,7 @@
         <f>G7*H7+G17*H17</f>
         <v>270189.59999999998</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9543,7 +9599,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9557,7 +9613,7 @@
         <f>G9*H9+G21*H21</f>
         <v>291382.60000000003</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9571,11 +9627,11 @@
         <f>SUM(D79:D81)</f>
         <v>561572.19999999995</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9586,76 +9642,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-2098335.05720622</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.81179849779954905</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>15287237.65725345</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>5.9142873884908855</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>608617.383177132</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>0.23546033589874474</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>13797519.983224362</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>5.3379492265900819</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9776,7 +9832,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9790,7 +9846,7 @@
         <v>26162449.5</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9846,7 +9902,7 @@
         <f>C25</f>
         <v>-21529127.876097865</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-23718447</v>
@@ -9901,7 +9957,7 @@
         <f>C4+C5</f>
         <v>4633321.6239021346</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>4957196</v>
@@ -9956,7 +10012,7 @@
         <f>C35</f>
         <v>-1427907</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1427907</v>
@@ -10012,7 +10068,7 @@
         <v>3205414.6239021346</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10068,7 +10124,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10123,7 +10179,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>1815.2739999999999</v>
@@ -10179,7 +10235,7 @@
         <v>179409.3</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10235,7 +10291,7 @@
         <f>C50</f>
         <v>-158447.36594681756</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-158447.36594681756</v>
@@ -10290,7 +10346,7 @@
         <f>SUM(C8:C12)</f>
         <v>3226376.5579553167</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3628955.9080531825</v>
@@ -10345,7 +10401,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-806594.13948882918</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-1096691</v>
@@ -10401,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10458,7 +10514,7 @@
         <v>2419782.4184664874</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10515,8 +10571,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10540,8 +10596,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10566,7 +10622,7 @@
         <v>2419782.4184664874</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10662,7 +10718,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10686,7 +10742,7 @@
         <v>-13136432.380387567</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10743,7 +10799,7 @@
         <v>-8392695.4957102966</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10800,7 +10856,7 @@
         <v>-21529127.876097865</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10849,14 +10905,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10868,8 +10924,8 @@
         <v>0.50211018583667277</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10928,8 +10984,8 @@
         <v>0.32079165583139668</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10986,7 +11042,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.82290184166806957</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.82712868897133363</v>
@@ -11034,14 +11090,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -11052,8 +11108,8 @@
         <f>G33</f>
         <v>-1427907</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11110,8 +11166,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11169,7 +11225,7 @@
         <v>-1427907</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11218,14 +11274,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11238,7 +11294,7 @@
         <v>5.4578490442953362E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11296,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11352,7 +11408,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>5.4578490442953362E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>4.9795117061542438E-2</v>
@@ -11400,26 +11456,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11498,7 +11554,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11509,7 +11565,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-254421</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-254421</v>
@@ -11558,111 +11614,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>95973.634053182453</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>95973.634053182453</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>111844.89463273335</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>100045.40527337021</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>32420.665572934322</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>429525</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>429525</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>500556</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>447748</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>145097</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11676,7 +11732,7 @@
         <f>C47+C48</f>
         <v>-158447.36594681756</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-158447.36594681756</v>
@@ -11724,14 +11780,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11745,8 +11801,8 @@
         <f>G53</f>
         <v>2.3646804360316024E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11772,8 +11828,8 @@
         <f>G54</f>
         <v>0.13140650687425529</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11799,7 +11855,7 @@
         <f>-C8/C47</f>
         <v>12.598860250931073</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>13.871846270551567</v>
@@ -11847,14 +11903,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11868,7 +11924,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11923,7 +11979,7 @@
         <f>BS!$C68*C67</f>
         <v>179409.3</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>256299</v>
@@ -11978,7 +12034,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -12033,7 +12089,7 @@
         <f>SUM(C58:C60)</f>
         <v>179409.3</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>256299</v>
@@ -12084,11 +12140,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12144,7 +12200,7 @@
         <f>C61+C62</f>
         <v>179409.3</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>405216</v>
@@ -12192,14 +12248,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12213,7 +12269,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12238,7 +12294,7 @@
         <f>G67*0.7</f>
         <v>0.10287596233352332</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0.1469656604764619</v>
@@ -12263,7 +12319,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12289,7 +12345,7 @@
         <v>9.0118627941173368E-3</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12317,7 +12373,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12339,7 +12395,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12363,7 +12419,7 @@
         <v>0.82290184166806957</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12420,7 +12476,7 @@
         <v>0.17709815833193046</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12477,7 +12533,7 @@
         <v>5.4578490442953362E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12534,7 +12590,7 @@
         <v>0.12251966788897709</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12591,7 +12647,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12648,8 +12704,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>453</v>
+      <c r="E78" s="295" t="s">
+        <v>461</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12707,7 +12763,7 @@
         <v>6.8575115644274815E-3</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12764,7 +12820,7 @@
         <v>6.0562894138340359E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12821,7 +12877,7 @@
         <v>0.12332089003957052</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12878,7 +12934,7 @@
         <v>3.0830222509892629E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12931,12 +12987,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12993,7 +13049,7 @@
         <v>9.2490667529677884E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -13045,26 +13101,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13074,7 +13130,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13100,7 +13156,7 @@
         <v>9.2490667529677884E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13149,14 +13205,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13168,7 +13224,7 @@
         <f>G90</f>
         <v>0.53959586373565716</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.53959586373565716</v>
@@ -13224,7 +13280,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1394746.258670188</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1394746.258670188</v>
@@ -13279,7 +13335,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.57639325256115148</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.55079002762885332</v>
@@ -13328,13 +13384,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>3.5313865427726257E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>3.5313865427726257E-2</v>
@@ -13382,7 +13438,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13391,7 +13447,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13415,7 +13471,7 @@
         <v>-8.7642097511117734E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13472,7 +13528,7 @@
         <v>-0.11093531040277549</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13550,7 +13606,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13565,7 +13621,7 @@
         <v>35708406</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13622,7 +13678,7 @@
         <v>1250023</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13679,7 +13735,7 @@
         <v>2598226</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13736,7 +13792,7 @@
         <v>9604717</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13793,7 +13849,7 @@
         <v>26103689</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13842,7 +13898,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13851,7 +13907,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13877,7 +13933,7 @@
         <v>4.7779279994405725E-2</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13934,7 +13990,7 @@
         <v>9.9311266706888432E-2</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13991,7 +14047,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -14010,63 +14066,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>0</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4709732968262565</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.96304737643927274</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.6269053137360105</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.6269426147081751</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>2.3369811952562229</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>2.3374185439481701</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.250085896477759</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.4203453141742608</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>11.152390228065904</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14074,58 +14130,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>0</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>2.0773328106076989</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.3549323555766097</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.8733723206359201</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>1.9746300057985322</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.5408832696503736</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>2.8191980169637287</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>2.5561117493864103</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>4.3015244745575218</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>57.096567771960444</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14134,7 +14190,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14190,7 +14246,7 @@
         <f>C81</f>
         <v>0.12332089003957052</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.12655185824614926</v>
@@ -14244,7 +14300,7 @@
         <f>C4/C101</f>
         <v>0.73266920679685343</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>0.80305021176246283</v>
@@ -14299,7 +14355,7 @@
         <v>1.3679448142367923</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14356,7 +14412,7 @@
         <v>0.12279546480584161</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14452,7 +14508,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14477,7 +14533,7 @@
         <v>1.0145850899563691</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14534,7 +14590,7 @@
         <v>6.6399547772013678E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14583,7 +14639,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15316,7 +15372,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15384,7 +15440,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15394,7 +15450,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15412,10 +15468,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15430,8 +15486,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15446,8 +15502,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15462,8 +15518,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16808,7 +16864,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16839,12 +16895,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16859,6 +16915,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>442</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>1394746.258670188</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>17434328.233377349</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>20</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>9.9831116323349498</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>1470407.1447621584</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>1361488.0970019985</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>1550172.4115962433</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>1329022.9866222935</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>1634264.7097670413</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>1297332.0169745474</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>1722918.7680096526</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>1266396.7284303815</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>1816382.0484033101</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>1236199.1015370418</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>1914915.4371178809</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>1206721.546521272</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>2018793.9726313376</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>1177946.8930434727</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>2128307.6134508858</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>1149858.3801961723</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>2243762.0474807099</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>1122439.6467409928</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>2365479.5452955351</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>1095674.7215784118</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>2493799.8597017792</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0.42888285933767062</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>1069548.014444781</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>2629081.1740972498</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0.39711375864599124</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>1044044.3068311745</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>2771701.1022765688</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0.36769792467221413</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>1019148.7431187826</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>2922057.7424731036</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0.34046104136316119</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>994846.82192568074</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>3080570.7885795766</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0.31524170496588994</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>971124.3876599418</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>3247682.7016491252</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0.29189046756100923</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>947967.62227416481</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>3423859.9449468558</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0.27026895144537894</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>925363.03721661959</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>3609594.2859993107</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0.25024902911609154</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>903297.46557431913</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>3805404.1692762952</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0.23171206399638106</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>881758.05440344417</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>4011836.1633366621</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>5.4247061515052201E-2</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0.21454820740405653</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>860732.25724264863</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>18380089.30952698</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.21454820740405653</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>3943415.2132854764</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>25804326.04262362</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>25804326.04262362</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.05</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>17434328.233377345</v>
+      </c>
+      <c r="C51" s="124">
+        <v>17996850.926218797</v>
+      </c>
+      <c r="D51" s="124">
+        <v>18872453.816006616</v>
+      </c>
+      <c r="E51" s="124">
+        <v>19173177.553779721</v>
+      </c>
+      <c r="F51" s="124">
+        <v>20422922.753029287</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>17434328.233377345</v>
+      </c>
+      <c r="C52" s="124">
+        <v>18559891.613567758</v>
+      </c>
+      <c r="D52" s="124">
+        <v>20463920.872148946</v>
+      </c>
+      <c r="E52" s="124">
+        <v>21162955.268989965</v>
+      </c>
+      <c r="F52" s="124">
+        <v>24332972.541716758</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>17434328.233377341</v>
+      </c>
+      <c r="C53" s="124">
+        <v>19256810.5807156</v>
+      </c>
+      <c r="D53" s="124">
+        <v>22594578.564841274</v>
+      </c>
+      <c r="E53" s="124">
+        <v>23899971.284159724</v>
+      </c>
+      <c r="F53" s="124">
+        <v>30350974.821000371</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>17434328.233377341</v>
+      </c>
+      <c r="C54" s="124">
+        <v>19966859.245056447</v>
+      </c>
+      <c r="D54" s="124">
+        <v>24954571.182261888</v>
+      </c>
+      <c r="E54" s="124">
+        <v>27022162.598057847</v>
+      </c>
+      <c r="F54" s="124">
+        <v>38126164.244786076</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>17434328.233377341</v>
+      </c>
+      <c r="C55" s="124">
+        <v>20627243.903500639</v>
+      </c>
+      <c r="D55" s="124">
+        <v>27351098.432762552</v>
+      </c>
+      <c r="E55" s="124">
+        <v>30294124.165115036</v>
+      </c>
+      <c r="F55" s="124">
+        <v>47450808.37566115</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>17434328.233377337</v>
+      </c>
+      <c r="C56" s="124">
+        <v>21209795.037155975</v>
+      </c>
+      <c r="D56" s="124">
+        <v>29668650.248105202</v>
+      </c>
+      <c r="E56" s="124">
+        <v>33565669.929902732</v>
+      </c>
+      <c r="F56" s="124">
+        <v>58217498.523299791</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.02</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.05</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.06</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.1</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>7.3100000000000005</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>7.3099999999999987</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>7.5458588658895751</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>7.9129884184980401</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>8.0390781934348716</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>8.5630810276263549</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>7.3099999999999987</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>7.7819349205230592</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>8.5802710361401857</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>8.8733675852303371</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>10.202516948110251</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>7.3099999999999961</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>8.074144495888147</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>9.4736296746315158</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>10.020964831483116</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>12.725791494320928</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>7.3099999999999961</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>8.3718591922533712</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>10.463145634318295</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>11.330061356401187</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>15.985833058702053</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>7.3099999999999961</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>8.6487503800643886</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>11.467980117566187</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>12.701954711569174</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>19.895541978039766</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>7.3099999999999943</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>8.8930069255427444</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>12.439701169468908</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>14.073673725945289</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>24.409883105824761</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.1</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>30</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>24.409883105824761</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>20</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>11.330061356401187</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.22499999999999992</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.05</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>20</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>10.463145634318295</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.495</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.02</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>20</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>8.3718591922533712</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>30</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>7.3099999999999943</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16879,19 +18386,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-15.28</v>
       </c>
@@ -16908,19 +18415,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.53959586373565716</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>0.53959586373565716</v>
       </c>
@@ -16934,13 +18441,13 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>24.651966296664511</v>
       </c>
@@ -16957,15 +18464,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16982,12 +18489,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17004,37 +18511,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>449</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17048,12 +18555,12 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17066,12 +18573,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17084,8 +18591,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.10082655111598315</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17101,7 +18608,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17111,25 +18618,25 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17139,23 +18646,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>18.020262851044695</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17175,8 +18682,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17186,23 +18693,23 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>23.490739162673215</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17212,8 +18719,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17233,8 +18740,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17244,23 +18751,23 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>19.862510635062108</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17270,8 +18777,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17291,8 +18798,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17302,23 +18809,23 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>24.994774330036517</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17329,8 +18836,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17392,8 +18899,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17403,23 +18910,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>18.020262851044684</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17429,12 +18936,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17450,8 +18957,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17461,23 +18968,23 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>47.687305325679809</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17487,8 +18994,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17503,16 +19010,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17521,10 +19028,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17536,8 +19043,8 @@
         <v>20</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17548,8 +19055,8 @@
         <v>5.4247061515052201E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17557,30 +19064,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>24.108879276748858</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17588,38 +19095,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>0.22137803669855521</v>
       </c>
@@ -17639,10 +19146,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17663,12 +19170,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17712,7 +19219,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.60001102388865557</v>
       </c>
@@ -17722,14 +19229,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>15.28</v>
       </c>
@@ -17740,9 +19247,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.19487700460896362</v>
       </c>
@@ -17752,12 +19259,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17801,28 +19308,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.39987248390043673</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17834,7 +19341,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17846,23 +19353,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>20.531767931844971</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>0.14849649523441566</v>
       </c>
@@ -17872,12 +19379,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17906,19 +19413,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>18.584622775616808</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.22913783912219288</v>
       </c>
@@ -17927,33 +19434,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65A8D80-D609-7C47-A7D0-479C259309C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B973B10E-0B26-1549-81DD-243A5F837141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="5080" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3877,6 +3877,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3912,9 +3915,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4223,7 +4223,7 @@
       <c r="C1" s="44">
         <v>45778</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>462</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4368,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>1.0837740600000001</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4378,13 +4378,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4460,14 +4460,14 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>24.112370432928856</v>
+        <v>24.112370432928852</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19487700460896362</v>
+        <v>0.19487700460896318</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>9.6446823610846675</v>
+        <v>9.6446823610846657</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>14.470496975186144</v>
+        <v>14.470496975186142</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>20.531767931844971</v>
+        <v>20.531767931844968</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>18.584622775616808</v>
+        <v>18.584622775616804</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4584,22 +4584,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4611,13 +4611,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4637,13 +4637,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4672,13 +4672,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4764,13 +4764,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4786,13 +4786,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4808,22 +4808,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4867,14 +4867,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5313865427726257E-2</v>
+        <v>3.5313865427726264E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
       </c>
       <c r="F70" s="345">
         <f>Normalized_FCF!C92</f>
-        <v>0.57639325256115148</v>
+        <v>0.57639325256115159</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
@@ -4892,22 +4892,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4951,22 +4951,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.682313624454613</v>
+        <v>12.682313624454611</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -5003,13 +5003,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5022,13 +5022,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C97" s="245">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.81179849779954916</v>
+        <v>0.81179849779954893</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="C105" s="245">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>5.9142873884908855</v>
+        <v>5.9142873884908846</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C109" s="245">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.23546033589874474</v>
+        <v>0.23546033589874468</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5159,13 +5159,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C114" s="245">
         <f>BS!D47</f>
-        <v>4.5689822452120339</v>
+        <v>4.568982245212033</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5204,13 +5204,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>24.112370432928856</v>
+        <v>24.112370432928852</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5353,13 +5353,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5372,22 +5372,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C138" s="235">
         <f>Scenarios!C77</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D138" s="234" t="str">
         <f>Market_currency</f>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>0.85737535199980486</v>
+        <v>0.85737535199980497</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>8.7873070090848628</v>
+        <v>8.7873070090848611</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>9.6446823610846675</v>
+        <v>9.6446823610846657</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>13.36410917162844</v>
+        <v>13.364109171628439</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.15">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>14.470496975186144</v>
+        <v>14.470496975186142</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>1.3905908747645797</v>
+        <v>1.3905908747645801</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.15">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>19.141177057080391</v>
+        <v>19.141177057080387</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.15">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>20.531767931844971</v>
+        <v>20.531767931844968</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>1.3018306675922118</v>
+        <v>1.3018306675922122</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>17.282792108024594</v>
+        <v>17.282792108024591</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>18.584622775616808</v>
+        <v>18.584622775616804</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5720,13 +5720,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5763,13 +5763,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5777,22 +5777,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C25" s="39">
         <f>(0.2073+0.3775)/Exchange_Rate</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
@@ -9257,11 +9257,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>10.944956641615038</v>
+        <v>10.944956641615036</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>4.5689822452120339</v>
+        <v>4.568982245212033</v>
       </c>
       <c r="F47" s="275"/>
     </row>
@@ -9667,11 +9667,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-2098335.05720622</v>
+        <v>-2098335.0572062195</v>
       </c>
       <c r="D86" s="245">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-0.81179849779954905</v>
+        <v>-0.81179849779954882</v>
       </c>
       <c r="E86" s="262" t="str">
         <f>Market_currency</f>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>15287237.65725345</v>
+        <v>15287237.657253448</v>
       </c>
       <c r="D87" s="245">
         <f>C87*scaling_factor/Common_Shares</f>
@@ -9701,11 +9701,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>608617.383177132</v>
+        <v>608617.38317713188</v>
       </c>
       <c r="D88" s="245">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.23546033589874474</v>
+        <v>0.23546033589874468</v>
       </c>
       <c r="E88" s="262" t="str">
         <f>Market_currency</f>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>13797519.983224362</v>
+        <v>13797519.98322436</v>
       </c>
       <c r="D89" s="264">
         <f>SUM(D86:D88)</f>
@@ -13235,12 +13235,12 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="E90" s="293"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1394746.258670188</v>
+        <v>1394746.2586701883</v>
       </c>
       <c r="E91" s="293"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1394746.258670188</v>
+        <v>1394746.2586701883</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
@@ -13346,12 +13346,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.57639325256115148</v>
+        <v>0.57639325256115159</v>
       </c>
       <c r="E92" s="293"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.55079002762885332</v>
+        <v>0.55079002762885343</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13401,12 +13401,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5313865427726257E-2</v>
+        <v>3.5313865427726264E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5313865427726257E-2</v>
+        <v>3.5313865427726264E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14543,50 +14543,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>1.0145850899563691</v>
+        <v>1.0145850899563689</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="290"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>1.0617476182667274</v>
+        <v>1.0617476182667271</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>0.9462104763591227</v>
+        <v>0.94621047635912248</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2110760739766175</v>
+        <v>1.2110760739766171</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>1.460464053804593</v>
+        <v>1.4604640538045928</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>0.58675948895785512</v>
+        <v>0.58675948895785501</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>0.57813029034371066</v>
+        <v>0.57813029034371055</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>0.24865020561564941</v>
+        <v>0.24865020561564935</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>0.19013818287840256</v>
+        <v>0.19013818287840253</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>9.7033244834824631E-2</v>
+        <v>9.7033244834824617E-2</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0452893178643734E-3</v>
+        <v>5.0452893178643725E-3</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14607,43 +14607,43 @@
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9486100671906248E-2</v>
+        <v>6.9486100671906234E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.1924769395230547E-2</v>
+        <v>6.1924769395230533E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>7.9258905364961885E-2</v>
+        <v>7.9258905364961857E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>9.5580108233284888E-2</v>
+        <v>9.5580108233284874E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>3.8400490115042873E-2</v>
+        <v>3.8400490115042867E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.7835751985844941E-2</v>
+        <v>3.7835751985844934E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.6272919215683863E-2</v>
+        <v>1.627291921568386E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2443598355916399E-2</v>
+        <v>1.2443598355916397E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>6.3503432483523973E-3</v>
+        <v>6.3503432483523964E-3</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>3.3018909148327055E-4</v>
+        <v>3.3018909148327044E-4</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -15481,10 +15481,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15499,8 +15499,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15515,8 +15515,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15531,8 +15531,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="C11" s="229">
         <f>Exchange_Rate</f>
-        <v>1.0837740600000001</v>
+        <v>1.0837740599999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>24.108879276748858</v>
+        <v>24.108879276748851</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16558,23 +16558,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16585,23 +16585,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>18.020262851044691</v>
+        <v>18.020262851044688</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>18.429460677080229</v>
+        <v>18.429460677080225</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>19.066403512509272</v>
+        <v>19.066403512509268</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>19.285160020113349</v>
+        <v>19.285160020113345</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>20.1942664884197</v>
+        <v>20.194266488419697</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16612,23 +16612,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044691</v>
+        <v>18.020262851044688</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>18.839035309650104</v>
+        <v>18.8390353096501</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>20.224089891864224</v>
+        <v>20.224089891864217</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>20.732590898404116</v>
+        <v>20.732590898404112</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>23.038567515885259</v>
+        <v>23.038567515885255</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16639,23 +16639,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044684</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>19.345997481859229</v>
+        <v>19.345997481859225</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>21.774001578931642</v>
+        <v>21.774001578931635</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>22.723587915030411</v>
+        <v>22.723587915030407</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>27.416263706808262</v>
+        <v>27.416263706808259</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16666,23 +16666,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044688</v>
+        <v>18.020262851044684</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>19.862510635062108</v>
+        <v>19.862510635062101</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>23.490739162673215</v>
+        <v>23.490739162673211</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>24.994774330036517</v>
+        <v>24.994774330036513</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>33.072196613544115</v>
+        <v>33.072196613544108</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16693,23 +16693,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044684</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>20.342896528860614</v>
+        <v>20.34289652886061</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>25.234053260787658</v>
+        <v>25.23405326078765</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>27.374908637771913</v>
+        <v>27.37490863777191</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>39.855254711405735</v>
+        <v>39.855254711405728</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.15">
@@ -16719,23 +16719,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>18.020262851044684</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>20.766663712798017</v>
+        <v>20.76666371279801</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>26.91991798523571</v>
+        <v>26.919917985235706</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>29.75474047702577</v>
+        <v>29.754740477025763</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>47.687305325679809</v>
+        <v>47.687305325679802</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>47.687305325679809</v>
+        <v>47.687305325679802</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16792,7 +16792,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>24.994774330036517</v>
+        <v>24.994774330036513</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>23.490739162673215</v>
+        <v>23.490739162673211</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>19.862510635062108</v>
+        <v>19.862510635062101</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>18.020262851044684</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C91</f>
-        <v>1394746.258670188</v>
+        <v>1394746.2586701883</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17005,14 +17005,14 @@
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>17434328.233377349</v>
+        <v>17434328.233377352</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -17021,7 +17021,7 @@
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>7.3100000000000005</v>
+        <v>7.31</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17074,7 +17074,7 @@
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>9.9831116323349498</v>
+        <v>9.9831116323349516</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17109,7 +17109,7 @@
       </c>
       <c r="C16" s="124">
         <f>C4*(1+D16)</f>
-        <v>1470407.1447621584</v>
+        <v>1470407.1447621586</v>
       </c>
       <c r="D16" s="139">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1361488.0970019985</v>
+        <v>1361488.0970019987</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="C17" s="124">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>1550172.4115962433</v>
+        <v>1550172.4115962435</v>
       </c>
       <c r="D17" s="139">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>1329022.9866222935</v>
+        <v>1329022.9866222937</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="C18" s="124">
         <f t="shared" si="2"/>
-        <v>1634264.7097670413</v>
+        <v>1634264.7097670417</v>
       </c>
       <c r="D18" s="139">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>1297332.0169745474</v>
+        <v>1297332.0169745476</v>
       </c>
       <c r="H18" s="121"/>
     </row>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="C19" s="124">
         <f t="shared" si="2"/>
-        <v>1722918.7680096526</v>
+        <v>1722918.7680096531</v>
       </c>
       <c r="D19" s="139">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>1266396.7284303815</v>
+        <v>1266396.728430382</v>
       </c>
       <c r="H19" s="121"/>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="C20" s="124">
         <f t="shared" si="2"/>
-        <v>1816382.0484033101</v>
+        <v>1816382.0484033104</v>
       </c>
       <c r="D20" s="139">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>1236199.1015370418</v>
+        <v>1236199.1015370421</v>
       </c>
       <c r="H20" s="121"/>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C21" s="124">
         <f t="shared" si="2"/>
-        <v>1914915.4371178809</v>
+        <v>1914915.4371178811</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
@@ -17241,7 +17241,7 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" si="2"/>
-        <v>2018793.9726313376</v>
+        <v>2018793.9726313378</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
@@ -17263,7 +17263,7 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2128307.6134508858</v>
+        <v>2128307.6134508862</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>1149858.3801961723</v>
+        <v>1149858.3801961725</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -17285,7 +17285,7 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2243762.0474807099</v>
+        <v>2243762.0474807103</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
@@ -17297,7 +17297,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>1122439.6467409928</v>
+        <v>1122439.646740993</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>2365479.5452955351</v>
+        <v>2365479.5452955356</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
@@ -17319,7 +17319,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>1095674.7215784118</v>
+        <v>1095674.721578412</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -17329,7 +17329,7 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>2493799.8597017792</v>
+        <v>2493799.8597017797</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
@@ -17351,7 +17351,7 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>2629081.1740972498</v>
+        <v>2629081.1740972502</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
@@ -17363,7 +17363,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>1044044.3068311745</v>
+        <v>1044044.3068311748</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>2771701.1022765688</v>
+        <v>2771701.1022765692</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1019148.7431187826</v>
+        <v>1019148.7431187828</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>2922057.7424731036</v>
+        <v>2922057.742473104</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>994846.82192568074</v>
+        <v>994846.82192568085</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>3080570.7885795766</v>
+        <v>3080570.7885795771</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
@@ -17429,7 +17429,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>971124.3876599418</v>
+        <v>971124.38765994192</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>3247682.7016491252</v>
+        <v>3247682.7016491257</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>947967.62227416481</v>
+        <v>947967.62227416493</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>3423859.9449468558</v>
+        <v>3423859.9449468562</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>925363.03721661959</v>
+        <v>925363.0372166197</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -17483,7 +17483,7 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>3609594.2859993107</v>
+        <v>3609594.2859993111</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
@@ -17495,7 +17495,7 @@
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>903297.46557431913</v>
+        <v>903297.46557431924</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -17505,7 +17505,7 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>3805404.1692762952</v>
+        <v>3805404.1692762962</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
@@ -17517,7 +17517,7 @@
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>881758.05440344417</v>
+        <v>881758.0544034444</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>4011836.1633366621</v>
+        <v>4011836.1633366626</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>860732.25724264863</v>
+        <v>860732.25724264875</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -17769,7 +17769,7 @@
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>18380089.30952698</v>
+        <v>18380089.309526984</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>3943415.2132854764</v>
+        <v>3943415.2132854774</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>25804326.04262362</v>
+        <v>25804326.042623624</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -17813,7 +17813,7 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>25804326.04262362</v>
+        <v>25804326.042623624</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17843,19 +17843,19 @@
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>17434328.233377345</v>
+        <v>17434328.233377352</v>
       </c>
       <c r="C51" s="124">
-        <v>17996850.926218797</v>
+        <v>17996850.9262188</v>
       </c>
       <c r="D51" s="124">
-        <v>18872453.816006616</v>
+        <v>18872453.816006619</v>
       </c>
       <c r="E51" s="124">
-        <v>19173177.553779721</v>
+        <v>19173177.553779725</v>
       </c>
       <c r="F51" s="124">
-        <v>20422922.753029287</v>
+        <v>20422922.753029291</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -17867,7 +17867,7 @@
         <v>17434328.233377345</v>
       </c>
       <c r="C52" s="124">
-        <v>18559891.613567758</v>
+        <v>18559891.613567762</v>
       </c>
       <c r="D52" s="124">
         <v>20463920.872148946</v>
@@ -17885,16 +17885,16 @@
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>17434328.233377341</v>
+        <v>17434328.233377345</v>
       </c>
       <c r="C53" s="124">
-        <v>19256810.5807156</v>
+        <v>19256810.580715604</v>
       </c>
       <c r="D53" s="124">
-        <v>22594578.564841274</v>
+        <v>22594578.564841278</v>
       </c>
       <c r="E53" s="124">
-        <v>23899971.284159724</v>
+        <v>23899971.284159727</v>
       </c>
       <c r="F53" s="124">
         <v>30350974.821000371</v>
@@ -17906,16 +17906,16 @@
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>17434328.233377341</v>
+        <v>17434328.233377345</v>
       </c>
       <c r="C54" s="124">
-        <v>19966859.245056447</v>
+        <v>19966859.24505645</v>
       </c>
       <c r="D54" s="124">
-        <v>24954571.182261888</v>
+        <v>24954571.182261895</v>
       </c>
       <c r="E54" s="124">
-        <v>27022162.598057847</v>
+        <v>27022162.598057855</v>
       </c>
       <c r="F54" s="124">
         <v>38126164.244786076</v>
@@ -17930,16 +17930,16 @@
         <v>17434328.233377341</v>
       </c>
       <c r="C55" s="124">
-        <v>20627243.903500639</v>
+        <v>20627243.903500643</v>
       </c>
       <c r="D55" s="124">
-        <v>27351098.432762552</v>
+        <v>27351098.43276256</v>
       </c>
       <c r="E55" s="124">
-        <v>30294124.165115036</v>
+        <v>30294124.165115044</v>
       </c>
       <c r="F55" s="124">
-        <v>47450808.37566115</v>
+        <v>47450808.375661165</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -17948,19 +17948,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>17434328.233377337</v>
+        <v>17434328.233377341</v>
       </c>
       <c r="C56" s="124">
-        <v>21209795.037155975</v>
+        <v>21209795.037155978</v>
       </c>
       <c r="D56" s="124">
-        <v>29668650.248105202</v>
+        <v>29668650.248105213</v>
       </c>
       <c r="E56" s="124">
-        <v>33565669.929902732</v>
+        <v>33565669.92990274</v>
       </c>
       <c r="F56" s="124">
-        <v>58217498.523299791</v>
+        <v>58217498.523299798</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -18010,23 +18010,23 @@
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>7.3100000000000005</v>
+        <v>7.31</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>7.3100000000000005</v>
+        <v>7.31</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>7.3100000000000005</v>
+        <v>7.31</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>7.3100000000000005</v>
+        <v>7.31</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>7.3100000000000005</v>
+        <v>7.31</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -18041,11 +18041,11 @@
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>7.5458588658895751</v>
+        <v>7.5458588658895742</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>7.9129884184980401</v>
+        <v>7.9129884184980392</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
@@ -18064,11 +18064,11 @@
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>7.3099999999999987</v>
+        <v>7.3099999999999969</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>7.7819349205230592</v>
+        <v>7.7819349205230601</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
@@ -18076,11 +18076,11 @@
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>8.8733675852303371</v>
+        <v>8.8733675852303353</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>10.202516948110251</v>
+        <v>10.202516948110249</v>
       </c>
       <c r="H62" s="121"/>
     </row>
@@ -18091,11 +18091,11 @@
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>7.3099999999999961</v>
+        <v>7.3099999999999969</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>8.074144495888147</v>
+        <v>8.0741444958881452</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
@@ -18103,11 +18103,11 @@
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>10.020964831483116</v>
+        <v>10.020964831483115</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>12.725791494320928</v>
+        <v>12.725791494320926</v>
       </c>
       <c r="H63" s="121"/>
     </row>
@@ -18118,7 +18118,7 @@
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>7.3099999999999961</v>
+        <v>7.3099999999999969</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>10.463145634318295</v>
+        <v>10.463145634318296</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>15.985833058702053</v>
+        <v>15.985833058702049</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -18145,7 +18145,7 @@
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>7.3099999999999961</v>
+        <v>7.3099999999999952</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
@@ -18161,7 +18161,7 @@
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>19.895541978039766</v>
+        <v>19.89554197803977</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>7.3099999999999943</v>
+        <v>7.3099999999999952</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
@@ -18179,15 +18179,15 @@
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>12.439701169468908</v>
+        <v>12.439701169468909</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>14.073673725945289</v>
+        <v>14.073673725945291</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>24.409883105824761</v>
+        <v>24.409883105824758</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
@@ -18222,7 +18222,7 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>24.409883105824761</v>
+        <v>24.409883105824758</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>10.463145634318295</v>
+        <v>10.463145634318296</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18313,7 +18313,7 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>7.3099999999999943</v>
+        <v>7.3099999999999952</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
@@ -18433,7 +18433,7 @@
       </c>
       <c r="I4" s="125">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.15">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="I5" s="125">
         <f t="shared" si="0"/>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.15">
@@ -18462,7 +18462,7 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>24.651966296664511</v>
+        <v>24.651966296664508</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -18477,11 +18477,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 20-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 李宁(2331.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18502,8 +18502,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18524,8 +18524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18535,8 +18535,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18549,8 +18549,8 @@
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18568,8 +18568,8 @@
         <v>8.3043513409933434E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18586,8 +18586,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.2379152048964186E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18604,8 +18604,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.10082655111598315</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18631,21 +18631,21 @@
       <c r="C18" s="151">
         <v>20</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18659,8 +18659,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18668,14 +18668,14 @@
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>18.020262851044695</v>
+        <v>18.020262851044691</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18695,8 +18695,8 @@
         <v>20</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18706,8 +18706,8 @@
         <v>0.05</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18715,14 +18715,14 @@
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>23.490739162673215</v>
+        <v>23.490739162673211</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18732,8 +18732,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18753,8 +18753,8 @@
         <v>20</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18764,8 +18764,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18773,14 +18773,14 @@
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>19.862510635062108</v>
+        <v>19.862510635062101</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18790,8 +18790,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18811,8 +18811,8 @@
         <v>20</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18822,8 +18822,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18831,14 +18831,14 @@
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>24.994774330036517</v>
+        <v>24.994774330036513</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18849,8 +18849,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18858,7 +18858,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>23.141102248991817</v>
+        <v>23.141102248991814</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18912,8 +18912,8 @@
         <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18923,8 +18923,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18932,14 +18932,14 @@
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>18.020262851044684</v>
+        <v>18.020262851044681</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18949,8 +18949,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18970,8 +18970,8 @@
         <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18981,8 +18981,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18990,14 +18990,14 @@
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>47.687305325679809</v>
+        <v>47.687305325679802</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -19007,8 +19007,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>24.112370432928856</v>
+        <v>24.112370432928852</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>24.108879276748858</v>
+        <v>24.108879276748851</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.22137803669855521</v>
+        <v>0.22137803669855524</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0.53959586373565716</v>
+        <v>0.53959586373565727</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.85737535199980486</v>
+        <v>0.85737535199980497</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>8.7873070090848628</v>
+        <v>8.7873070090848611</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>9.6446823610846675</v>
+        <v>9.6446823610846657</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19487700460896362</v>
+        <v>0.19487700460896318</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.15">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>13.36410917162844</v>
+        <v>13.364109171628439</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>14.470496975186144</v>
+        <v>14.470496975186142</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.3905908747645797</v>
+        <v>1.3905908747645801</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>19.141177057080391</v>
+        <v>19.141177057080387</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>20.531767931844971</v>
+        <v>20.531767931844968</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19410,7 +19410,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.3018306675922118</v>
+        <v>1.3018306675922122</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -19420,7 +19420,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>17.282792108024594</v>
+        <v>17.282792108024591</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>18.584622775616808</v>
+        <v>18.584622775616804</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>

--- a/financial_models/opportunities/2331.HK_Valuation.xlsx
+++ b/financial_models/opportunities/2331.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B973B10E-0B26-1549-81DD-243A5F837141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3F476E-ED8F-4EFF-B022-508909BD0F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="5080" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2505,7 +2494,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3918,7 +3907,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4207,7 +4196,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4216,7 +4205,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4222,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4247,7 +4236,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>417</v>
       </c>
@@ -4256,7 +4245,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4264,7 +4253,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4273,7 +4262,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4283,7 +4272,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4293,17 +4282,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>419</v>
       </c>
@@ -4315,7 +4304,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4325,7 +4314,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>418</v>
       </c>
@@ -4335,7 +4324,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>422</v>
       </c>
@@ -4349,7 +4338,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>421</v>
       </c>
@@ -4363,7 +4352,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4373,11 +4362,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4386,14 +4375,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4408,7 +4397,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4421,7 +4410,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>436</v>
       </c>
@@ -4429,7 +4418,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>437</v>
       </c>
@@ -4437,7 +4426,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4453,28 +4442,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>24.112370432928852</v>
+        <v>25.387759624610275</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19487700460896318</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.21459142389463892</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>435</v>
       </c>
@@ -4493,13 +4482,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>9.6446823610846657</v>
+        <v>10.823985104487992</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4509,16 +4498,16 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>14.470496975186142</v>
+        <v>15.177372329534087</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4531,13 +4520,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>20.531767931844968</v>
+        <v>21.83937837877221</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4547,16 +4536,16 @@
         <v>438</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>18.584622775616804</v>
+        <v>19.498771233893212</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4569,11 +4558,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4583,7 +4572,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4592,7 +4581,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4601,7 +4590,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4610,7 +4599,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4619,7 +4608,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4632,11 +4621,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4645,7 +4634,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4658,7 +4647,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4671,7 +4660,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4680,7 +4669,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4693,7 +4682,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4702,7 +4691,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4717,7 +4706,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4732,7 +4721,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4745,12 +4734,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4763,7 +4752,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4772,7 +4761,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4785,7 +4774,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4794,7 +4783,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4807,7 +4796,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4816,7 +4805,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4825,7 +4814,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4838,7 +4827,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4851,7 +4840,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4861,7 +4850,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4877,7 +4866,7 @@
         <v>0.57639325256115159</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4887,10 +4876,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4900,7 +4889,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4909,21 +4898,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>432</v>
       </c>
@@ -4932,25 +4921,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4959,7 +4948,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4968,7 +4957,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4976,20 +4965,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>12.682313624454611</v>
+        <v>13.527801199418253</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4999,10 +4988,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5011,17 +5000,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5030,7 +5019,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5043,7 +5032,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5056,7 +5045,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5065,7 +5054,7 @@
         <v>0.36794481423679237</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5074,7 +5063,7 @@
         <v>7.4171010848313429E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5083,12 +5072,12 @@
         <v>0.60402076709908736</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5101,7 +5090,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5114,7 +5103,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5127,12 +5116,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5145,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5158,7 +5147,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5167,20 +5156,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>451</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>18.020262851044691</v>
+        <v>18.865750426008336</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5203,7 +5192,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5212,7 +5201,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5229,7 +5218,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5244,14 +5233,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>47.69 HKD</v>
+        <v>51.37 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5266,14 +5255,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>24.99 HKD</v>
+        <v>26.28 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5288,14 +5277,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>23.49 HKD</v>
+        <v>24.68 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.495</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5310,14 +5299,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>19.86 HKD</v>
+        <v>20.82 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5332,27 +5321,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>18.02 HKD</v>
+        <v>18.87 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>24.112370432928852</v>
+        <v>25.387759624610275</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5361,7 +5350,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5371,7 +5360,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5380,7 +5369,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5389,12 +5378,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5403,16 +5392,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5425,7 +5414,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5438,49 +5427,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>0.85737535199980497</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.89425027386664846</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>8.7873070090848611</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>9.929734830621344</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>9.6446823610846657</v>
+        <v>10.823985104487992</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>418</v>
       </c>
@@ -5493,21 +5482,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.60001102388865557</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.57365339578859553</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5516,7 +5505,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5526,30 +5515,30 @@
         <v>1.1063878035577037</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>13.364109171628439</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>14.070984525976383</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>14.470496975186142</v>
+        <v>15.177372329534087</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>418</v>
       </c>
@@ -5562,63 +5551,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.39987248390043673</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.40217756296930141</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>1.3905908747645801</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>1.4032329327730193</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>19.141177057080387</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>20.436145445999191</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>20.531767931844968</v>
+        <v>21.83937837877221</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>418</v>
       </c>
@@ -5631,21 +5620,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.14849649523441566</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.13976740359548512</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>425</v>
       </c>
@@ -5654,7 +5643,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5664,30 +5653,30 @@
         <v>1.3018306675922122</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>17.282792108024591</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>18.196940566300999</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>18.584622775616804</v>
+        <v>19.498771233893212</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>418</v>
       </c>
@@ -5700,16 +5689,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22913783912219288</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.23038589225344475</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5719,7 +5708,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5728,12 +5717,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5742,27 +5731,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5771,12 +5760,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5785,7 +5774,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5794,22 +5783,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5870,15 +5859,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5927,7 +5916,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5943,7 +5932,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5951,7 +5940,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5987,7 +5976,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6023,7 +6012,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6069,7 +6058,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6105,7 +6094,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6121,7 +6110,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6157,7 +6146,7 @@
       </c>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6173,7 +6162,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6189,7 +6178,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6213,7 +6202,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6237,7 +6226,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6273,7 +6262,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6309,7 +6298,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6345,13 +6334,13 @@
       </c>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6367,7 +6356,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6395,7 +6384,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6421,7 +6410,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6455,7 +6444,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6489,7 +6478,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6523,7 +6512,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6543,7 +6532,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6551,7 +6540,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6588,7 +6577,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6625,7 +6614,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6662,7 +6651,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6699,7 +6688,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6736,7 +6725,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6752,12 +6741,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6806,7 +6795,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6855,7 +6844,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6904,7 +6893,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6953,7 +6942,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7002,7 +6991,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7051,7 +7040,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7100,7 +7089,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7149,7 +7138,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7198,7 +7187,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7247,7 +7236,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7296,7 +7285,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7345,7 +7334,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7394,12 +7383,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7448,7 +7437,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7497,12 +7486,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7551,7 +7540,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7600,7 +7589,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7649,7 +7638,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7698,13 +7687,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7753,7 +7742,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7802,7 +7791,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7851,7 +7840,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7900,7 +7889,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7949,12 +7938,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8004,7 +7993,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8053,7 +8042,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8103,7 +8092,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8152,7 +8141,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8202,7 +8191,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8218,13 +8207,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8273,7 +8262,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8307,7 +8296,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8341,7 +8330,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8390,7 +8379,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8471,7 +8460,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8482,7 +8471,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8498,7 +8487,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8509,7 +8498,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8529,7 +8518,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8552,7 +8541,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8573,7 +8562,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8594,7 +8583,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8615,7 +8604,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8636,7 +8625,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8657,7 +8646,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8669,7 +8658,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8681,7 +8670,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8705,12 +8694,12 @@
         <v>14202944</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8730,7 +8719,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8750,7 +8739,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8770,7 +8759,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8790,7 +8779,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8810,7 +8799,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8831,7 +8820,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8851,7 +8840,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8871,7 +8860,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8883,7 +8872,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8895,7 +8884,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8919,7 +8908,7 @@
         <v>2638342</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8936,7 +8925,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8955,7 +8944,7 @@
         <v>10897009.050000001</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8970,7 +8959,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8989,7 +8978,7 @@
         <v>10897009.050000001</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9005,7 +8994,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9022,7 +9011,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9042,7 +9031,7 @@
         <v>20501726.050000001</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9053,7 +9042,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9066,7 +9055,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9085,7 +9074,7 @@
         <v>3660440.05</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9101,7 +9090,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9117,7 +9106,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9133,7 +9122,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9152,7 +9141,7 @@
         <v>633798.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9172,7 +9161,7 @@
         <v>16841286</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9192,7 +9181,7 @@
         <v>16279713.800000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9211,7 +9200,7 @@
         <v>561572.19999999995</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9222,7 +9211,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9236,7 +9225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9250,7 +9239,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9265,10 +9254,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9281,7 +9270,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9295,7 +9284,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9306,10 +9295,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9321,7 +9310,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9335,7 +9324,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9349,10 +9338,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9364,7 +9353,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9375,7 +9364,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9386,10 +9375,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9401,7 +9390,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9417,7 +9406,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9428,7 +9417,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9442,7 +9431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9458,7 +9447,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9468,7 +9457,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9478,7 +9467,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9488,7 +9477,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9498,10 +9487,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9513,7 +9502,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9529,7 +9518,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9545,7 +9534,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9558,7 +9547,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9571,10 +9560,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9586,7 +9575,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9600,7 +9589,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9614,7 +9603,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9628,7 +9617,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9642,7 +9631,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9653,7 +9642,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9661,7 +9650,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9678,7 +9667,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9695,7 +9684,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9712,7 +9701,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9743,19 +9732,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9812,7 +9801,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9835,7 +9824,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9849,7 +9838,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9906,7 +9895,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9961,7 +9950,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10016,7 +10005,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10071,7 +10060,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10128,7 +10117,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10183,7 +10172,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10238,7 +10227,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10295,7 +10284,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10350,7 +10339,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10405,7 +10394,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10460,7 +10449,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10517,7 +10506,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10574,7 +10563,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10600,7 +10589,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10625,7 +10614,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10682,7 +10671,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10701,7 +10690,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10724,7 +10713,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10745,7 +10734,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10802,7 +10791,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10859,7 +10848,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10916,18 +10905,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10986,7 +10975,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11046,7 +11035,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11101,18 +11090,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11169,7 +11158,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11228,7 +11217,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11285,18 +11274,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11354,7 +11343,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11412,7 +11401,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11467,18 +11456,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11536,10 +11525,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11562,14 +11551,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11624,7 +11613,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11679,7 +11668,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11736,7 +11725,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11791,11 +11780,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11805,7 +11794,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11832,7 +11821,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11859,7 +11848,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11914,11 +11903,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11928,7 +11917,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11983,7 +11972,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12038,7 +12027,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12093,7 +12082,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12148,7 +12137,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12204,7 +12193,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12259,11 +12248,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12273,7 +12262,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12298,7 +12287,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12323,7 +12312,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12348,7 +12337,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12375,10 +12364,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12401,7 +12390,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12422,7 +12411,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12479,7 +12468,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12536,7 +12525,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12593,7 +12582,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12650,7 +12639,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12707,7 +12696,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12766,7 +12755,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12823,7 +12812,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12880,7 +12869,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12937,7 +12926,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12994,7 +12983,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13052,7 +13041,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13109,7 +13098,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13135,7 +13124,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13159,7 +13148,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13216,18 +13205,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13283,7 +13272,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13339,7 +13328,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13394,7 +13383,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13449,11 +13438,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13474,7 +13463,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13531,7 +13520,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13588,10 +13577,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13614,7 +13603,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13624,7 +13613,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13681,7 +13670,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13738,7 +13727,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13795,7 +13784,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13852,7 +13841,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13909,11 +13898,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13936,7 +13925,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13993,7 +13982,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14050,7 +14039,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14077,18 +14066,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14140,7 +14129,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14192,11 +14181,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14250,7 +14239,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14305,7 +14294,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14359,7 +14348,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14415,7 +14404,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14472,7 +14461,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14491,7 +14480,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14514,7 +14503,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14535,7 +14524,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14593,7 +14582,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14650,14 +14639,14 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6284686289976797E-2</v>
+        <v>7.6284686289976811E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14700,688 +14689,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" cu